--- a/grupos/2ALCV - Estadisticos 20222.xlsx
+++ b/grupos/2ALCV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="191">
   <si>
     <t>Materia</t>
   </si>
@@ -222,16 +222,16 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Flores Ovalle Victor</t>
+  </si>
+  <si>
+    <t>Rivera Serra Alma Lilian</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Desc Desc Desc</t>
-  </si>
-  <si>
-    <t>Flores Ovalle Victor</t>
-  </si>
-  <si>
-    <t>Rivera Serra Alma Lilian</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
     <t>Medina Tolentino Francisco</t>
@@ -1077,7 +1077,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -1131,7 +1131,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>8</v>
@@ -1154,7 +1154,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>7</v>
@@ -1208,7 +1208,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -1231,7 +1231,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -1285,7 +1285,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>6</v>
@@ -1308,7 +1308,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -1362,7 +1362,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -1385,7 +1385,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -1439,7 +1439,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
         <v>10</v>
@@ -1462,7 +1462,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1516,7 +1516,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C10">
         <v>7</v>
@@ -1593,7 +1593,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>7</v>
@@ -1616,7 +1616,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -1670,7 +1670,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -1693,7 +1693,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -1747,7 +1747,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U12">
         <v>5</v>
@@ -1770,7 +1770,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C13">
         <v>7</v>
@@ -1824,7 +1824,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -1847,7 +1847,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C14">
         <v>6</v>
@@ -1901,7 +1901,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>6</v>
@@ -1924,7 +1924,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -1978,7 +1978,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U15">
         <v>6</v>
@@ -2001,7 +2001,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>8</v>
@@ -2055,7 +2055,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>8</v>
@@ -2078,7 +2078,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>6</v>
@@ -2132,7 +2132,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>6</v>
@@ -2155,7 +2155,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C18">
         <v>9</v>
@@ -2209,7 +2209,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>9</v>
@@ -2232,7 +2232,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -2286,7 +2286,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>6</v>
@@ -2309,7 +2309,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>7</v>
@@ -2363,7 +2363,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -2386,7 +2386,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C21">
         <v>7</v>
@@ -2440,7 +2440,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -2463,7 +2463,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C22">
         <v>7</v>
@@ -2517,7 +2517,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2540,7 +2540,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C23">
         <v>7</v>
@@ -2594,7 +2594,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U23">
         <v>7</v>
@@ -2617,7 +2617,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C24">
         <v>6</v>
@@ -2671,7 +2671,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>6</v>
@@ -2694,7 +2694,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C25">
         <v>10</v>
@@ -2748,7 +2748,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>10</v>
@@ -2771,7 +2771,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C26">
         <v>6</v>
@@ -2816,7 +2816,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U26">
         <v>6</v>
@@ -2836,7 +2836,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C27">
         <v>5</v>
@@ -2890,7 +2890,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U27">
         <v>5</v>
@@ -2913,7 +2913,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C28">
         <v>10</v>
@@ -2967,7 +2967,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U28">
         <v>10</v>
@@ -2990,7 +2990,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C29">
         <v>6</v>
@@ -3044,7 +3044,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U29">
         <v>6</v>
@@ -3096,7 +3096,7 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C31">
         <v>9</v>
@@ -3150,7 +3150,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U31">
         <v>9</v>
@@ -3173,7 +3173,7 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C32">
         <v>6</v>
@@ -3227,7 +3227,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U32">
         <v>6</v>
@@ -3250,7 +3250,7 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C33">
         <v>6</v>
@@ -3304,7 +3304,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U33">
         <v>6</v>
@@ -3327,7 +3327,7 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C34">
         <v>7</v>
@@ -3381,7 +3381,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U34">
         <v>7</v>
@@ -3404,7 +3404,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C35">
         <v>6</v>
@@ -3458,7 +3458,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U35">
         <v>6</v>
@@ -3481,7 +3481,7 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C36">
         <v>8</v>
@@ -3535,7 +3535,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U36">
         <v>8</v>
@@ -3558,7 +3558,7 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>7</v>
@@ -3612,7 +3612,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U37">
         <v>7</v>
@@ -3635,7 +3635,7 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C38">
         <v>7</v>
@@ -3689,7 +3689,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U38">
         <v>7</v>
@@ -3712,7 +3712,7 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C39">
         <v>5</v>
@@ -3766,7 +3766,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U39">
         <v>5</v>
@@ -3789,7 +3789,7 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C40">
         <v>6</v>
@@ -3843,7 +3843,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U40">
         <v>6</v>
@@ -3866,7 +3866,7 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C41">
         <v>10</v>
@@ -3920,7 +3920,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U41">
         <v>10</v>
@@ -3943,7 +3943,7 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C42">
         <v>9</v>
@@ -3997,7 +3997,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U42">
         <v>9</v>
@@ -4020,7 +4020,7 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C43">
         <v>7</v>
@@ -4074,7 +4074,7 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U43">
         <v>7</v>
@@ -4097,7 +4097,7 @@
         <v>52</v>
       </c>
       <c r="B44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C44">
         <v>7</v>
@@ -4151,7 +4151,7 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U44">
         <v>7</v>
@@ -4174,7 +4174,7 @@
         <v>53</v>
       </c>
       <c r="B45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C45">
         <v>8</v>
@@ -4228,7 +4228,7 @@
         <v>-1</v>
       </c>
       <c r="T45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U45">
         <v>8</v>
@@ -4251,7 +4251,7 @@
         <v>54</v>
       </c>
       <c r="B46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C46">
         <v>6</v>
@@ -4305,7 +4305,7 @@
         <v>-1</v>
       </c>
       <c r="T46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U46">
         <v>6</v>
@@ -4438,7 +4438,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -4497,7 +4497,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -4556,7 +4556,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -4615,7 +4615,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -4674,7 +4674,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -4733,7 +4733,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -4792,7 +4792,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -4851,7 +4851,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -4910,7 +4910,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C12">
         <v>53.3</v>
@@ -4969,7 +4969,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -5028,7 +5028,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -5087,7 +5087,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C15">
         <v>86.7</v>
@@ -5146,7 +5146,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -5205,7 +5205,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -5264,7 +5264,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -5323,7 +5323,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -5382,7 +5382,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -5441,7 +5441,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -5500,7 +5500,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -5559,7 +5559,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -5618,7 +5618,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C24">
         <v>100</v>
@@ -5677,7 +5677,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -5736,7 +5736,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -5786,7 +5786,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C27">
         <v>66.7</v>
@@ -5845,7 +5845,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -5904,7 +5904,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -5986,7 +5986,7 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -6045,7 +6045,7 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -6104,7 +6104,7 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -6163,7 +6163,7 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -6222,7 +6222,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -6281,7 +6281,7 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C36">
         <v>100</v>
@@ -6340,7 +6340,7 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -6399,7 +6399,7 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -6458,7 +6458,7 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C39">
         <v>66.7</v>
@@ -6517,7 +6517,7 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -6576,7 +6576,7 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C41">
         <v>100</v>
@@ -6635,7 +6635,7 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C42">
         <v>100</v>
@@ -6694,7 +6694,7 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -6753,7 +6753,7 @@
         <v>52</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C44">
         <v>100</v>
@@ -6812,7 +6812,7 @@
         <v>53</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C45">
         <v>100</v>
@@ -6871,7 +6871,7 @@
         <v>54</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C46">
         <v>100</v>
@@ -6977,13 +6977,13 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -6998,7 +6998,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J2">
         <v>100</v>
@@ -7006,7 +7006,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
@@ -7035,36 +7035,39 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
       </c>
       <c r="C4">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>54.76</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>45.24</v>
+      </c>
+      <c r="H4">
+        <v>6.5</v>
       </c>
       <c r="I4">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
@@ -7073,19 +7076,19 @@
         <v>42</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F5">
-        <v>54.76</v>
+        <v>59.52</v>
       </c>
       <c r="G5">
-        <v>45.24</v>
+        <v>40.48</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7165,7 +7168,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7206,7 +7209,7 @@
         <v>148</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>67</v>
@@ -7226,7 +7229,7 @@
         <v>148</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>68</v>
@@ -7234,22 +7237,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330061460173</v>
+        <v>22330051920231</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="D4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7266,67 +7269,67 @@
         <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920231</v>
+        <v>22330051920230</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920231</v>
+        <v>22330051920230</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920230</v>
+        <v>22330051920260</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>67</v>
@@ -7334,19 +7337,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920230</v>
+        <v>22330051920260</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
         <v>68</v>
@@ -7354,99 +7357,99 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920230</v>
+        <v>22330051920232</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920260</v>
+        <v>22330051920232</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920260</v>
+        <v>22330051920233</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920260</v>
+        <v>22330051920233</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920232</v>
+        <v>22330051920234</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D14" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>67</v>
@@ -7454,19 +7457,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920232</v>
+        <v>22330051920234</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
         <v>68</v>
@@ -7474,99 +7477,99 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920232</v>
+        <v>22330051920236</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D16" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920233</v>
+        <v>22330051920236</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920233</v>
+        <v>22330051920237</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D18" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>22330051920233</v>
+        <v>22330051920237</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>22330051920234</v>
+        <v>22330051920238</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D20" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E20" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
         <v>67</v>
@@ -7574,19 +7577,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>22330051920234</v>
+        <v>22330051920238</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D21" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
         <v>68</v>
@@ -7594,99 +7597,99 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>22330051920234</v>
+        <v>22330051920239</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D22" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>22330051920236</v>
+        <v>22330051920239</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E23" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>22330051920236</v>
+        <v>22330051920240</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="D24" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>22330051920236</v>
+        <v>22330051920240</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="D25" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>22330051920237</v>
+        <v>22330051920422</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E26" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
         <v>67</v>
@@ -7694,19 +7697,19 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>22330051920237</v>
+        <v>22330051920422</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
         <v>68</v>
@@ -7714,99 +7717,99 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>22330051920237</v>
+        <v>22330051920241</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D28" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>22330051920238</v>
+        <v>22330051920241</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D29" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E29" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>22330051920238</v>
+        <v>22330051920242</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D30" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>22330051920238</v>
+        <v>22330051920242</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D31" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>22330051920239</v>
+        <v>22330051920357</v>
       </c>
       <c r="B32" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D32" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E32" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F32" t="s">
         <v>67</v>
@@ -7814,19 +7817,19 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>22330051920239</v>
+        <v>22330051920357</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D33" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F33" t="s">
         <v>68</v>
@@ -7834,99 +7837,99 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>22330051920239</v>
+        <v>22330051920243</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="D34" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>22330051920240</v>
+        <v>22330051920243</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D35" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E35" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>22330051920240</v>
+        <v>22330051920245</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D36" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>22330051920240</v>
+        <v>22330051920245</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D37" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>22330051920422</v>
+        <v>22330051920369</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C38" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="D38" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="E38" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F38" t="s">
         <v>67</v>
@@ -7934,19 +7937,19 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>22330051920422</v>
+        <v>22330051920369</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C39" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="D39" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="E39" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F39" t="s">
         <v>68</v>
@@ -7954,99 +7957,99 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>22330051920422</v>
+        <v>22330051920318</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C40" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="D40" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="E40" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F40" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>22330051920241</v>
+        <v>22330051920318</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C41" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="D41" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="E41" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>22330051920241</v>
+        <v>21330051420317</v>
       </c>
       <c r="B42" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C42" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="D42" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
       </c>
       <c r="F42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>22330051920241</v>
+        <v>21330051420317</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C43" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="D43" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>22330051920242</v>
+        <v>22330051920319</v>
       </c>
       <c r="B44" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C44" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D44" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="E44" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F44" t="s">
         <v>67</v>
@@ -8054,19 +8057,19 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>22330051920242</v>
+        <v>22330051920319</v>
       </c>
       <c r="B45" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C45" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D45" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F45" t="s">
         <v>68</v>
@@ -8074,99 +8077,99 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>22330051920242</v>
+        <v>22330051920246</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C46" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D46" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E46" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>22330051920357</v>
+        <v>22330051920246</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C47" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D47" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="E47" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>22330051920357</v>
+        <v>20330051920237</v>
       </c>
       <c r="B48" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C48" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="D48" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="E48" t="s">
         <v>10</v>
       </c>
       <c r="F48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>22330051920357</v>
+        <v>20330051920237</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C49" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="D49" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>22330051920243</v>
+        <v>22330051920249</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C50" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="D50" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E50" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F50" t="s">
         <v>67</v>
@@ -8174,19 +8177,19 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>22330051920243</v>
+        <v>22330051920249</v>
       </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C51" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="D51" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E51" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F51" t="s">
         <v>68</v>
@@ -8194,99 +8197,99 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>22330051920243</v>
+        <v>22330051920414</v>
       </c>
       <c r="B52" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52" t="s">
         <v>92</v>
       </c>
-      <c r="C52" t="s">
-        <v>95</v>
-      </c>
       <c r="D52" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E52" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>22330051920245</v>
+        <v>22330051920414</v>
       </c>
       <c r="B53" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C53" t="s">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="D53" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="E53" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F53" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>22330051920245</v>
+        <v>22330051920248</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C54" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D54" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="E54" t="s">
         <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>22330051920245</v>
+        <v>22330051920248</v>
       </c>
       <c r="B55" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C55" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D55" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
       </c>
       <c r="F55" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>22330051920369</v>
+        <v>22330051920250</v>
       </c>
       <c r="B56" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C56" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D56" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="E56" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F56" t="s">
         <v>67</v>
@@ -8294,19 +8297,19 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>22330051920369</v>
+        <v>22330051920250</v>
       </c>
       <c r="B57" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C57" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D57" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="E57" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F57" t="s">
         <v>68</v>
@@ -8314,99 +8317,99 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>22330051920369</v>
+        <v>22330051920251</v>
       </c>
       <c r="B58" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C58" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D58" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="E58" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F58" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>22330051920318</v>
+        <v>22330051920251</v>
       </c>
       <c r="B59" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C59" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D59" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="E59" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F59" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>22330051920318</v>
+        <v>22330051920399</v>
       </c>
       <c r="B60" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C60" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="D60" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
       </c>
       <c r="F60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>22330051920318</v>
+        <v>22330051920399</v>
       </c>
       <c r="B61" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C61" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="D61" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
       </c>
       <c r="F61" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>21330051420317</v>
+        <v>22330051920375</v>
       </c>
       <c r="B62" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C62" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D62" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="E62" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F62" t="s">
         <v>67</v>
@@ -8414,19 +8417,19 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>21330051420317</v>
+        <v>22330051920375</v>
       </c>
       <c r="B63" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C63" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D63" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="E63" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F63" t="s">
         <v>68</v>
@@ -8434,99 +8437,99 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>21330051420317</v>
+        <v>22330061460548</v>
       </c>
       <c r="B64" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="C64" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D64" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="E64" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F64" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>22330051920319</v>
+        <v>22330061460548</v>
       </c>
       <c r="B65" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C65" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D65" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="E65" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F65" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>22330051920319</v>
+        <v>22330051920400</v>
       </c>
       <c r="B66" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C66" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D66" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E66" t="s">
         <v>10</v>
       </c>
       <c r="F66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67">
-        <v>22330051920319</v>
+        <v>22330051920400</v>
       </c>
       <c r="B67" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C67" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D67" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
       </c>
       <c r="F67" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68">
-        <v>22330051920246</v>
+        <v>22330051920253</v>
       </c>
       <c r="B68" t="s">
+        <v>109</v>
+      </c>
+      <c r="C68" t="s">
         <v>98</v>
       </c>
-      <c r="C68" t="s">
-        <v>134</v>
-      </c>
       <c r="D68" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="E68" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F68" t="s">
         <v>67</v>
@@ -8534,19 +8537,19 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69">
-        <v>22330051920246</v>
+        <v>22330051920253</v>
       </c>
       <c r="B69" t="s">
+        <v>109</v>
+      </c>
+      <c r="C69" t="s">
         <v>98</v>
       </c>
-      <c r="C69" t="s">
-        <v>134</v>
-      </c>
       <c r="D69" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="E69" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F69" t="s">
         <v>68</v>
@@ -8554,39 +8557,39 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70">
-        <v>22330051920246</v>
+        <v>22330051920235</v>
       </c>
       <c r="B70" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C70" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D70" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="E70" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F70" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71">
-        <v>20330051920237</v>
+        <v>22330051920235</v>
       </c>
       <c r="B71" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C71" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="D71" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="E71" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F71" t="s">
         <v>68</v>
@@ -8594,99 +8597,99 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72">
-        <v>20330051920237</v>
+        <v>22330051920366</v>
       </c>
       <c r="B72" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C72" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="D72" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="E72" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F72" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73">
-        <v>22330051920249</v>
+        <v>22330051920366</v>
       </c>
       <c r="B73" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C73" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="D73" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="E73" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74">
-        <v>22330051920249</v>
+        <v>22330051920368</v>
       </c>
       <c r="B74" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C74" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="D74" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="E74" t="s">
         <v>10</v>
       </c>
       <c r="F74" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75">
-        <v>22330051920249</v>
+        <v>22330051920368</v>
       </c>
       <c r="B75" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C75" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="D75" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
       </c>
       <c r="F75" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76">
-        <v>22330051920414</v>
+        <v>22330051920254</v>
       </c>
       <c r="B76" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C76" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="D76" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="E76" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F76" t="s">
         <v>67</v>
@@ -8694,19 +8697,19 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77">
-        <v>22330051920414</v>
+        <v>22330051920254</v>
       </c>
       <c r="B77" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C77" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="D77" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="E77" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F77" t="s">
         <v>68</v>
@@ -8714,99 +8717,99 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78">
-        <v>22330051920414</v>
+        <v>22330051920257</v>
       </c>
       <c r="B78" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C78" t="s">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="D78" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="E78" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F78" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79">
-        <v>22330051920248</v>
+        <v>22330051920257</v>
       </c>
       <c r="B79" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C79" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D79" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="E79" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F79" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80">
-        <v>22330051920248</v>
+        <v>22330051920256</v>
       </c>
       <c r="B80" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C80" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D80" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="E80" t="s">
         <v>10</v>
       </c>
       <c r="F80" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81">
-        <v>22330051920248</v>
+        <v>22330051920256</v>
       </c>
       <c r="B81" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C81" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D81" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
       </c>
       <c r="F81" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82">
-        <v>22330051920250</v>
+        <v>22330051920401</v>
       </c>
       <c r="B82" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C82" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="D82" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="E82" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F82" t="s">
         <v>67</v>
@@ -8814,19 +8817,19 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83">
-        <v>22330051920250</v>
+        <v>22330051920401</v>
       </c>
       <c r="B83" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C83" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="D83" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="E83" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F83" t="s">
         <v>68</v>
@@ -8834,922 +8837,82 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84">
-        <v>22330051920250</v>
+        <v>22330051920259</v>
       </c>
       <c r="B84" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C84" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D84" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E84" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F84" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85">
-        <v>22330051920251</v>
+        <v>22330051920259</v>
       </c>
       <c r="B85" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C85" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="D85" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="E85" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F85" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86">
-        <v>22330051920251</v>
+        <v>22330051920176</v>
       </c>
       <c r="B86" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="C86" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="D86" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E86" t="s">
         <v>10</v>
       </c>
       <c r="F86" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87">
-        <v>22330051920251</v>
+        <v>22330051920176</v>
       </c>
       <c r="B87" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="C87" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="D87" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
       </c>
       <c r="F87" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>22330051920399</v>
-      </c>
-      <c r="B88" t="s">
-        <v>105</v>
-      </c>
-      <c r="C88" t="s">
-        <v>138</v>
-      </c>
-      <c r="D88" t="s">
-        <v>177</v>
-      </c>
-      <c r="E88" t="s">
-        <v>5</v>
-      </c>
-      <c r="F88" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>22330051920399</v>
-      </c>
-      <c r="B89" t="s">
-        <v>105</v>
-      </c>
-      <c r="C89" t="s">
-        <v>138</v>
-      </c>
-      <c r="D89" t="s">
-        <v>177</v>
-      </c>
-      <c r="E89" t="s">
-        <v>10</v>
-      </c>
-      <c r="F89" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>22330051920399</v>
-      </c>
-      <c r="B90" t="s">
-        <v>105</v>
-      </c>
-      <c r="C90" t="s">
-        <v>138</v>
-      </c>
-      <c r="D90" t="s">
-        <v>177</v>
-      </c>
-      <c r="E90" t="s">
-        <v>8</v>
-      </c>
-      <c r="F90" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>22330051920375</v>
-      </c>
-      <c r="B91" t="s">
-        <v>106</v>
-      </c>
-      <c r="C91" t="s">
-        <v>138</v>
-      </c>
-      <c r="D91" t="s">
-        <v>178</v>
-      </c>
-      <c r="E91" t="s">
-        <v>5</v>
-      </c>
-      <c r="F91" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>22330051920375</v>
-      </c>
-      <c r="B92" t="s">
-        <v>106</v>
-      </c>
-      <c r="C92" t="s">
-        <v>138</v>
-      </c>
-      <c r="D92" t="s">
-        <v>178</v>
-      </c>
-      <c r="E92" t="s">
-        <v>10</v>
-      </c>
-      <c r="F92" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>22330051920375</v>
-      </c>
-      <c r="B93" t="s">
-        <v>106</v>
-      </c>
-      <c r="C93" t="s">
-        <v>138</v>
-      </c>
-      <c r="D93" t="s">
-        <v>178</v>
-      </c>
-      <c r="E93" t="s">
-        <v>8</v>
-      </c>
-      <c r="F93" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>22330061460548</v>
-      </c>
-      <c r="B94" t="s">
-        <v>107</v>
-      </c>
-      <c r="C94" t="s">
-        <v>139</v>
-      </c>
-      <c r="D94" t="s">
-        <v>179</v>
-      </c>
-      <c r="E94" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>22330061460548</v>
-      </c>
-      <c r="B95" t="s">
-        <v>107</v>
-      </c>
-      <c r="C95" t="s">
-        <v>139</v>
-      </c>
-      <c r="D95" t="s">
-        <v>179</v>
-      </c>
-      <c r="E95" t="s">
-        <v>10</v>
-      </c>
-      <c r="F95" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>22330061460548</v>
-      </c>
-      <c r="B96" t="s">
-        <v>107</v>
-      </c>
-      <c r="C96" t="s">
-        <v>139</v>
-      </c>
-      <c r="D96" t="s">
-        <v>179</v>
-      </c>
-      <c r="E96" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>22330051920400</v>
-      </c>
-      <c r="B97" t="s">
-        <v>108</v>
-      </c>
-      <c r="C97" t="s">
-        <v>140</v>
-      </c>
-      <c r="D97" t="s">
-        <v>180</v>
-      </c>
-      <c r="E97" t="s">
-        <v>5</v>
-      </c>
-      <c r="F97" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>22330051920400</v>
-      </c>
-      <c r="B98" t="s">
-        <v>108</v>
-      </c>
-      <c r="C98" t="s">
-        <v>140</v>
-      </c>
-      <c r="D98" t="s">
-        <v>180</v>
-      </c>
-      <c r="E98" t="s">
-        <v>10</v>
-      </c>
-      <c r="F98" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>22330051920400</v>
-      </c>
-      <c r="B99" t="s">
-        <v>108</v>
-      </c>
-      <c r="C99" t="s">
-        <v>140</v>
-      </c>
-      <c r="D99" t="s">
-        <v>180</v>
-      </c>
-      <c r="E99" t="s">
-        <v>8</v>
-      </c>
-      <c r="F99" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>22330051920253</v>
-      </c>
-      <c r="B100" t="s">
-        <v>109</v>
-      </c>
-      <c r="C100" t="s">
-        <v>98</v>
-      </c>
-      <c r="D100" t="s">
-        <v>181</v>
-      </c>
-      <c r="E100" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>22330051920253</v>
-      </c>
-      <c r="B101" t="s">
-        <v>109</v>
-      </c>
-      <c r="C101" t="s">
-        <v>98</v>
-      </c>
-      <c r="D101" t="s">
-        <v>181</v>
-      </c>
-      <c r="E101" t="s">
-        <v>10</v>
-      </c>
-      <c r="F101" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>22330051920253</v>
-      </c>
-      <c r="B102" t="s">
-        <v>109</v>
-      </c>
-      <c r="C102" t="s">
-        <v>98</v>
-      </c>
-      <c r="D102" t="s">
-        <v>181</v>
-      </c>
-      <c r="E102" t="s">
-        <v>8</v>
-      </c>
-      <c r="F102" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>22330051920235</v>
-      </c>
-      <c r="B103" t="s">
-        <v>110</v>
-      </c>
-      <c r="C103" t="s">
-        <v>141</v>
-      </c>
-      <c r="D103" t="s">
-        <v>182</v>
-      </c>
-      <c r="E103" t="s">
-        <v>5</v>
-      </c>
-      <c r="F103" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>22330051920235</v>
-      </c>
-      <c r="B104" t="s">
-        <v>110</v>
-      </c>
-      <c r="C104" t="s">
-        <v>141</v>
-      </c>
-      <c r="D104" t="s">
-        <v>182</v>
-      </c>
-      <c r="E104" t="s">
-        <v>10</v>
-      </c>
-      <c r="F104" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>22330051920235</v>
-      </c>
-      <c r="B105" t="s">
-        <v>110</v>
-      </c>
-      <c r="C105" t="s">
-        <v>141</v>
-      </c>
-      <c r="D105" t="s">
-        <v>182</v>
-      </c>
-      <c r="E105" t="s">
-        <v>8</v>
-      </c>
-      <c r="F105" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>22330051920366</v>
-      </c>
-      <c r="B106" t="s">
-        <v>111</v>
-      </c>
-      <c r="C106" t="s">
-        <v>142</v>
-      </c>
-      <c r="D106" t="s">
-        <v>183</v>
-      </c>
-      <c r="E106" t="s">
-        <v>5</v>
-      </c>
-      <c r="F106" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>22330051920366</v>
-      </c>
-      <c r="B107" t="s">
-        <v>111</v>
-      </c>
-      <c r="C107" t="s">
-        <v>142</v>
-      </c>
-      <c r="D107" t="s">
-        <v>183</v>
-      </c>
-      <c r="E107" t="s">
-        <v>10</v>
-      </c>
-      <c r="F107" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>22330051920366</v>
-      </c>
-      <c r="B108" t="s">
-        <v>111</v>
-      </c>
-      <c r="C108" t="s">
-        <v>142</v>
-      </c>
-      <c r="D108" t="s">
-        <v>183</v>
-      </c>
-      <c r="E108" t="s">
-        <v>8</v>
-      </c>
-      <c r="F108" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>22330051920368</v>
-      </c>
-      <c r="B109" t="s">
-        <v>112</v>
-      </c>
-      <c r="C109" t="s">
-        <v>95</v>
-      </c>
-      <c r="D109" t="s">
-        <v>184</v>
-      </c>
-      <c r="E109" t="s">
-        <v>5</v>
-      </c>
-      <c r="F109" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>22330051920368</v>
-      </c>
-      <c r="B110" t="s">
-        <v>112</v>
-      </c>
-      <c r="C110" t="s">
-        <v>95</v>
-      </c>
-      <c r="D110" t="s">
-        <v>184</v>
-      </c>
-      <c r="E110" t="s">
-        <v>10</v>
-      </c>
-      <c r="F110" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>22330051920368</v>
-      </c>
-      <c r="B111" t="s">
-        <v>112</v>
-      </c>
-      <c r="C111" t="s">
-        <v>95</v>
-      </c>
-      <c r="D111" t="s">
-        <v>184</v>
-      </c>
-      <c r="E111" t="s">
-        <v>8</v>
-      </c>
-      <c r="F111" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>22330051920254</v>
-      </c>
-      <c r="B112" t="s">
-        <v>113</v>
-      </c>
-      <c r="C112" t="s">
-        <v>112</v>
-      </c>
-      <c r="D112" t="s">
-        <v>185</v>
-      </c>
-      <c r="E112" t="s">
-        <v>5</v>
-      </c>
-      <c r="F112" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>22330051920254</v>
-      </c>
-      <c r="B113" t="s">
-        <v>113</v>
-      </c>
-      <c r="C113" t="s">
-        <v>112</v>
-      </c>
-      <c r="D113" t="s">
-        <v>185</v>
-      </c>
-      <c r="E113" t="s">
-        <v>10</v>
-      </c>
-      <c r="F113" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>22330051920254</v>
-      </c>
-      <c r="B114" t="s">
-        <v>113</v>
-      </c>
-      <c r="C114" t="s">
-        <v>112</v>
-      </c>
-      <c r="D114" t="s">
-        <v>185</v>
-      </c>
-      <c r="E114" t="s">
-        <v>8</v>
-      </c>
-      <c r="F114" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>22330051920257</v>
-      </c>
-      <c r="B115" t="s">
-        <v>114</v>
-      </c>
-      <c r="C115" t="s">
-        <v>143</v>
-      </c>
-      <c r="D115" t="s">
-        <v>186</v>
-      </c>
-      <c r="E115" t="s">
-        <v>5</v>
-      </c>
-      <c r="F115" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>22330051920257</v>
-      </c>
-      <c r="B116" t="s">
-        <v>114</v>
-      </c>
-      <c r="C116" t="s">
-        <v>143</v>
-      </c>
-      <c r="D116" t="s">
-        <v>186</v>
-      </c>
-      <c r="E116" t="s">
-        <v>10</v>
-      </c>
-      <c r="F116" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>22330051920257</v>
-      </c>
-      <c r="B117" t="s">
-        <v>114</v>
-      </c>
-      <c r="C117" t="s">
-        <v>143</v>
-      </c>
-      <c r="D117" t="s">
-        <v>186</v>
-      </c>
-      <c r="E117" t="s">
-        <v>8</v>
-      </c>
-      <c r="F117" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>22330051920256</v>
-      </c>
-      <c r="B118" t="s">
-        <v>115</v>
-      </c>
-      <c r="C118" t="s">
-        <v>144</v>
-      </c>
-      <c r="D118" t="s">
-        <v>187</v>
-      </c>
-      <c r="E118" t="s">
-        <v>5</v>
-      </c>
-      <c r="F118" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>22330051920256</v>
-      </c>
-      <c r="B119" t="s">
-        <v>115</v>
-      </c>
-      <c r="C119" t="s">
-        <v>144</v>
-      </c>
-      <c r="D119" t="s">
-        <v>187</v>
-      </c>
-      <c r="E119" t="s">
-        <v>10</v>
-      </c>
-      <c r="F119" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>22330051920256</v>
-      </c>
-      <c r="B120" t="s">
-        <v>115</v>
-      </c>
-      <c r="C120" t="s">
-        <v>144</v>
-      </c>
-      <c r="D120" t="s">
-        <v>187</v>
-      </c>
-      <c r="E120" t="s">
-        <v>8</v>
-      </c>
-      <c r="F120" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>22330051920401</v>
-      </c>
-      <c r="B121" t="s">
-        <v>116</v>
-      </c>
-      <c r="C121" t="s">
-        <v>145</v>
-      </c>
-      <c r="D121" t="s">
-        <v>188</v>
-      </c>
-      <c r="E121" t="s">
-        <v>5</v>
-      </c>
-      <c r="F121" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122">
-        <v>22330051920401</v>
-      </c>
-      <c r="B122" t="s">
-        <v>116</v>
-      </c>
-      <c r="C122" t="s">
-        <v>145</v>
-      </c>
-      <c r="D122" t="s">
-        <v>188</v>
-      </c>
-      <c r="E122" t="s">
-        <v>10</v>
-      </c>
-      <c r="F122" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123">
-        <v>22330051920401</v>
-      </c>
-      <c r="B123" t="s">
-        <v>116</v>
-      </c>
-      <c r="C123" t="s">
-        <v>145</v>
-      </c>
-      <c r="D123" t="s">
-        <v>188</v>
-      </c>
-      <c r="E123" t="s">
-        <v>8</v>
-      </c>
-      <c r="F123" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124">
-        <v>22330051920259</v>
-      </c>
-      <c r="B124" t="s">
-        <v>117</v>
-      </c>
-      <c r="C124" t="s">
-        <v>146</v>
-      </c>
-      <c r="D124" t="s">
-        <v>189</v>
-      </c>
-      <c r="E124" t="s">
-        <v>5</v>
-      </c>
-      <c r="F124" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125">
-        <v>22330051920259</v>
-      </c>
-      <c r="B125" t="s">
-        <v>117</v>
-      </c>
-      <c r="C125" t="s">
-        <v>146</v>
-      </c>
-      <c r="D125" t="s">
-        <v>189</v>
-      </c>
-      <c r="E125" t="s">
-        <v>10</v>
-      </c>
-      <c r="F125" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126">
-        <v>22330051920259</v>
-      </c>
-      <c r="B126" t="s">
-        <v>117</v>
-      </c>
-      <c r="C126" t="s">
-        <v>146</v>
-      </c>
-      <c r="D126" t="s">
-        <v>189</v>
-      </c>
-      <c r="E126" t="s">
-        <v>8</v>
-      </c>
-      <c r="F126" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
-        <v>22330051920176</v>
-      </c>
-      <c r="B127" t="s">
-        <v>118</v>
-      </c>
-      <c r="C127" t="s">
-        <v>147</v>
-      </c>
-      <c r="D127" t="s">
-        <v>190</v>
-      </c>
-      <c r="E127" t="s">
-        <v>5</v>
-      </c>
-      <c r="F127" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128">
-        <v>22330051920176</v>
-      </c>
-      <c r="B128" t="s">
-        <v>118</v>
-      </c>
-      <c r="C128" t="s">
-        <v>147</v>
-      </c>
-      <c r="D128" t="s">
-        <v>190</v>
-      </c>
-      <c r="E128" t="s">
-        <v>10</v>
-      </c>
-      <c r="F128" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129">
-        <v>22330051920176</v>
-      </c>
-      <c r="B129" t="s">
-        <v>118</v>
-      </c>
-      <c r="C129" t="s">
-        <v>147</v>
-      </c>
-      <c r="D129" t="s">
-        <v>190</v>
-      </c>
-      <c r="E129" t="s">
-        <v>8</v>
-      </c>
-      <c r="F129" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -9797,7 +8960,7 @@
         <v>148</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -9814,7 +8977,7 @@
         <v>149</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -9831,7 +8994,7 @@
         <v>150</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -9848,7 +9011,7 @@
         <v>151</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -9865,7 +9028,7 @@
         <v>152</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -9882,7 +9045,7 @@
         <v>153</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -9899,7 +9062,7 @@
         <v>154</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -9916,7 +9079,7 @@
         <v>155</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -9933,7 +9096,7 @@
         <v>156</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -9950,7 +9113,7 @@
         <v>157</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -9967,7 +9130,7 @@
         <v>158</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -9984,7 +9147,7 @@
         <v>159</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -10001,7 +9164,7 @@
         <v>160</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -10018,7 +9181,7 @@
         <v>161</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -10035,7 +9198,7 @@
         <v>162</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -10052,7 +9215,7 @@
         <v>163</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -10069,7 +9232,7 @@
         <v>164</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -10086,7 +9249,7 @@
         <v>165</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -10103,7 +9266,7 @@
         <v>166</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -10120,7 +9283,7 @@
         <v>167</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -10137,7 +9300,7 @@
         <v>168</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -10154,7 +9317,7 @@
         <v>169</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -10171,344 +9334,344 @@
         <v>170</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920249</v>
+        <v>20330051920237</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920414</v>
+        <v>22330051920249</v>
       </c>
       <c r="B26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920248</v>
+        <v>22330051920414</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C27" t="s">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920250</v>
+        <v>22330051920248</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D28" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920251</v>
+        <v>22330051920250</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D29" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920399</v>
+        <v>22330051920251</v>
       </c>
       <c r="B30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C30" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920375</v>
+        <v>22330051920399</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C31" t="s">
         <v>138</v>
       </c>
       <c r="D31" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330061460548</v>
+        <v>22330051920375</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C32" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D32" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>22330051920400</v>
+        <v>22330061460548</v>
       </c>
       <c r="B33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D33" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>22330051920253</v>
+        <v>22330051920400</v>
       </c>
       <c r="B34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="D34" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>22330051920235</v>
+        <v>22330051920253</v>
       </c>
       <c r="B35" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>22330051920366</v>
+        <v>22330051920235</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C36" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D36" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>22330051920368</v>
+        <v>22330051920366</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C37" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="D37" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>22330051920254</v>
+        <v>22330051920368</v>
       </c>
       <c r="B38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C38" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="D38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>22330051920257</v>
+        <v>22330051920254</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C39" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="D39" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E39">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>22330051920256</v>
+        <v>22330051920257</v>
       </c>
       <c r="B40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C40" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>22330051920401</v>
+        <v>22330051920256</v>
       </c>
       <c r="B41" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C41" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D41" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E41">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>22330051920259</v>
+        <v>22330051920401</v>
       </c>
       <c r="B42" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C42" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D42" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E42">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>22330051920176</v>
+        <v>22330051920259</v>
       </c>
       <c r="B43" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C43" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D43" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E43">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>20330051920237</v>
+        <v>22330051920176</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="C44" t="s">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="D44" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="E44">
         <v>2</v>
@@ -10521,7 +9684,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -10553,22 +9716,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920237</v>
+        <v>22330051920231</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="D2" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -10576,24 +9739,806 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920237</v>
+        <v>22330051920231</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="D3" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920260</v>
+      </c>
+      <c r="B4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
         <v>68</v>
       </c>
-      <c r="G3">
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920260</v>
+      </c>
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920234</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920234</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920238</v>
+      </c>
+      <c r="B8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920238</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" t="s">
+        <v>157</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920241</v>
+      </c>
+      <c r="B10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" t="s">
+        <v>161</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920241</v>
+      </c>
+      <c r="B11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920243</v>
+      </c>
+      <c r="B12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920243</v>
+      </c>
+      <c r="B13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" t="s">
+        <v>164</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920245</v>
+      </c>
+      <c r="B14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D14" t="s">
+        <v>165</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920245</v>
+      </c>
+      <c r="B15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" t="s">
+        <v>165</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920318</v>
+      </c>
+      <c r="B16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" t="s">
+        <v>131</v>
+      </c>
+      <c r="D16" t="s">
+        <v>167</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920318</v>
+      </c>
+      <c r="B17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D17" t="s">
+        <v>167</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920319</v>
+      </c>
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>133</v>
+      </c>
+      <c r="D18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920319</v>
+      </c>
+      <c r="B19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" t="s">
+        <v>133</v>
+      </c>
+      <c r="D19" t="s">
+        <v>169</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>67</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920237</v>
+      </c>
+      <c r="B20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" t="s">
+        <v>171</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20330051920237</v>
+      </c>
+      <c r="B21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" t="s">
+        <v>171</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>67</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>22330051920414</v>
+      </c>
+      <c r="B22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" t="s">
+        <v>92</v>
+      </c>
+      <c r="D22" t="s">
+        <v>173</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>22330051920414</v>
+      </c>
+      <c r="B23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" t="s">
+        <v>173</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>67</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>22330051920248</v>
+      </c>
+      <c r="B24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" t="s">
+        <v>135</v>
+      </c>
+      <c r="D24" t="s">
+        <v>174</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>22330051920248</v>
+      </c>
+      <c r="B25" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" t="s">
+        <v>135</v>
+      </c>
+      <c r="D25" t="s">
+        <v>174</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>67</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>22330051920250</v>
+      </c>
+      <c r="B26" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" t="s">
+        <v>175</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>22330051920250</v>
+      </c>
+      <c r="B27" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D27" t="s">
+        <v>175</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>22330051920399</v>
+      </c>
+      <c r="B28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" t="s">
+        <v>177</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>22330051920399</v>
+      </c>
+      <c r="B29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" t="s">
+        <v>177</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>67</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>22330051920235</v>
+      </c>
+      <c r="B30" t="s">
+        <v>110</v>
+      </c>
+      <c r="C30" t="s">
+        <v>141</v>
+      </c>
+      <c r="D30" t="s">
+        <v>182</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>22330051920235</v>
+      </c>
+      <c r="B31" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" t="s">
+        <v>141</v>
+      </c>
+      <c r="D31" t="s">
+        <v>182</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s">
+        <v>67</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>22330051920254</v>
+      </c>
+      <c r="B32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" t="s">
+        <v>185</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>68</v>
+      </c>
+      <c r="G32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>22330051920254</v>
+      </c>
+      <c r="B33" t="s">
+        <v>113</v>
+      </c>
+      <c r="C33" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33" t="s">
+        <v>185</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>67</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>22330051920257</v>
+      </c>
+      <c r="B34" t="s">
+        <v>114</v>
+      </c>
+      <c r="C34" t="s">
+        <v>143</v>
+      </c>
+      <c r="D34" t="s">
+        <v>186</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>68</v>
+      </c>
+      <c r="G34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>22330051920257</v>
+      </c>
+      <c r="B35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" t="s">
+        <v>143</v>
+      </c>
+      <c r="D35" t="s">
+        <v>186</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" t="s">
+        <v>67</v>
+      </c>
+      <c r="G35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>22330051920256</v>
+      </c>
+      <c r="B36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" t="s">
+        <v>144</v>
+      </c>
+      <c r="D36" t="s">
+        <v>187</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>68</v>
+      </c>
+      <c r="G36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>22330051920256</v>
+      </c>
+      <c r="B37" t="s">
+        <v>115</v>
+      </c>
+      <c r="C37" t="s">
+        <v>144</v>
+      </c>
+      <c r="D37" t="s">
+        <v>187</v>
+      </c>
+      <c r="E37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s">
+        <v>67</v>
+      </c>
+      <c r="G37">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ALCV - Estadisticos 20222.xlsx
+++ b/grupos/2ALCV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="191">
   <si>
     <t>Materia</t>
   </si>
@@ -222,16 +222,16 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
+    <t>Desc Desc Desc</t>
+  </si>
+  <si>
+    <t>Rivera Serra Alma Lilian</t>
+  </si>
+  <si>
     <t>Flores Ovalle Victor</t>
-  </si>
-  <si>
-    <t>Rivera Serra Alma Lilian</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Desc Desc Desc</t>
   </si>
   <si>
     <t>Medina Tolentino Francisco</t>
@@ -1086,13 +1086,13 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F4">
         <v>5</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -1140,13 +1140,13 @@
         <v>5</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1163,13 +1163,13 @@
         <v>10</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F5">
         <v>7</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -1217,13 +1217,13 @@
         <v>10</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1240,13 +1240,13 @@
         <v>7</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>5</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>-1</v>
@@ -1294,13 +1294,13 @@
         <v>7</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>5</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1317,13 +1317,13 @@
         <v>9</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F7">
         <v>8</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1371,13 +1371,13 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1394,13 +1394,13 @@
         <v>5</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F8">
         <v>5</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -1448,13 +1448,13 @@
         <v>5</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X8">
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1471,13 +1471,13 @@
         <v>6</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F9">
         <v>5</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H9">
         <v>-1</v>
@@ -1525,13 +1525,13 @@
         <v>6</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1548,13 +1548,13 @@
         <v>10</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F10">
         <v>10</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H10">
         <v>-1</v>
@@ -1602,13 +1602,13 @@
         <v>10</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1625,13 +1625,13 @@
         <v>8</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <v>8</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -1679,13 +1679,13 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1702,13 +1702,13 @@
         <v>5</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F12">
         <v>5</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -1756,13 +1756,13 @@
         <v>5</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X12">
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1779,13 +1779,13 @@
         <v>5</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F13">
         <v>5</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -1833,13 +1833,13 @@
         <v>5</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1856,13 +1856,13 @@
         <v>9</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F14">
         <v>8</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -1910,13 +1910,13 @@
         <v>9</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1933,13 +1933,13 @@
         <v>5</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F15">
         <v>5</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -1987,13 +1987,13 @@
         <v>5</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X15">
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2010,13 +2010,13 @@
         <v>6</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F16">
         <v>5</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -2064,13 +2064,13 @@
         <v>6</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X16">
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2087,13 +2087,13 @@
         <v>6</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F17">
         <v>5</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -2141,13 +2141,13 @@
         <v>6</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2164,13 +2164,13 @@
         <v>9</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F18">
         <v>8</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -2218,13 +2218,13 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2241,13 +2241,13 @@
         <v>7</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F19">
         <v>6</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H19">
         <v>-1</v>
@@ -2295,13 +2295,13 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X19">
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2318,13 +2318,13 @@
         <v>6</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F20">
         <v>7</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2372,13 +2372,13 @@
         <v>6</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X20">
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2395,13 +2395,13 @@
         <v>7</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F21">
         <v>6</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H21">
         <v>-1</v>
@@ -2449,13 +2449,13 @@
         <v>7</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2472,13 +2472,13 @@
         <v>9</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F22">
         <v>10</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -2526,13 +2526,13 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2549,13 +2549,13 @@
         <v>6</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F23">
         <v>5</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H23">
         <v>-1</v>
@@ -2603,13 +2603,13 @@
         <v>6</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2626,13 +2626,13 @@
         <v>6</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F24">
         <v>6</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H24">
         <v>-1</v>
@@ -2680,13 +2680,13 @@
         <v>6</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2703,13 +2703,13 @@
         <v>7</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F25">
         <v>7</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H25">
         <v>-1</v>
@@ -2757,13 +2757,13 @@
         <v>7</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2777,13 +2777,13 @@
         <v>6</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F26">
         <v>10</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2822,13 +2822,13 @@
         <v>6</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2845,13 +2845,13 @@
         <v>7</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F27">
         <v>5</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H27">
         <v>-1</v>
@@ -2899,13 +2899,13 @@
         <v>7</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>5</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2922,13 +2922,13 @@
         <v>6</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F28">
         <v>10</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H28">
         <v>-1</v>
@@ -2976,13 +2976,13 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2999,13 +2999,13 @@
         <v>8</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F29">
         <v>6</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H29">
         <v>-1</v>
@@ -3053,13 +3053,13 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>6</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3067,10 +3067,10 @@
         <v>38</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -3085,10 +3085,10 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3105,13 +3105,13 @@
         <v>10</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F31">
         <v>10</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H31">
         <v>-1</v>
@@ -3159,13 +3159,13 @@
         <v>10</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3182,13 +3182,13 @@
         <v>7</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F32">
         <v>9</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -3236,13 +3236,13 @@
         <v>7</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X32">
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3259,13 +3259,13 @@
         <v>5</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F33">
         <v>8</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H33">
         <v>-1</v>
@@ -3313,13 +3313,13 @@
         <v>5</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X33">
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3336,13 +3336,13 @@
         <v>6</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F34">
         <v>6</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H34">
         <v>-1</v>
@@ -3390,13 +3390,13 @@
         <v>6</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>6</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3413,13 +3413,13 @@
         <v>8</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F35">
         <v>5</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H35">
         <v>-1</v>
@@ -3467,13 +3467,13 @@
         <v>8</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>5</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3490,13 +3490,13 @@
         <v>6</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F36">
         <v>5</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H36">
         <v>-1</v>
@@ -3544,13 +3544,13 @@
         <v>6</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3567,13 +3567,13 @@
         <v>10</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F37">
         <v>6</v>
       </c>
       <c r="G37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H37">
         <v>-1</v>
@@ -3621,13 +3621,13 @@
         <v>10</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3644,13 +3644,13 @@
         <v>6</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F38">
         <v>5</v>
       </c>
       <c r="G38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H38">
         <v>-1</v>
@@ -3698,13 +3698,13 @@
         <v>6</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X38">
         <v>5</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3721,13 +3721,13 @@
         <v>5</v>
       </c>
       <c r="E39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F39">
         <v>5</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H39">
         <v>-1</v>
@@ -3775,13 +3775,13 @@
         <v>5</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X39">
         <v>5</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3798,13 +3798,13 @@
         <v>10</v>
       </c>
       <c r="E40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F40">
         <v>5</v>
       </c>
       <c r="G40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H40">
         <v>-1</v>
@@ -3852,13 +3852,13 @@
         <v>10</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X40">
         <v>5</v>
       </c>
       <c r="Y40">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3875,13 +3875,13 @@
         <v>8</v>
       </c>
       <c r="E41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F41">
         <v>9</v>
       </c>
       <c r="G41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H41">
         <v>-1</v>
@@ -3929,13 +3929,13 @@
         <v>8</v>
       </c>
       <c r="W41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X41">
         <v>9</v>
       </c>
       <c r="Y41">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3952,13 +3952,13 @@
         <v>6</v>
       </c>
       <c r="E42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F42">
         <v>6</v>
       </c>
       <c r="G42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H42">
         <v>-1</v>
@@ -4006,13 +4006,13 @@
         <v>6</v>
       </c>
       <c r="W42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X42">
         <v>6</v>
       </c>
       <c r="Y42">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -4029,13 +4029,13 @@
         <v>6</v>
       </c>
       <c r="E43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F43">
         <v>6</v>
       </c>
       <c r="G43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H43">
         <v>-1</v>
@@ -4083,13 +4083,13 @@
         <v>6</v>
       </c>
       <c r="W43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X43">
         <v>6</v>
       </c>
       <c r="Y43">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4106,13 +4106,13 @@
         <v>9</v>
       </c>
       <c r="E44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F44">
         <v>5</v>
       </c>
       <c r="G44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H44">
         <v>-1</v>
@@ -4160,13 +4160,13 @@
         <v>9</v>
       </c>
       <c r="W44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X44">
         <v>5</v>
       </c>
       <c r="Y44">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -4183,13 +4183,13 @@
         <v>5</v>
       </c>
       <c r="E45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F45">
         <v>5</v>
       </c>
       <c r="G45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H45">
         <v>-1</v>
@@ -4237,13 +4237,13 @@
         <v>5</v>
       </c>
       <c r="W45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X45">
         <v>5</v>
       </c>
       <c r="Y45">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -4260,13 +4260,13 @@
         <v>6</v>
       </c>
       <c r="E46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F46">
         <v>5</v>
       </c>
       <c r="G46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H46">
         <v>-1</v>
@@ -4314,13 +4314,13 @@
         <v>6</v>
       </c>
       <c r="W46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X46">
         <v>5</v>
       </c>
       <c r="Y46">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4447,13 +4447,13 @@
         <v>75</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F4">
         <v>90</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -4506,13 +4506,13 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F5">
         <v>100</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -4565,13 +4565,13 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F6">
         <v>100</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -4624,13 +4624,13 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F7">
         <v>95</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -4683,13 +4683,13 @@
         <v>90</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F8">
         <v>85</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -4742,13 +4742,13 @@
         <v>75</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="F9">
         <v>70</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -4801,13 +4801,13 @@
         <v>85</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="F10">
         <v>100</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -4860,13 +4860,13 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F11">
         <v>95</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -4919,13 +4919,13 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F12">
         <v>80</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -4978,13 +4978,13 @@
         <v>60</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F13">
         <v>90</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -5037,13 +5037,13 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F14">
         <v>100</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -5096,13 +5096,13 @@
         <v>50</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="F15">
         <v>80</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -5155,13 +5155,13 @@
         <v>90</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F16">
         <v>95</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -5214,13 +5214,13 @@
         <v>85</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F17">
         <v>90</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -5273,13 +5273,13 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F18">
         <v>100</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -5332,13 +5332,13 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F19">
         <v>100</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -5391,13 +5391,13 @@
         <v>95</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F20">
         <v>100</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -5450,13 +5450,13 @@
         <v>100</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F21">
         <v>100</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -5509,13 +5509,13 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F22">
         <v>100</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -5568,13 +5568,13 @@
         <v>100</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F23">
         <v>90</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -5627,13 +5627,13 @@
         <v>85</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F24">
         <v>90</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -5686,13 +5686,13 @@
         <v>100</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F25">
         <v>100</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -5742,13 +5742,13 @@
         <v>100</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F26">
         <v>100</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -5795,13 +5795,13 @@
         <v>80</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="F27">
         <v>90</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -5854,13 +5854,13 @@
         <v>100</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F28">
         <v>100</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -5913,13 +5913,13 @@
         <v>90</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F29">
         <v>100</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -5963,10 +5963,10 @@
         <v>38</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -5995,13 +5995,13 @@
         <v>100</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F31">
         <v>90</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -6054,13 +6054,13 @@
         <v>100</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F32">
         <v>100</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -6113,13 +6113,13 @@
         <v>70</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F33">
         <v>100</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -6172,13 +6172,13 @@
         <v>85</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F34">
         <v>100</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -6231,13 +6231,13 @@
         <v>100</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F35">
         <v>100</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -6290,13 +6290,13 @@
         <v>85</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F36">
         <v>100</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -6349,13 +6349,13 @@
         <v>100</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F37">
         <v>100</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -6408,13 +6408,13 @@
         <v>100</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F38">
         <v>100</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -6467,13 +6467,13 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F39">
         <v>100</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -6526,13 +6526,13 @@
         <v>100</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F40">
         <v>80</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -6585,13 +6585,13 @@
         <v>100</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F41">
         <v>90</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -6644,13 +6644,13 @@
         <v>100</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F42">
         <v>100</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -6703,13 +6703,13 @@
         <v>80</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F43">
         <v>90</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -6762,13 +6762,13 @@
         <v>100</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F44">
         <v>100</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -6821,13 +6821,13 @@
         <v>75</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F45">
         <v>100</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -6880,13 +6880,13 @@
         <v>80</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F46">
         <v>100</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -6977,86 +6977,92 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>54.76</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>45.24</v>
+      </c>
+      <c r="H2">
+        <v>6.5</v>
       </c>
       <c r="I2">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
       </c>
       <c r="C3">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>59.52</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>40.48</v>
+      </c>
+      <c r="H3">
+        <v>6.3</v>
       </c>
       <c r="I3">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
       </c>
       <c r="C4">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>54.76</v>
+        <v>69.77</v>
       </c>
       <c r="G4">
-        <v>45.24</v>
+        <v>30.23</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7067,28 +7073,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
       </c>
       <c r="C5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>59.52</v>
+        <v>74.42</v>
       </c>
       <c r="G5">
-        <v>40.48</v>
+        <v>25.58</v>
       </c>
       <c r="H5">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7168,7 +7174,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7193,1726 +7199,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330061460173</v>
-      </c>
-      <c r="B2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330061460173</v>
-      </c>
-      <c r="B3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920231</v>
-      </c>
-      <c r="B4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D4" t="s">
-        <v>149</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920231</v>
-      </c>
-      <c r="B5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D5" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920230</v>
-      </c>
-      <c r="B6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920230</v>
-      </c>
-      <c r="B7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D7" t="s">
-        <v>150</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920260</v>
-      </c>
-      <c r="B8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" t="s">
-        <v>151</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920260</v>
-      </c>
-      <c r="B9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920232</v>
-      </c>
-      <c r="B10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" t="s">
-        <v>121</v>
-      </c>
-      <c r="D10" t="s">
-        <v>152</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920232</v>
-      </c>
-      <c r="B11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D11" t="s">
-        <v>152</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920233</v>
-      </c>
-      <c r="B12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" t="s">
-        <v>122</v>
-      </c>
-      <c r="D12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920233</v>
-      </c>
-      <c r="B13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D13" t="s">
-        <v>153</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920234</v>
-      </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s">
-        <v>123</v>
-      </c>
-      <c r="D14" t="s">
-        <v>154</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920234</v>
-      </c>
-      <c r="B15" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" t="s">
-        <v>123</v>
-      </c>
-      <c r="D15" t="s">
-        <v>154</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920236</v>
-      </c>
-      <c r="B16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" t="s">
-        <v>124</v>
-      </c>
-      <c r="D16" t="s">
-        <v>155</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920236</v>
-      </c>
-      <c r="B17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" t="s">
-        <v>124</v>
-      </c>
-      <c r="D17" t="s">
-        <v>155</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920237</v>
-      </c>
-      <c r="B18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" t="s">
-        <v>125</v>
-      </c>
-      <c r="D18" t="s">
-        <v>156</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920237</v>
-      </c>
-      <c r="B19" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" t="s">
-        <v>125</v>
-      </c>
-      <c r="D19" t="s">
-        <v>156</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920238</v>
-      </c>
-      <c r="B20" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" t="s">
-        <v>126</v>
-      </c>
-      <c r="D20" t="s">
-        <v>157</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920238</v>
-      </c>
-      <c r="B21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" t="s">
-        <v>126</v>
-      </c>
-      <c r="D21" t="s">
-        <v>157</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920239</v>
-      </c>
-      <c r="B22" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" t="s">
-        <v>125</v>
-      </c>
-      <c r="D22" t="s">
-        <v>158</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920239</v>
-      </c>
-      <c r="B23" t="s">
-        <v>87</v>
-      </c>
-      <c r="C23" t="s">
-        <v>125</v>
-      </c>
-      <c r="D23" t="s">
-        <v>158</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920240</v>
-      </c>
-      <c r="B24" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" t="s">
-        <v>159</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920240</v>
-      </c>
-      <c r="B25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" t="s">
-        <v>100</v>
-      </c>
-      <c r="D25" t="s">
-        <v>159</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>22330051920422</v>
-      </c>
-      <c r="B26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" t="s">
-        <v>160</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>22330051920422</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" t="s">
-        <v>160</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>22330051920241</v>
-      </c>
-      <c r="B28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" t="s">
-        <v>114</v>
-      </c>
-      <c r="D28" t="s">
-        <v>161</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>22330051920241</v>
-      </c>
-      <c r="B29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" t="s">
-        <v>114</v>
-      </c>
-      <c r="D29" t="s">
-        <v>161</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>22330051920242</v>
-      </c>
-      <c r="B30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>127</v>
-      </c>
-      <c r="D30" t="s">
-        <v>162</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>22330051920242</v>
-      </c>
-      <c r="B31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" t="s">
-        <v>127</v>
-      </c>
-      <c r="D31" t="s">
-        <v>162</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>22330051920357</v>
-      </c>
-      <c r="B32" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" t="s">
-        <v>128</v>
-      </c>
-      <c r="D32" t="s">
-        <v>163</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>22330051920357</v>
-      </c>
-      <c r="B33" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" t="s">
-        <v>128</v>
-      </c>
-      <c r="D33" t="s">
-        <v>163</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>22330051920243</v>
-      </c>
-      <c r="B34" t="s">
-        <v>92</v>
-      </c>
-      <c r="C34" t="s">
-        <v>95</v>
-      </c>
-      <c r="D34" t="s">
-        <v>164</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>22330051920243</v>
-      </c>
-      <c r="B35" t="s">
-        <v>92</v>
-      </c>
-      <c r="C35" t="s">
-        <v>95</v>
-      </c>
-      <c r="D35" t="s">
-        <v>164</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>22330051920245</v>
-      </c>
-      <c r="B36" t="s">
-        <v>93</v>
-      </c>
-      <c r="C36" t="s">
-        <v>129</v>
-      </c>
-      <c r="D36" t="s">
-        <v>165</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>22330051920245</v>
-      </c>
-      <c r="B37" t="s">
-        <v>93</v>
-      </c>
-      <c r="C37" t="s">
-        <v>129</v>
-      </c>
-      <c r="D37" t="s">
-        <v>165</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>22330051920369</v>
-      </c>
-      <c r="B38" t="s">
-        <v>94</v>
-      </c>
-      <c r="C38" t="s">
-        <v>130</v>
-      </c>
-      <c r="D38" t="s">
-        <v>166</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>22330051920369</v>
-      </c>
-      <c r="B39" t="s">
-        <v>94</v>
-      </c>
-      <c r="C39" t="s">
-        <v>130</v>
-      </c>
-      <c r="D39" t="s">
-        <v>166</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>22330051920318</v>
-      </c>
-      <c r="B40" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40" t="s">
-        <v>131</v>
-      </c>
-      <c r="D40" t="s">
-        <v>167</v>
-      </c>
-      <c r="E40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>22330051920318</v>
-      </c>
-      <c r="B41" t="s">
-        <v>95</v>
-      </c>
-      <c r="C41" t="s">
-        <v>131</v>
-      </c>
-      <c r="D41" t="s">
-        <v>167</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051420317</v>
-      </c>
-      <c r="B42" t="s">
-        <v>96</v>
-      </c>
-      <c r="C42" t="s">
-        <v>132</v>
-      </c>
-      <c r="D42" t="s">
-        <v>168</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051420317</v>
-      </c>
-      <c r="B43" t="s">
-        <v>96</v>
-      </c>
-      <c r="C43" t="s">
-        <v>132</v>
-      </c>
-      <c r="D43" t="s">
-        <v>168</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>22330051920319</v>
-      </c>
-      <c r="B44" t="s">
-        <v>97</v>
-      </c>
-      <c r="C44" t="s">
-        <v>133</v>
-      </c>
-      <c r="D44" t="s">
-        <v>169</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>22330051920319</v>
-      </c>
-      <c r="B45" t="s">
-        <v>97</v>
-      </c>
-      <c r="C45" t="s">
-        <v>133</v>
-      </c>
-      <c r="D45" t="s">
-        <v>169</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>22330051920246</v>
-      </c>
-      <c r="B46" t="s">
-        <v>98</v>
-      </c>
-      <c r="C46" t="s">
-        <v>134</v>
-      </c>
-      <c r="D46" t="s">
-        <v>170</v>
-      </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>22330051920246</v>
-      </c>
-      <c r="B47" t="s">
-        <v>98</v>
-      </c>
-      <c r="C47" t="s">
-        <v>134</v>
-      </c>
-      <c r="D47" t="s">
-        <v>170</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>20330051920237</v>
-      </c>
-      <c r="B48" t="s">
-        <v>99</v>
-      </c>
-      <c r="C48" t="s">
-        <v>80</v>
-      </c>
-      <c r="D48" t="s">
-        <v>171</v>
-      </c>
-      <c r="E48" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920237</v>
-      </c>
-      <c r="B49" t="s">
-        <v>99</v>
-      </c>
-      <c r="C49" t="s">
-        <v>80</v>
-      </c>
-      <c r="D49" t="s">
-        <v>171</v>
-      </c>
-      <c r="E49" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>22330051920249</v>
-      </c>
-      <c r="B50" t="s">
-        <v>100</v>
-      </c>
-      <c r="C50" t="s">
-        <v>126</v>
-      </c>
-      <c r="D50" t="s">
-        <v>172</v>
-      </c>
-      <c r="E50" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>22330051920249</v>
-      </c>
-      <c r="B51" t="s">
-        <v>100</v>
-      </c>
-      <c r="C51" t="s">
-        <v>126</v>
-      </c>
-      <c r="D51" t="s">
-        <v>172</v>
-      </c>
-      <c r="E51" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>22330051920414</v>
-      </c>
-      <c r="B52" t="s">
-        <v>101</v>
-      </c>
-      <c r="C52" t="s">
-        <v>92</v>
-      </c>
-      <c r="D52" t="s">
-        <v>173</v>
-      </c>
-      <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>22330051920414</v>
-      </c>
-      <c r="B53" t="s">
-        <v>101</v>
-      </c>
-      <c r="C53" t="s">
-        <v>92</v>
-      </c>
-      <c r="D53" t="s">
-        <v>173</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>22330051920248</v>
-      </c>
-      <c r="B54" t="s">
-        <v>102</v>
-      </c>
-      <c r="C54" t="s">
-        <v>135</v>
-      </c>
-      <c r="D54" t="s">
-        <v>174</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>22330051920248</v>
-      </c>
-      <c r="B55" t="s">
-        <v>102</v>
-      </c>
-      <c r="C55" t="s">
-        <v>135</v>
-      </c>
-      <c r="D55" t="s">
-        <v>174</v>
-      </c>
-      <c r="E55" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>22330051920250</v>
-      </c>
-      <c r="B56" t="s">
-        <v>103</v>
-      </c>
-      <c r="C56" t="s">
-        <v>136</v>
-      </c>
-      <c r="D56" t="s">
-        <v>175</v>
-      </c>
-      <c r="E56" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>22330051920250</v>
-      </c>
-      <c r="B57" t="s">
-        <v>103</v>
-      </c>
-      <c r="C57" t="s">
-        <v>136</v>
-      </c>
-      <c r="D57" t="s">
-        <v>175</v>
-      </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>22330051920251</v>
-      </c>
-      <c r="B58" t="s">
-        <v>104</v>
-      </c>
-      <c r="C58" t="s">
-        <v>137</v>
-      </c>
-      <c r="D58" t="s">
-        <v>176</v>
-      </c>
-      <c r="E58" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>22330051920251</v>
-      </c>
-      <c r="B59" t="s">
-        <v>104</v>
-      </c>
-      <c r="C59" t="s">
-        <v>137</v>
-      </c>
-      <c r="D59" t="s">
-        <v>176</v>
-      </c>
-      <c r="E59" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>22330051920399</v>
-      </c>
-      <c r="B60" t="s">
-        <v>105</v>
-      </c>
-      <c r="C60" t="s">
-        <v>138</v>
-      </c>
-      <c r="D60" t="s">
-        <v>177</v>
-      </c>
-      <c r="E60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>22330051920399</v>
-      </c>
-      <c r="B61" t="s">
-        <v>105</v>
-      </c>
-      <c r="C61" t="s">
-        <v>138</v>
-      </c>
-      <c r="D61" t="s">
-        <v>177</v>
-      </c>
-      <c r="E61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>22330051920375</v>
-      </c>
-      <c r="B62" t="s">
-        <v>106</v>
-      </c>
-      <c r="C62" t="s">
-        <v>138</v>
-      </c>
-      <c r="D62" t="s">
-        <v>178</v>
-      </c>
-      <c r="E62" t="s">
-        <v>10</v>
-      </c>
-      <c r="F62" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>22330051920375</v>
-      </c>
-      <c r="B63" t="s">
-        <v>106</v>
-      </c>
-      <c r="C63" t="s">
-        <v>138</v>
-      </c>
-      <c r="D63" t="s">
-        <v>178</v>
-      </c>
-      <c r="E63" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>22330061460548</v>
-      </c>
-      <c r="B64" t="s">
-        <v>107</v>
-      </c>
-      <c r="C64" t="s">
-        <v>139</v>
-      </c>
-      <c r="D64" t="s">
-        <v>179</v>
-      </c>
-      <c r="E64" t="s">
-        <v>10</v>
-      </c>
-      <c r="F64" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>22330061460548</v>
-      </c>
-      <c r="B65" t="s">
-        <v>107</v>
-      </c>
-      <c r="C65" t="s">
-        <v>139</v>
-      </c>
-      <c r="D65" t="s">
-        <v>179</v>
-      </c>
-      <c r="E65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>22330051920400</v>
-      </c>
-      <c r="B66" t="s">
-        <v>108</v>
-      </c>
-      <c r="C66" t="s">
-        <v>140</v>
-      </c>
-      <c r="D66" t="s">
-        <v>180</v>
-      </c>
-      <c r="E66" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>22330051920400</v>
-      </c>
-      <c r="B67" t="s">
-        <v>108</v>
-      </c>
-      <c r="C67" t="s">
-        <v>140</v>
-      </c>
-      <c r="D67" t="s">
-        <v>180</v>
-      </c>
-      <c r="E67" t="s">
-        <v>8</v>
-      </c>
-      <c r="F67" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>22330051920253</v>
-      </c>
-      <c r="B68" t="s">
-        <v>109</v>
-      </c>
-      <c r="C68" t="s">
-        <v>98</v>
-      </c>
-      <c r="D68" t="s">
-        <v>181</v>
-      </c>
-      <c r="E68" t="s">
-        <v>10</v>
-      </c>
-      <c r="F68" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>22330051920253</v>
-      </c>
-      <c r="B69" t="s">
-        <v>109</v>
-      </c>
-      <c r="C69" t="s">
-        <v>98</v>
-      </c>
-      <c r="D69" t="s">
-        <v>181</v>
-      </c>
-      <c r="E69" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>22330051920235</v>
-      </c>
-      <c r="B70" t="s">
-        <v>110</v>
-      </c>
-      <c r="C70" t="s">
-        <v>141</v>
-      </c>
-      <c r="D70" t="s">
-        <v>182</v>
-      </c>
-      <c r="E70" t="s">
-        <v>10</v>
-      </c>
-      <c r="F70" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>22330051920235</v>
-      </c>
-      <c r="B71" t="s">
-        <v>110</v>
-      </c>
-      <c r="C71" t="s">
-        <v>141</v>
-      </c>
-      <c r="D71" t="s">
-        <v>182</v>
-      </c>
-      <c r="E71" t="s">
-        <v>8</v>
-      </c>
-      <c r="F71" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>22330051920366</v>
-      </c>
-      <c r="B72" t="s">
-        <v>111</v>
-      </c>
-      <c r="C72" t="s">
-        <v>142</v>
-      </c>
-      <c r="D72" t="s">
-        <v>183</v>
-      </c>
-      <c r="E72" t="s">
-        <v>10</v>
-      </c>
-      <c r="F72" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>22330051920366</v>
-      </c>
-      <c r="B73" t="s">
-        <v>111</v>
-      </c>
-      <c r="C73" t="s">
-        <v>142</v>
-      </c>
-      <c r="D73" t="s">
-        <v>183</v>
-      </c>
-      <c r="E73" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>22330051920368</v>
-      </c>
-      <c r="B74" t="s">
-        <v>112</v>
-      </c>
-      <c r="C74" t="s">
-        <v>95</v>
-      </c>
-      <c r="D74" t="s">
-        <v>184</v>
-      </c>
-      <c r="E74" t="s">
-        <v>10</v>
-      </c>
-      <c r="F74" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>22330051920368</v>
-      </c>
-      <c r="B75" t="s">
-        <v>112</v>
-      </c>
-      <c r="C75" t="s">
-        <v>95</v>
-      </c>
-      <c r="D75" t="s">
-        <v>184</v>
-      </c>
-      <c r="E75" t="s">
-        <v>8</v>
-      </c>
-      <c r="F75" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>22330051920254</v>
-      </c>
-      <c r="B76" t="s">
-        <v>113</v>
-      </c>
-      <c r="C76" t="s">
-        <v>112</v>
-      </c>
-      <c r="D76" t="s">
-        <v>185</v>
-      </c>
-      <c r="E76" t="s">
-        <v>10</v>
-      </c>
-      <c r="F76" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>22330051920254</v>
-      </c>
-      <c r="B77" t="s">
-        <v>113</v>
-      </c>
-      <c r="C77" t="s">
-        <v>112</v>
-      </c>
-      <c r="D77" t="s">
-        <v>185</v>
-      </c>
-      <c r="E77" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>22330051920257</v>
-      </c>
-      <c r="B78" t="s">
-        <v>114</v>
-      </c>
-      <c r="C78" t="s">
-        <v>143</v>
-      </c>
-      <c r="D78" t="s">
-        <v>186</v>
-      </c>
-      <c r="E78" t="s">
-        <v>10</v>
-      </c>
-      <c r="F78" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>22330051920257</v>
-      </c>
-      <c r="B79" t="s">
-        <v>114</v>
-      </c>
-      <c r="C79" t="s">
-        <v>143</v>
-      </c>
-      <c r="D79" t="s">
-        <v>186</v>
-      </c>
-      <c r="E79" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>22330051920256</v>
-      </c>
-      <c r="B80" t="s">
-        <v>115</v>
-      </c>
-      <c r="C80" t="s">
-        <v>144</v>
-      </c>
-      <c r="D80" t="s">
-        <v>187</v>
-      </c>
-      <c r="E80" t="s">
-        <v>10</v>
-      </c>
-      <c r="F80" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>22330051920256</v>
-      </c>
-      <c r="B81" t="s">
-        <v>115</v>
-      </c>
-      <c r="C81" t="s">
-        <v>144</v>
-      </c>
-      <c r="D81" t="s">
-        <v>187</v>
-      </c>
-      <c r="E81" t="s">
-        <v>8</v>
-      </c>
-      <c r="F81" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>22330051920401</v>
-      </c>
-      <c r="B82" t="s">
-        <v>116</v>
-      </c>
-      <c r="C82" t="s">
-        <v>145</v>
-      </c>
-      <c r="D82" t="s">
-        <v>188</v>
-      </c>
-      <c r="E82" t="s">
-        <v>10</v>
-      </c>
-      <c r="F82" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>22330051920401</v>
-      </c>
-      <c r="B83" t="s">
-        <v>116</v>
-      </c>
-      <c r="C83" t="s">
-        <v>145</v>
-      </c>
-      <c r="D83" t="s">
-        <v>188</v>
-      </c>
-      <c r="E83" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>22330051920259</v>
-      </c>
-      <c r="B84" t="s">
-        <v>117</v>
-      </c>
-      <c r="C84" t="s">
-        <v>146</v>
-      </c>
-      <c r="D84" t="s">
-        <v>189</v>
-      </c>
-      <c r="E84" t="s">
-        <v>10</v>
-      </c>
-      <c r="F84" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>22330051920259</v>
-      </c>
-      <c r="B85" t="s">
-        <v>117</v>
-      </c>
-      <c r="C85" t="s">
-        <v>146</v>
-      </c>
-      <c r="D85" t="s">
-        <v>189</v>
-      </c>
-      <c r="E85" t="s">
-        <v>8</v>
-      </c>
-      <c r="F85" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>22330051920176</v>
-      </c>
-      <c r="B86" t="s">
-        <v>118</v>
-      </c>
-      <c r="C86" t="s">
-        <v>147</v>
-      </c>
-      <c r="D86" t="s">
-        <v>190</v>
-      </c>
-      <c r="E86" t="s">
-        <v>10</v>
-      </c>
-      <c r="F86" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>22330051920176</v>
-      </c>
-      <c r="B87" t="s">
-        <v>118</v>
-      </c>
-      <c r="C87" t="s">
-        <v>147</v>
-      </c>
-      <c r="D87" t="s">
-        <v>190</v>
-      </c>
-      <c r="E87" t="s">
-        <v>8</v>
-      </c>
-      <c r="F87" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -8960,7 +7246,7 @@
         <v>148</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -8977,7 +7263,7 @@
         <v>149</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8994,7 +7280,7 @@
         <v>150</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -9011,7 +7297,7 @@
         <v>151</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -9028,7 +7314,7 @@
         <v>152</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -9045,7 +7331,7 @@
         <v>153</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -9062,7 +7348,7 @@
         <v>154</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -9079,7 +7365,7 @@
         <v>155</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -9096,7 +7382,7 @@
         <v>156</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -9113,7 +7399,7 @@
         <v>157</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -9130,7 +7416,7 @@
         <v>158</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -9147,7 +7433,7 @@
         <v>159</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -9164,7 +7450,7 @@
         <v>160</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -9181,7 +7467,7 @@
         <v>161</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -9198,7 +7484,7 @@
         <v>162</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -9215,7 +7501,7 @@
         <v>163</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -9232,7 +7518,7 @@
         <v>164</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -9249,7 +7535,7 @@
         <v>165</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -9266,7 +7552,7 @@
         <v>166</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -9283,7 +7569,7 @@
         <v>167</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -9300,7 +7586,7 @@
         <v>168</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -9317,7 +7603,7 @@
         <v>169</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -9334,7 +7620,7 @@
         <v>170</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -9351,7 +7637,7 @@
         <v>171</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -9368,7 +7654,7 @@
         <v>172</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -9385,7 +7671,7 @@
         <v>173</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -9402,7 +7688,7 @@
         <v>174</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -9419,7 +7705,7 @@
         <v>175</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -9436,7 +7722,7 @@
         <v>176</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -9453,7 +7739,7 @@
         <v>177</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -9470,7 +7756,7 @@
         <v>178</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -9487,7 +7773,7 @@
         <v>179</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -9504,7 +7790,7 @@
         <v>180</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -9521,7 +7807,7 @@
         <v>181</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -9538,7 +7824,7 @@
         <v>182</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -9555,7 +7841,7 @@
         <v>183</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -9572,7 +7858,7 @@
         <v>184</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -9589,7 +7875,7 @@
         <v>185</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -9606,7 +7892,7 @@
         <v>186</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -9623,7 +7909,7 @@
         <v>187</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -9640,7 +7926,7 @@
         <v>188</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -9657,7 +7943,7 @@
         <v>189</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -9674,7 +7960,7 @@
         <v>190</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9684,7 +7970,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9716,830 +8002,393 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920231</v>
+        <v>22330051920230</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920231</v>
+        <v>22330051920230</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>67</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920260</v>
+        <v>22330051920233</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>68</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920260</v>
+        <v>22330051920233</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>67</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920234</v>
+        <v>20330051920237</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920234</v>
+        <v>20330051920237</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920238</v>
+        <v>22330051920401</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>68</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920238</v>
+        <v>22330051920401</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>67</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920241</v>
+        <v>22330061460173</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920241</v>
+        <v>22330051920240</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
         <v>67</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920243</v>
+        <v>22330051920241</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920243</v>
+        <v>21330051420317</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="D13" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920245</v>
+        <v>22330051920249</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D14" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
         <v>68</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920245</v>
+        <v>22330051920251</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D15" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920318</v>
+        <v>22330051920375</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="D16" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920318</v>
+        <v>22330061460548</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D17" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
         <v>67</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920319</v>
+        <v>22330051920400</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D18" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
         <v>68</v>
       </c>
       <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920319</v>
-      </c>
-      <c r="B19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" t="s">
-        <v>133</v>
-      </c>
-      <c r="D19" t="s">
-        <v>169</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>67</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920237</v>
-      </c>
-      <c r="B20" t="s">
-        <v>99</v>
-      </c>
-      <c r="C20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" t="s">
-        <v>171</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920237</v>
-      </c>
-      <c r="B21" t="s">
-        <v>99</v>
-      </c>
-      <c r="C21" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" t="s">
-        <v>171</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920414</v>
-      </c>
-      <c r="B22" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" t="s">
-        <v>92</v>
-      </c>
-      <c r="D22" t="s">
-        <v>173</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>68</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920414</v>
-      </c>
-      <c r="B23" t="s">
-        <v>101</v>
-      </c>
-      <c r="C23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" t="s">
-        <v>173</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>67</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920248</v>
-      </c>
-      <c r="B24" t="s">
-        <v>102</v>
-      </c>
-      <c r="C24" t="s">
-        <v>135</v>
-      </c>
-      <c r="D24" t="s">
-        <v>174</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920248</v>
-      </c>
-      <c r="B25" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" t="s">
-        <v>135</v>
-      </c>
-      <c r="D25" t="s">
-        <v>174</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>67</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920250</v>
-      </c>
-      <c r="B26" t="s">
-        <v>103</v>
-      </c>
-      <c r="C26" t="s">
-        <v>136</v>
-      </c>
-      <c r="D26" t="s">
-        <v>175</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>68</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920250</v>
-      </c>
-      <c r="B27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C27" t="s">
-        <v>136</v>
-      </c>
-      <c r="D27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>67</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>22330051920399</v>
-      </c>
-      <c r="B28" t="s">
-        <v>105</v>
-      </c>
-      <c r="C28" t="s">
-        <v>138</v>
-      </c>
-      <c r="D28" t="s">
-        <v>177</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>68</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>22330051920399</v>
-      </c>
-      <c r="B29" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29" t="s">
-        <v>138</v>
-      </c>
-      <c r="D29" t="s">
-        <v>177</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>67</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>22330051920235</v>
-      </c>
-      <c r="B30" t="s">
-        <v>110</v>
-      </c>
-      <c r="C30" t="s">
-        <v>141</v>
-      </c>
-      <c r="D30" t="s">
-        <v>182</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>68</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>22330051920235</v>
-      </c>
-      <c r="B31" t="s">
-        <v>110</v>
-      </c>
-      <c r="C31" t="s">
-        <v>141</v>
-      </c>
-      <c r="D31" t="s">
-        <v>182</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>67</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>22330051920254</v>
-      </c>
-      <c r="B32" t="s">
-        <v>113</v>
-      </c>
-      <c r="C32" t="s">
-        <v>112</v>
-      </c>
-      <c r="D32" t="s">
-        <v>185</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>68</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>22330051920254</v>
-      </c>
-      <c r="B33" t="s">
-        <v>113</v>
-      </c>
-      <c r="C33" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" t="s">
-        <v>185</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>67</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>22330051920257</v>
-      </c>
-      <c r="B34" t="s">
-        <v>114</v>
-      </c>
-      <c r="C34" t="s">
-        <v>143</v>
-      </c>
-      <c r="D34" t="s">
-        <v>186</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>68</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>22330051920257</v>
-      </c>
-      <c r="B35" t="s">
-        <v>114</v>
-      </c>
-      <c r="C35" t="s">
-        <v>143</v>
-      </c>
-      <c r="D35" t="s">
-        <v>186</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>67</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>22330051920256</v>
-      </c>
-      <c r="B36" t="s">
-        <v>115</v>
-      </c>
-      <c r="C36" t="s">
-        <v>144</v>
-      </c>
-      <c r="D36" t="s">
-        <v>187</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>68</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>22330051920256</v>
-      </c>
-      <c r="B37" t="s">
-        <v>115</v>
-      </c>
-      <c r="C37" t="s">
-        <v>144</v>
-      </c>
-      <c r="D37" t="s">
-        <v>187</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>67</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2ALCV - Estadisticos 20222.xlsx
+++ b/grupos/2ALCV - Estadisticos 20222.xlsx
@@ -225,7 +225,7 @@
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
     <t>Rivera Serra Alma Lilian</t>

--- a/grupos/2ALCV - Estadisticos 20222.xlsx
+++ b/grupos/2ALCV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="187">
   <si>
     <t>Materia</t>
   </si>
@@ -129,9 +129,6 @@
     <t>LOPEZ CIRUELO LUISA MARIA</t>
   </si>
   <si>
-    <t>MALDONADO RAMON JOSE ALBIN</t>
-  </si>
-  <si>
     <t>MARES HERNANDEZ JULIO ANTONIO</t>
   </si>
   <si>
@@ -327,9 +324,6 @@
     <t>MARES</t>
   </si>
   <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
     <t>MENDOZA</t>
   </si>
   <si>
@@ -426,9 +420,6 @@
     <t>CIRUELO</t>
   </si>
   <si>
-    <t>RAMON</t>
-  </si>
-  <si>
     <t>ORTEGA</t>
   </si>
   <si>
@@ -541,9 +532,6 @@
   </si>
   <si>
     <t>JULIO ANTONIO</t>
-  </si>
-  <si>
-    <t>JOSE ALBIN</t>
   </si>
   <si>
     <t>ATZIN LUCERO</t>
@@ -949,7 +937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y46"/>
+  <dimension ref="A1:Y45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -2913,182 +2901,182 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E28">
+        <v>7</v>
+      </c>
+      <c r="F28">
+        <v>6</v>
+      </c>
+      <c r="G28">
+        <v>7</v>
+      </c>
+      <c r="H28">
+        <v>-1</v>
+      </c>
+      <c r="I28">
+        <v>-1</v>
+      </c>
+      <c r="J28">
+        <v>-1</v>
+      </c>
+      <c r="K28">
+        <v>-1</v>
+      </c>
+      <c r="L28">
+        <v>-1</v>
+      </c>
+      <c r="M28">
+        <v>-1</v>
+      </c>
+      <c r="N28">
+        <v>-1</v>
+      </c>
+      <c r="O28">
+        <v>-1</v>
+      </c>
+      <c r="P28">
+        <v>-1</v>
+      </c>
+      <c r="Q28">
+        <v>-1</v>
+      </c>
+      <c r="R28">
+        <v>-1</v>
+      </c>
+      <c r="S28">
+        <v>-1</v>
+      </c>
+      <c r="T28">
+        <v>6</v>
+      </c>
+      <c r="U28">
+        <v>6</v>
+      </c>
+      <c r="V28">
         <v>8</v>
       </c>
-      <c r="F28">
-        <v>10</v>
-      </c>
-      <c r="G28">
-        <v>8</v>
-      </c>
-      <c r="H28">
-        <v>-1</v>
-      </c>
-      <c r="I28">
-        <v>-1</v>
-      </c>
-      <c r="J28">
-        <v>-1</v>
-      </c>
-      <c r="K28">
-        <v>-1</v>
-      </c>
-      <c r="L28">
-        <v>-1</v>
-      </c>
-      <c r="M28">
-        <v>-1</v>
-      </c>
-      <c r="N28">
-        <v>-1</v>
-      </c>
-      <c r="O28">
-        <v>-1</v>
-      </c>
-      <c r="P28">
-        <v>-1</v>
-      </c>
-      <c r="Q28">
-        <v>-1</v>
-      </c>
-      <c r="R28">
-        <v>-1</v>
-      </c>
-      <c r="S28">
-        <v>-1</v>
-      </c>
-      <c r="T28">
-        <v>10</v>
-      </c>
-      <c r="U28">
-        <v>10</v>
-      </c>
-      <c r="V28">
-        <v>6</v>
-      </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B29">
-        <v>6</v>
-      </c>
-      <c r="C29">
-        <v>6</v>
-      </c>
-      <c r="D29">
-        <v>8</v>
-      </c>
       <c r="E29">
-        <v>7</v>
-      </c>
-      <c r="F29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G29">
-        <v>7</v>
-      </c>
-      <c r="H29">
-        <v>-1</v>
-      </c>
-      <c r="I29">
-        <v>-1</v>
-      </c>
-      <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
-      <c r="L29">
-        <v>-1</v>
-      </c>
       <c r="M29">
         <v>-1</v>
       </c>
-      <c r="N29">
-        <v>-1</v>
-      </c>
-      <c r="O29">
-        <v>-1</v>
-      </c>
-      <c r="P29">
-        <v>-1</v>
-      </c>
       <c r="Q29">
         <v>-1</v>
       </c>
-      <c r="R29">
-        <v>-1</v>
-      </c>
       <c r="S29">
         <v>-1</v>
       </c>
-      <c r="T29">
-        <v>6</v>
-      </c>
-      <c r="U29">
-        <v>6</v>
-      </c>
-      <c r="V29">
-        <v>8</v>
-      </c>
       <c r="W29">
-        <v>7</v>
-      </c>
-      <c r="X29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>9</v>
+      </c>
+      <c r="D30">
+        <v>10</v>
+      </c>
       <c r="E30">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="F30">
+        <v>10</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="H30">
+        <v>-1</v>
+      </c>
+      <c r="I30">
+        <v>-1</v>
+      </c>
+      <c r="J30">
+        <v>-1</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
+      <c r="L30">
+        <v>-1</v>
+      </c>
       <c r="M30">
         <v>-1</v>
       </c>
+      <c r="N30">
+        <v>-1</v>
+      </c>
+      <c r="O30">
+        <v>-1</v>
+      </c>
+      <c r="P30">
+        <v>-1</v>
+      </c>
       <c r="Q30">
         <v>-1</v>
       </c>
+      <c r="R30">
+        <v>-1</v>
+      </c>
       <c r="S30">
         <v>-1</v>
       </c>
+      <c r="T30">
+        <v>5</v>
+      </c>
+      <c r="U30">
+        <v>9</v>
+      </c>
+      <c r="V30">
+        <v>10</v>
+      </c>
       <c r="W30">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="X30">
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3096,23 +3084,23 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C31">
+        <v>6</v>
+      </c>
+      <c r="D31">
+        <v>7</v>
+      </c>
+      <c r="E31">
+        <v>7</v>
+      </c>
+      <c r="F31">
         <v>9</v>
       </c>
-      <c r="D31">
-        <v>10</v>
-      </c>
-      <c r="E31">
+      <c r="G31">
         <v>9</v>
       </c>
-      <c r="F31">
-        <v>10</v>
-      </c>
-      <c r="G31">
-        <v>7</v>
-      </c>
       <c r="H31">
         <v>-1</v>
       </c>
@@ -3150,22 +3138,22 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U31">
+        <v>6</v>
+      </c>
+      <c r="V31">
+        <v>7</v>
+      </c>
+      <c r="W31">
+        <v>7</v>
+      </c>
+      <c r="X31">
         <v>9</v>
       </c>
-      <c r="V31">
-        <v>10</v>
-      </c>
-      <c r="W31">
+      <c r="Y31">
         <v>9</v>
-      </c>
-      <c r="X31">
-        <v>10</v>
-      </c>
-      <c r="Y31">
-        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3173,22 +3161,22 @@
         <v>40</v>
       </c>
       <c r="B32">
+        <v>6</v>
+      </c>
+      <c r="C32">
+        <v>6</v>
+      </c>
+      <c r="D32">
+        <v>5</v>
+      </c>
+      <c r="E32">
+        <v>6</v>
+      </c>
+      <c r="F32">
         <v>8</v>
       </c>
-      <c r="C32">
-        <v>6</v>
-      </c>
-      <c r="D32">
-        <v>7</v>
-      </c>
-      <c r="E32">
-        <v>7</v>
-      </c>
-      <c r="F32">
-        <v>9</v>
-      </c>
       <c r="G32">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -3227,22 +3215,22 @@
         <v>-1</v>
       </c>
       <c r="T32">
+        <v>6</v>
+      </c>
+      <c r="U32">
+        <v>6</v>
+      </c>
+      <c r="V32">
+        <v>5</v>
+      </c>
+      <c r="W32">
+        <v>6</v>
+      </c>
+      <c r="X32">
         <v>8</v>
       </c>
-      <c r="U32">
-        <v>6</v>
-      </c>
-      <c r="V32">
-        <v>7</v>
-      </c>
-      <c r="W32">
-        <v>7</v>
-      </c>
-      <c r="X32">
-        <v>9</v>
-      </c>
       <c r="Y32">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3250,76 +3238,76 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F33">
+        <v>6</v>
+      </c>
+      <c r="G33">
+        <v>6</v>
+      </c>
+      <c r="H33">
+        <v>-1</v>
+      </c>
+      <c r="I33">
+        <v>-1</v>
+      </c>
+      <c r="J33">
+        <v>-1</v>
+      </c>
+      <c r="K33">
+        <v>-1</v>
+      </c>
+      <c r="L33">
+        <v>-1</v>
+      </c>
+      <c r="M33">
+        <v>-1</v>
+      </c>
+      <c r="N33">
+        <v>-1</v>
+      </c>
+      <c r="O33">
+        <v>-1</v>
+      </c>
+      <c r="P33">
+        <v>-1</v>
+      </c>
+      <c r="Q33">
+        <v>-1</v>
+      </c>
+      <c r="R33">
+        <v>-1</v>
+      </c>
+      <c r="S33">
+        <v>-1</v>
+      </c>
+      <c r="T33">
         <v>8</v>
       </c>
-      <c r="G33">
-        <v>7</v>
-      </c>
-      <c r="H33">
-        <v>-1</v>
-      </c>
-      <c r="I33">
-        <v>-1</v>
-      </c>
-      <c r="J33">
-        <v>-1</v>
-      </c>
-      <c r="K33">
-        <v>-1</v>
-      </c>
-      <c r="L33">
-        <v>-1</v>
-      </c>
-      <c r="M33">
-        <v>-1</v>
-      </c>
-      <c r="N33">
-        <v>-1</v>
-      </c>
-      <c r="O33">
-        <v>-1</v>
-      </c>
-      <c r="P33">
-        <v>-1</v>
-      </c>
-      <c r="Q33">
-        <v>-1</v>
-      </c>
-      <c r="R33">
-        <v>-1</v>
-      </c>
-      <c r="S33">
-        <v>-1</v>
-      </c>
-      <c r="T33">
-        <v>6</v>
-      </c>
       <c r="U33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3327,19 +3315,19 @@
         <v>42</v>
       </c>
       <c r="B34">
+        <v>7</v>
+      </c>
+      <c r="C34">
+        <v>6</v>
+      </c>
+      <c r="D34">
         <v>8</v>
       </c>
-      <c r="C34">
-        <v>7</v>
-      </c>
-      <c r="D34">
-        <v>6</v>
-      </c>
       <c r="E34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G34">
         <v>6</v>
@@ -3381,19 +3369,19 @@
         <v>-1</v>
       </c>
       <c r="T34">
+        <v>7</v>
+      </c>
+      <c r="U34">
+        <v>6</v>
+      </c>
+      <c r="V34">
         <v>8</v>
       </c>
-      <c r="U34">
-        <v>7</v>
-      </c>
-      <c r="V34">
-        <v>6</v>
-      </c>
       <c r="W34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y34">
         <v>6</v>
@@ -3404,70 +3392,70 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D35">
+        <v>6</v>
+      </c>
+      <c r="E35">
+        <v>9</v>
+      </c>
+      <c r="F35">
+        <v>5</v>
+      </c>
+      <c r="G35">
+        <v>6</v>
+      </c>
+      <c r="H35">
+        <v>-1</v>
+      </c>
+      <c r="I35">
+        <v>-1</v>
+      </c>
+      <c r="J35">
+        <v>-1</v>
+      </c>
+      <c r="K35">
+        <v>-1</v>
+      </c>
+      <c r="L35">
+        <v>-1</v>
+      </c>
+      <c r="M35">
+        <v>-1</v>
+      </c>
+      <c r="N35">
+        <v>-1</v>
+      </c>
+      <c r="O35">
+        <v>-1</v>
+      </c>
+      <c r="P35">
+        <v>-1</v>
+      </c>
+      <c r="Q35">
+        <v>-1</v>
+      </c>
+      <c r="R35">
+        <v>-1</v>
+      </c>
+      <c r="S35">
+        <v>-1</v>
+      </c>
+      <c r="T35">
+        <v>6</v>
+      </c>
+      <c r="U35">
         <v>8</v>
       </c>
-      <c r="E35">
-        <v>8</v>
-      </c>
-      <c r="F35">
-        <v>5</v>
-      </c>
-      <c r="G35">
-        <v>6</v>
-      </c>
-      <c r="H35">
-        <v>-1</v>
-      </c>
-      <c r="I35">
-        <v>-1</v>
-      </c>
-      <c r="J35">
-        <v>-1</v>
-      </c>
-      <c r="K35">
-        <v>-1</v>
-      </c>
-      <c r="L35">
-        <v>-1</v>
-      </c>
-      <c r="M35">
-        <v>-1</v>
-      </c>
-      <c r="N35">
-        <v>-1</v>
-      </c>
-      <c r="O35">
-        <v>-1</v>
-      </c>
-      <c r="P35">
-        <v>-1</v>
-      </c>
-      <c r="Q35">
-        <v>-1</v>
-      </c>
-      <c r="R35">
-        <v>-1</v>
-      </c>
-      <c r="S35">
-        <v>-1</v>
-      </c>
-      <c r="T35">
-        <v>7</v>
-      </c>
-      <c r="U35">
-        <v>6</v>
-      </c>
       <c r="V35">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>5</v>
@@ -3481,19 +3469,19 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E36">
         <v>9</v>
       </c>
       <c r="F36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G36">
         <v>6</v>
@@ -3535,19 +3523,19 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W36">
         <v>9</v>
       </c>
       <c r="X36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -3558,22 +3546,22 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C37">
         <v>7</v>
       </c>
       <c r="D37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E37">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H37">
         <v>-1</v>
@@ -3612,22 +3600,22 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U37">
         <v>7</v>
       </c>
       <c r="V37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3635,13 +3623,13 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38">
         <v>5</v>
@@ -3650,7 +3638,7 @@
         <v>5</v>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H38">
         <v>-1</v>
@@ -3689,13 +3677,13 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W38">
         <v>5</v>
@@ -3704,7 +3692,7 @@
         <v>5</v>
       </c>
       <c r="Y38">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3715,10 +3703,10 @@
         <v>5</v>
       </c>
       <c r="C39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E39">
         <v>5</v>
@@ -3769,10 +3757,10 @@
         <v>5</v>
       </c>
       <c r="U39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V39">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W39">
         <v>5</v>
@@ -3789,22 +3777,22 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C40">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D40">
+        <v>8</v>
+      </c>
+      <c r="E40">
         <v>10</v>
       </c>
-      <c r="E40">
-        <v>5</v>
-      </c>
       <c r="F40">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G40">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H40">
         <v>-1</v>
@@ -3843,22 +3831,22 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U40">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V40">
+        <v>8</v>
+      </c>
+      <c r="W40">
         <v>10</v>
       </c>
-      <c r="W40">
-        <v>5</v>
-      </c>
       <c r="X40">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y40">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3866,76 +3854,76 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D41">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E41">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F41">
+        <v>6</v>
+      </c>
+      <c r="G41">
+        <v>7</v>
+      </c>
+      <c r="H41">
+        <v>-1</v>
+      </c>
+      <c r="I41">
+        <v>-1</v>
+      </c>
+      <c r="J41">
+        <v>-1</v>
+      </c>
+      <c r="K41">
+        <v>-1</v>
+      </c>
+      <c r="L41">
+        <v>-1</v>
+      </c>
+      <c r="M41">
+        <v>-1</v>
+      </c>
+      <c r="N41">
+        <v>-1</v>
+      </c>
+      <c r="O41">
+        <v>-1</v>
+      </c>
+      <c r="P41">
+        <v>-1</v>
+      </c>
+      <c r="Q41">
+        <v>-1</v>
+      </c>
+      <c r="R41">
+        <v>-1</v>
+      </c>
+      <c r="S41">
+        <v>-1</v>
+      </c>
+      <c r="T41">
+        <v>6</v>
+      </c>
+      <c r="U41">
         <v>9</v>
       </c>
-      <c r="G41">
-        <v>9</v>
-      </c>
-      <c r="H41">
-        <v>-1</v>
-      </c>
-      <c r="I41">
-        <v>-1</v>
-      </c>
-      <c r="J41">
-        <v>-1</v>
-      </c>
-      <c r="K41">
-        <v>-1</v>
-      </c>
-      <c r="L41">
-        <v>-1</v>
-      </c>
-      <c r="M41">
-        <v>-1</v>
-      </c>
-      <c r="N41">
-        <v>-1</v>
-      </c>
-      <c r="O41">
-        <v>-1</v>
-      </c>
-      <c r="P41">
-        <v>-1</v>
-      </c>
-      <c r="Q41">
-        <v>-1</v>
-      </c>
-      <c r="R41">
-        <v>-1</v>
-      </c>
-      <c r="S41">
-        <v>-1</v>
-      </c>
-      <c r="T41">
-        <v>8</v>
-      </c>
-      <c r="U41">
-        <v>10</v>
-      </c>
       <c r="V41">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W41">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X41">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y41">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3946,19 +3934,19 @@
         <v>6</v>
       </c>
       <c r="C42">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D42">
         <v>6</v>
       </c>
       <c r="E42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F42">
         <v>6</v>
       </c>
       <c r="G42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H42">
         <v>-1</v>
@@ -4000,19 +3988,19 @@
         <v>6</v>
       </c>
       <c r="U42">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V42">
         <v>6</v>
       </c>
       <c r="W42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X42">
         <v>6</v>
       </c>
       <c r="Y42">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -4020,22 +4008,22 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43">
         <v>7</v>
       </c>
       <c r="D43">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G43">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H43">
         <v>-1</v>
@@ -4074,22 +4062,22 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U43">
         <v>7</v>
       </c>
       <c r="V43">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y43">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4097,22 +4085,22 @@
         <v>52</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D44">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F44">
         <v>5</v>
       </c>
       <c r="G44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H44">
         <v>-1</v>
@@ -4151,22 +4139,22 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U44">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V44">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X44">
         <v>5</v>
       </c>
       <c r="Y44">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -4174,13 +4162,13 @@
         <v>53</v>
       </c>
       <c r="B45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E45">
         <v>5</v>
@@ -4189,7 +4177,7 @@
         <v>5</v>
       </c>
       <c r="G45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H45">
         <v>-1</v>
@@ -4228,13 +4216,13 @@
         <v>-1</v>
       </c>
       <c r="T45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U45">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W45">
         <v>5</v>
@@ -4243,83 +4231,6 @@
         <v>5</v>
       </c>
       <c r="Y45">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25">
-      <c r="A46" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B46">
-        <v>5</v>
-      </c>
-      <c r="C46">
-        <v>6</v>
-      </c>
-      <c r="D46">
-        <v>6</v>
-      </c>
-      <c r="E46">
-        <v>5</v>
-      </c>
-      <c r="F46">
-        <v>5</v>
-      </c>
-      <c r="G46">
-        <v>6</v>
-      </c>
-      <c r="H46">
-        <v>-1</v>
-      </c>
-      <c r="I46">
-        <v>-1</v>
-      </c>
-      <c r="J46">
-        <v>-1</v>
-      </c>
-      <c r="K46">
-        <v>-1</v>
-      </c>
-      <c r="L46">
-        <v>-1</v>
-      </c>
-      <c r="M46">
-        <v>-1</v>
-      </c>
-      <c r="N46">
-        <v>-1</v>
-      </c>
-      <c r="O46">
-        <v>-1</v>
-      </c>
-      <c r="P46">
-        <v>-1</v>
-      </c>
-      <c r="Q46">
-        <v>-1</v>
-      </c>
-      <c r="R46">
-        <v>-1</v>
-      </c>
-      <c r="S46">
-        <v>-1</v>
-      </c>
-      <c r="T46">
-        <v>5</v>
-      </c>
-      <c r="U46">
-        <v>6</v>
-      </c>
-      <c r="V46">
-        <v>6</v>
-      </c>
-      <c r="W46">
-        <v>5</v>
-      </c>
-      <c r="X46">
-        <v>5</v>
-      </c>
-      <c r="Y46">
         <v>6</v>
       </c>
     </row>
@@ -4336,7 +4247,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:S45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -4345,7 +4256,7 @@
     <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -4353,7 +4264,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -4361,7 +4272,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -5845,13 +5756,13 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C28">
         <v>100</v>
       </c>
       <c r="D28">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E28">
         <v>104</v>
@@ -5903,55 +5814,19 @@
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B29">
-        <v>100</v>
-      </c>
-      <c r="C29">
-        <v>100</v>
-      </c>
-      <c r="D29">
-        <v>90</v>
-      </c>
       <c r="E29">
-        <v>104</v>
-      </c>
-      <c r="F29">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G29">
-        <v>100</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
       <c r="M29">
         <v>0</v>
       </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
       <c r="Q29">
-        <v>0</v>
-      </c>
-      <c r="R29">
         <v>0</v>
       </c>
       <c r="S29">
@@ -5962,19 +5837,55 @@
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="B30">
+        <v>90</v>
+      </c>
+      <c r="C30">
+        <v>100</v>
+      </c>
+      <c r="D30">
+        <v>100</v>
+      </c>
       <c r="E30">
-        <v>88</v>
+        <v>104</v>
+      </c>
+      <c r="F30">
+        <v>90</v>
       </c>
       <c r="G30">
-        <v>83.3</v>
+        <v>100</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
       <c r="M30">
         <v>0</v>
       </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
       <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
         <v>0</v>
       </c>
       <c r="S30">
@@ -5998,7 +5909,7 @@
         <v>104</v>
       </c>
       <c r="F31">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G31">
         <v>100</v>
@@ -6045,13 +5956,13 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C32">
         <v>100</v>
       </c>
       <c r="D32">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E32">
         <v>104</v>
@@ -6110,7 +6021,7 @@
         <v>100</v>
       </c>
       <c r="D33">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="E33">
         <v>104</v>
@@ -6163,13 +6074,13 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C34">
         <v>100</v>
       </c>
       <c r="D34">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E34">
         <v>104</v>
@@ -6222,13 +6133,13 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C35">
         <v>100</v>
       </c>
       <c r="D35">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E35">
         <v>104</v>
@@ -6281,13 +6192,13 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C36">
         <v>100</v>
       </c>
       <c r="D36">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E36">
         <v>104</v>
@@ -6340,7 +6251,7 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -6399,13 +6310,13 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C38">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="D38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>104</v>
@@ -6461,16 +6372,16 @@
         <v>90</v>
       </c>
       <c r="C39">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E39">
         <v>104</v>
       </c>
       <c r="F39">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G39">
         <v>100</v>
@@ -6517,7 +6428,7 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -6529,7 +6440,7 @@
         <v>104</v>
       </c>
       <c r="F40">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G40">
         <v>100</v>
@@ -6576,7 +6487,7 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C41">
         <v>100</v>
@@ -6588,7 +6499,7 @@
         <v>104</v>
       </c>
       <c r="F41">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G41">
         <v>100</v>
@@ -6641,13 +6552,13 @@
         <v>100</v>
       </c>
       <c r="D42">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E42">
         <v>104</v>
       </c>
       <c r="F42">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G42">
         <v>100</v>
@@ -6694,19 +6605,19 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C43">
         <v>100</v>
       </c>
       <c r="D43">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E43">
         <v>104</v>
       </c>
       <c r="F43">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G43">
         <v>100</v>
@@ -6753,13 +6664,13 @@
         <v>52</v>
       </c>
       <c r="B44">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C44">
         <v>100</v>
       </c>
       <c r="D44">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="E44">
         <v>104</v>
@@ -6812,13 +6723,13 @@
         <v>53</v>
       </c>
       <c r="B45">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C45">
         <v>100</v>
       </c>
       <c r="D45">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E45">
         <v>104</v>
@@ -6863,65 +6774,6 @@
         <v>0</v>
       </c>
       <c r="S45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19">
-      <c r="A46" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B46">
-        <v>100</v>
-      </c>
-      <c r="C46">
-        <v>100</v>
-      </c>
-      <c r="D46">
-        <v>80</v>
-      </c>
-      <c r="E46">
-        <v>104</v>
-      </c>
-      <c r="F46">
-        <v>100</v>
-      </c>
-      <c r="G46">
-        <v>100</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46">
-        <v>0</v>
-      </c>
-      <c r="P46">
-        <v>0</v>
-      </c>
-      <c r="Q46">
-        <v>0</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
         <v>0</v>
       </c>
     </row>
@@ -6948,31 +6800,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -6980,25 +6832,25 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E2">
         <v>19</v>
       </c>
       <c r="F2">
-        <v>54.76</v>
+        <v>53.66</v>
       </c>
       <c r="G2">
-        <v>45.24</v>
+        <v>46.34</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7012,25 +6864,25 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3">
         <v>17</v>
       </c>
       <c r="F3">
-        <v>59.52</v>
+        <v>58.54</v>
       </c>
       <c r="G3">
-        <v>40.48</v>
+        <v>41.46</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7044,22 +6896,22 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4">
         <v>13</v>
       </c>
       <c r="F4">
-        <v>69.77</v>
+        <v>69.05</v>
       </c>
       <c r="G4">
-        <v>30.23</v>
+        <v>30.95</v>
       </c>
       <c r="H4">
         <v>6.9</v>
@@ -7076,22 +6928,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5">
         <v>11</v>
       </c>
       <c r="F5">
-        <v>74.42</v>
+        <v>73.81</v>
       </c>
       <c r="G5">
-        <v>25.58</v>
+        <v>26.19</v>
       </c>
       <c r="H5">
         <v>6.7</v>
@@ -7108,22 +6960,22 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6">
         <v>8</v>
       </c>
       <c r="F6">
-        <v>80.48999999999999</v>
+        <v>80</v>
       </c>
       <c r="G6">
-        <v>19.51</v>
+        <v>20</v>
       </c>
       <c r="H6">
         <v>7</v>
@@ -7140,25 +6992,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7">
-        <v>92.86</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="G7">
-        <v>7.14</v>
+        <v>7.32</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7183,16 +7035,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -7208,7 +7060,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7217,19 +7069,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -7237,13 +7089,13 @@
         <v>22330061460173</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -7254,13 +7106,13 @@
         <v>22330051920231</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -7271,13 +7123,13 @@
         <v>22330051920230</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -7288,13 +7140,13 @@
         <v>22330051920260</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -7305,13 +7157,13 @@
         <v>22330051920232</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -7322,13 +7174,13 @@
         <v>22330051920233</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -7339,13 +7191,13 @@
         <v>22330051920234</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -7356,13 +7208,13 @@
         <v>22330051920236</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -7373,13 +7225,13 @@
         <v>22330051920237</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -7390,13 +7242,13 @@
         <v>22330051920238</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -7407,13 +7259,13 @@
         <v>22330051920239</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -7424,13 +7276,13 @@
         <v>22330051920240</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -7441,13 +7293,13 @@
         <v>22330051920422</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -7458,13 +7310,13 @@
         <v>22330051920241</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -7475,13 +7327,13 @@
         <v>22330051920242</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D16" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -7492,13 +7344,13 @@
         <v>22330051920357</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D17" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -7509,13 +7361,13 @@
         <v>22330051920243</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -7526,13 +7378,13 @@
         <v>22330051920245</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -7543,13 +7395,13 @@
         <v>22330051920369</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D20" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -7560,13 +7412,13 @@
         <v>22330051920318</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D21" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -7577,13 +7429,13 @@
         <v>21330051420317</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D22" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -7594,13 +7446,13 @@
         <v>22330051920319</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D23" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -7611,13 +7463,13 @@
         <v>22330051920246</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D24" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -7628,13 +7480,13 @@
         <v>20330051920237</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -7645,13 +7497,13 @@
         <v>22330051920249</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D26" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -7662,13 +7514,13 @@
         <v>22330051920414</v>
       </c>
       <c r="B27" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D27" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -7676,16 +7528,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920248</v>
+        <v>22330051920250</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C28" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D28" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -7693,16 +7545,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920250</v>
+        <v>22330051920251</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D29" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -7710,16 +7562,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920251</v>
+        <v>22330051920399</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C30" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -7727,16 +7579,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920399</v>
+        <v>22330051920375</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D31" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -7744,16 +7596,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330051920375</v>
+        <v>22330061460548</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C32" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D32" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -7761,16 +7613,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>22330061460548</v>
+        <v>22330051920400</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C33" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D33" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -7778,16 +7630,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>22330051920400</v>
+        <v>22330051920253</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C34" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -7795,16 +7647,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>22330051920253</v>
+        <v>22330051920235</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="D35" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -7812,16 +7664,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>22330051920235</v>
+        <v>22330051920366</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D36" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -7829,16 +7681,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>22330051920366</v>
+        <v>22330051920368</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C37" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="D37" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -7846,16 +7698,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>22330051920368</v>
+        <v>22330051920254</v>
       </c>
       <c r="B38" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="D38" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -7863,16 +7715,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>22330051920254</v>
+        <v>22330051920257</v>
       </c>
       <c r="B39" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C39" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="D39" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -7880,16 +7732,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>22330051920257</v>
+        <v>22330051920256</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C40" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D40" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -7897,16 +7749,16 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>22330051920256</v>
+        <v>22330051920401</v>
       </c>
       <c r="B41" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C41" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D41" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -7914,16 +7766,16 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>22330051920401</v>
+        <v>22330051920259</v>
       </c>
       <c r="B42" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C42" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D42" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -7931,35 +7783,18 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>22330051920259</v>
+        <v>22330051920176</v>
       </c>
       <c r="B43" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C43" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D43" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44">
-        <v>22330051920176</v>
-      </c>
-      <c r="B44" t="s">
-        <v>118</v>
-      </c>
-      <c r="C44" t="s">
-        <v>147</v>
-      </c>
-      <c r="D44" t="s">
-        <v>190</v>
-      </c>
-      <c r="E44">
         <v>0</v>
       </c>
     </row>
@@ -7979,22 +7814,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -8005,19 +7840,19 @@
         <v>22330051920230</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -8028,19 +7863,19 @@
         <v>22330051920230</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -8051,19 +7886,19 @@
         <v>22330051920233</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -8074,19 +7909,19 @@
         <v>22330051920233</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -8097,19 +7932,19 @@
         <v>20330051920237</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -8120,19 +7955,19 @@
         <v>20330051920237</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -8143,19 +7978,19 @@
         <v>22330051920401</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D8" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -8166,19 +8001,19 @@
         <v>22330051920401</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D9" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -8189,19 +8024,19 @@
         <v>22330061460173</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -8212,19 +8047,19 @@
         <v>22330051920240</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -8235,19 +8070,19 @@
         <v>22330051920241</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -8258,19 +8093,19 @@
         <v>21330051420317</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D13" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -8281,19 +8116,19 @@
         <v>22330051920249</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C14" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D14" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -8304,19 +8139,19 @@
         <v>22330051920251</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D15" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -8327,19 +8162,19 @@
         <v>22330051920375</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D16" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -8350,19 +8185,19 @@
         <v>22330061460548</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D17" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -8373,19 +8208,19 @@
         <v>22330051920400</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D18" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G18">
         <v>5</v>

--- a/grupos/2ALCV - Estadisticos 20222.xlsx
+++ b/grupos/2ALCV - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="110">
   <si>
     <t>Materia</t>
   </si>
@@ -219,12 +218,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
@@ -249,183 +248,60 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
     <t>APARICIO</t>
   </si>
   <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
+    <t>GAYTAN</t>
+  </si>
+  <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PIÑA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
   </si>
   <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
-    <t>FALFAN</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>GAYTAN</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LLANOS</t>
-  </si>
-  <si>
-    <t>LLAME</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MARES</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>DE ROMAN</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZAVALA</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>APOLINAR</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
+    <t>GROT</t>
+  </si>
+  <si>
+    <t>PULIDO</t>
   </si>
   <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>GROT</t>
-  </si>
-  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
@@ -435,114 +311,33 @@
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
+    <t>FERNANDA MARGARITA</t>
+  </si>
+  <si>
+    <t>AMALIA PAULINA</t>
+  </si>
+  <si>
+    <t>JACQUELINE</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>JUAN EMANUEL</t>
   </si>
   <si>
     <t>LUZ ARELY</t>
   </si>
   <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
-    <t>AZURA</t>
-  </si>
-  <si>
-    <t>FERNANDA</t>
-  </si>
-  <si>
-    <t>VANNYA</t>
-  </si>
-  <si>
-    <t>FERNANDA MARGARITA</t>
-  </si>
-  <si>
-    <t>ANA SHECIT</t>
-  </si>
-  <si>
-    <t>KEVIN ALEXIS</t>
-  </si>
-  <si>
-    <t>LUZ ALONDRA</t>
-  </si>
-  <si>
-    <t>JOSAVIA ARIDAI</t>
-  </si>
-  <si>
-    <t>CRHIS AMINADAB</t>
-  </si>
-  <si>
-    <t>AMALIA PAULINA</t>
-  </si>
-  <si>
-    <t>KARLOS ARATH</t>
-  </si>
-  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>JARET</t>
-  </si>
-  <si>
-    <t>MARIA ANGELES</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>ARACELI</t>
-  </si>
-  <si>
     <t>SERGIO</t>
   </si>
   <si>
-    <t>BRENDA</t>
-  </si>
-  <si>
-    <t>LUISA MARIA</t>
-  </si>
-  <si>
-    <t>JACQUELINE</t>
-  </si>
-  <si>
-    <t>LILIAN</t>
-  </si>
-  <si>
-    <t>JULIO ANTONIO</t>
-  </si>
-  <si>
-    <t>ATZIN LUCERO</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
     <t>ADAMARI</t>
   </si>
   <si>
@@ -552,40 +347,16 @@
     <t>JULISSA MICHELLE</t>
   </si>
   <si>
-    <t>NOEMI DEL ROCIO</t>
-  </si>
-  <si>
-    <t>NATHALI</t>
-  </si>
-  <si>
-    <t>AILYN</t>
-  </si>
-  <si>
-    <t>HAZEL</t>
-  </si>
-  <si>
-    <t>KAREN ARLET</t>
-  </si>
-  <si>
     <t>KAREN</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>JUAN EMANUEL</t>
-  </si>
-  <si>
-    <t>BRENDA JANELY</t>
-  </si>
-  <si>
-    <t>AXEL GAEL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -638,11 +409,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1083,7 +855,7 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -1119,7 +891,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U4">
         <v>8</v>
@@ -1160,7 +932,7 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1196,7 +968,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -1237,7 +1009,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1314,7 +1086,7 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1391,7 +1163,7 @@
         <v>5</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1468,7 +1240,7 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1545,7 +1317,7 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1581,7 +1353,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>7</v>
@@ -1622,7 +1394,7 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1699,7 +1471,7 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1776,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1853,7 +1625,7 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1889,7 +1661,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>6</v>
@@ -1930,7 +1702,7 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -2007,7 +1779,7 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -2084,7 +1856,7 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2120,7 +1892,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U17">
         <v>6</v>
@@ -2161,7 +1933,7 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2197,7 +1969,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>9</v>
@@ -2238,7 +2010,7 @@
         <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2315,7 +2087,7 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2392,7 +2164,7 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2428,7 +2200,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -2469,7 +2241,7 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2546,7 +2318,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2623,7 +2395,7 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2659,7 +2431,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>6</v>
@@ -2700,7 +2472,7 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2736,7 +2508,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U25">
         <v>10</v>
@@ -2774,7 +2546,7 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2842,7 +2614,7 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -2919,7 +2691,7 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -3025,7 +2797,7 @@
         <v>7</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -3061,7 +2833,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U30">
         <v>9</v>
@@ -3102,7 +2874,7 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3138,7 +2910,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U31">
         <v>6</v>
@@ -3179,7 +2951,7 @@
         <v>7</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3215,7 +2987,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U32">
         <v>6</v>
@@ -3256,7 +3028,7 @@
         <v>6</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3292,7 +3064,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>7</v>
@@ -3333,7 +3105,7 @@
         <v>6</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3410,7 +3182,7 @@
         <v>6</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -3487,7 +3259,7 @@
         <v>6</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I36">
         <v>-1</v>
@@ -3564,7 +3336,7 @@
         <v>5</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>-1</v>
@@ -3600,7 +3372,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U37">
         <v>7</v>
@@ -3641,7 +3413,7 @@
         <v>6</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -3718,7 +3490,7 @@
         <v>6</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I39">
         <v>-1</v>
@@ -3795,7 +3567,7 @@
         <v>9</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -3831,7 +3603,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U40">
         <v>10</v>
@@ -3872,7 +3644,7 @@
         <v>7</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I41">
         <v>-1</v>
@@ -3949,7 +3721,7 @@
         <v>8</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I42">
         <v>-1</v>
@@ -3985,7 +3757,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U42">
         <v>7</v>
@@ -4026,7 +3798,7 @@
         <v>6</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I43">
         <v>-1</v>
@@ -4103,7 +3875,7 @@
         <v>5</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I44">
         <v>-1</v>
@@ -4139,7 +3911,7 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U44">
         <v>8</v>
@@ -4180,7 +3952,7 @@
         <v>6</v>
       </c>
       <c r="H45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -4367,7 +4139,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4426,7 +4198,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4485,7 +4257,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4544,7 +4316,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4603,7 +4375,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4662,7 +4434,7 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -4721,7 +4493,7 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -4780,7 +4552,7 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -4839,7 +4611,7 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -4898,7 +4670,7 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -4957,7 +4729,7 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -5016,7 +4788,7 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -5075,7 +4847,7 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -5134,7 +4906,7 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -5193,7 +4965,7 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -5252,7 +5024,7 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -5311,7 +5083,7 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -5370,7 +5142,7 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -5429,7 +5201,7 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -5488,7 +5260,7 @@
         <v>100</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -5547,7 +5319,7 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -5606,7 +5378,7 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -5662,7 +5434,7 @@
         <v>100</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -5715,7 +5487,7 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -5774,7 +5546,7 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -5856,7 +5628,7 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -5915,7 +5687,7 @@
         <v>100</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5974,7 +5746,7 @@
         <v>100</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -6033,7 +5805,7 @@
         <v>100</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -6092,7 +5864,7 @@
         <v>100</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -6151,7 +5923,7 @@
         <v>100</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -6210,7 +5982,7 @@
         <v>100</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -6269,7 +6041,7 @@
         <v>100</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -6328,7 +6100,7 @@
         <v>100</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -6387,7 +6159,7 @@
         <v>100</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -6446,7 +6218,7 @@
         <v>100</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -6505,7 +6277,7 @@
         <v>100</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -6564,7 +6336,7 @@
         <v>100</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -6623,7 +6395,7 @@
         <v>100</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -6682,7 +6454,7 @@
         <v>100</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -6741,7 +6513,7 @@
         <v>100</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -6793,6 +6565,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -6829,7 +6603,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
@@ -6838,30 +6612,30 @@
         <v>41</v>
       </c>
       <c r="D2">
+        <v>19</v>
+      </c>
+      <c r="E2">
         <v>22</v>
       </c>
-      <c r="E2">
-        <v>19</v>
-      </c>
-      <c r="F2">
-        <v>53.66</v>
-      </c>
-      <c r="G2">
-        <v>46.34</v>
+      <c r="F2" s="2">
+        <v>46.3</v>
+      </c>
+      <c r="G2" s="2">
+        <v>53.7</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -6870,24 +6644,24 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>17</v>
-      </c>
-      <c r="F3">
-        <v>58.54</v>
-      </c>
-      <c r="G3">
-        <v>41.46</v>
+        <v>19</v>
+      </c>
+      <c r="F3" s="2">
+        <v>53.7</v>
+      </c>
+      <c r="G3" s="2">
+        <v>46.3</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6907,11 +6681,11 @@
       <c r="E4">
         <v>13</v>
       </c>
-      <c r="F4">
-        <v>69.05</v>
-      </c>
-      <c r="G4">
-        <v>30.95</v>
+      <c r="F4" s="2">
+        <v>69</v>
+      </c>
+      <c r="G4" s="2">
+        <v>31</v>
       </c>
       <c r="H4">
         <v>6.9</v>
@@ -6919,7 +6693,7 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6939,11 +6713,11 @@
       <c r="E5">
         <v>11</v>
       </c>
-      <c r="F5">
-        <v>73.81</v>
-      </c>
-      <c r="G5">
-        <v>26.19</v>
+      <c r="F5" s="2">
+        <v>73.8</v>
+      </c>
+      <c r="G5" s="2">
+        <v>26.2</v>
       </c>
       <c r="H5">
         <v>6.7</v>
@@ -6951,7 +6725,7 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6971,10 +6745,10 @@
       <c r="E6">
         <v>8</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>80</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="2">
         <v>20</v>
       </c>
       <c r="H6">
@@ -6983,7 +6757,7 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7003,11 +6777,11 @@
       <c r="E7">
         <v>3</v>
       </c>
-      <c r="F7">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="G7">
-        <v>7.32</v>
+      <c r="F7" s="2">
+        <v>92.7</v>
+      </c>
+      <c r="G7" s="2">
+        <v>7.3</v>
       </c>
       <c r="H7">
         <v>7</v>
@@ -7015,7 +6789,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7060,751 +6834,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>22330061460173</v>
-      </c>
-      <c r="B2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>22330051920231</v>
-      </c>
-      <c r="B3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>22330051920230</v>
-      </c>
-      <c r="B4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>22330051920260</v>
-      </c>
-      <c r="B5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D5" t="s">
-        <v>148</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>22330051920232</v>
-      </c>
-      <c r="B6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>22330051920233</v>
-      </c>
-      <c r="B7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D7" t="s">
-        <v>150</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>22330051920234</v>
-      </c>
-      <c r="B8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" t="s">
-        <v>121</v>
-      </c>
-      <c r="D8" t="s">
-        <v>151</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>22330051920236</v>
-      </c>
-      <c r="B9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" t="s">
-        <v>122</v>
-      </c>
-      <c r="D9" t="s">
-        <v>152</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>22330051920237</v>
-      </c>
-      <c r="B10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" t="s">
-        <v>123</v>
-      </c>
-      <c r="D10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>22330051920238</v>
-      </c>
-      <c r="B11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" t="s">
-        <v>124</v>
-      </c>
-      <c r="D11" t="s">
-        <v>154</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>22330051920239</v>
-      </c>
-      <c r="B12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" t="s">
-        <v>155</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>22330051920240</v>
-      </c>
-      <c r="B13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" t="s">
-        <v>99</v>
-      </c>
-      <c r="D13" t="s">
-        <v>156</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>22330051920422</v>
-      </c>
-      <c r="B14" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" t="s">
-        <v>157</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>22330051920241</v>
-      </c>
-      <c r="B15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" t="s">
-        <v>112</v>
-      </c>
-      <c r="D15" t="s">
-        <v>158</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>22330051920242</v>
-      </c>
-      <c r="B16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" t="s">
-        <v>125</v>
-      </c>
-      <c r="D16" t="s">
-        <v>159</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>22330051920357</v>
-      </c>
-      <c r="B17" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" t="s">
-        <v>126</v>
-      </c>
-      <c r="D17" t="s">
-        <v>160</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>22330051920243</v>
-      </c>
-      <c r="B18" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" t="s">
-        <v>161</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>22330051920245</v>
-      </c>
-      <c r="B19" t="s">
-        <v>92</v>
-      </c>
-      <c r="C19" t="s">
-        <v>127</v>
-      </c>
-      <c r="D19" t="s">
-        <v>162</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>22330051920369</v>
-      </c>
-      <c r="B20" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" t="s">
-        <v>128</v>
-      </c>
-      <c r="D20" t="s">
-        <v>163</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>22330051920318</v>
-      </c>
-      <c r="B21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" t="s">
-        <v>129</v>
-      </c>
-      <c r="D21" t="s">
-        <v>164</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>21330051420317</v>
-      </c>
-      <c r="B22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" t="s">
-        <v>130</v>
-      </c>
-      <c r="D22" t="s">
-        <v>165</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>22330051920319</v>
-      </c>
-      <c r="B23" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" t="s">
-        <v>131</v>
-      </c>
-      <c r="D23" t="s">
-        <v>166</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>22330051920246</v>
-      </c>
-      <c r="B24" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" t="s">
-        <v>132</v>
-      </c>
-      <c r="D24" t="s">
-        <v>167</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>20330051920237</v>
-      </c>
-      <c r="B25" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" t="s">
-        <v>168</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>22330051920249</v>
-      </c>
-      <c r="B26" t="s">
-        <v>99</v>
-      </c>
-      <c r="C26" t="s">
-        <v>124</v>
-      </c>
-      <c r="D26" t="s">
-        <v>169</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>22330051920414</v>
-      </c>
-      <c r="B27" t="s">
-        <v>100</v>
-      </c>
-      <c r="C27" t="s">
-        <v>91</v>
-      </c>
-      <c r="D27" t="s">
-        <v>170</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>22330051920250</v>
-      </c>
-      <c r="B28" t="s">
-        <v>101</v>
-      </c>
-      <c r="C28" t="s">
-        <v>133</v>
-      </c>
-      <c r="D28" t="s">
-        <v>171</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>22330051920251</v>
-      </c>
-      <c r="B29" t="s">
-        <v>102</v>
-      </c>
-      <c r="C29" t="s">
-        <v>134</v>
-      </c>
-      <c r="D29" t="s">
-        <v>172</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>22330051920399</v>
-      </c>
-      <c r="B30" t="s">
-        <v>103</v>
-      </c>
-      <c r="C30" t="s">
-        <v>135</v>
-      </c>
-      <c r="D30" t="s">
-        <v>173</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>22330051920375</v>
-      </c>
-      <c r="B31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C31" t="s">
-        <v>135</v>
-      </c>
-      <c r="D31" t="s">
-        <v>174</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>22330061460548</v>
-      </c>
-      <c r="B32" t="s">
-        <v>105</v>
-      </c>
-      <c r="C32" t="s">
-        <v>136</v>
-      </c>
-      <c r="D32" t="s">
-        <v>175</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>22330051920400</v>
-      </c>
-      <c r="B33" t="s">
-        <v>106</v>
-      </c>
-      <c r="C33" t="s">
-        <v>137</v>
-      </c>
-      <c r="D33" t="s">
-        <v>176</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>22330051920253</v>
-      </c>
-      <c r="B34" t="s">
-        <v>107</v>
-      </c>
-      <c r="C34" t="s">
-        <v>97</v>
-      </c>
-      <c r="D34" t="s">
-        <v>177</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35">
-        <v>22330051920235</v>
-      </c>
-      <c r="B35" t="s">
-        <v>108</v>
-      </c>
-      <c r="C35" t="s">
-        <v>138</v>
-      </c>
-      <c r="D35" t="s">
-        <v>178</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36">
-        <v>22330051920366</v>
-      </c>
-      <c r="B36" t="s">
-        <v>109</v>
-      </c>
-      <c r="C36" t="s">
-        <v>139</v>
-      </c>
-      <c r="D36" t="s">
-        <v>179</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37">
-        <v>22330051920368</v>
-      </c>
-      <c r="B37" t="s">
-        <v>110</v>
-      </c>
-      <c r="C37" t="s">
-        <v>94</v>
-      </c>
-      <c r="D37" t="s">
-        <v>180</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38">
-        <v>22330051920254</v>
-      </c>
-      <c r="B38" t="s">
-        <v>111</v>
-      </c>
-      <c r="C38" t="s">
-        <v>110</v>
-      </c>
-      <c r="D38" t="s">
-        <v>181</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39">
-        <v>22330051920257</v>
-      </c>
-      <c r="B39" t="s">
-        <v>112</v>
-      </c>
-      <c r="C39" t="s">
-        <v>140</v>
-      </c>
-      <c r="D39" t="s">
-        <v>182</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40">
-        <v>22330051920256</v>
-      </c>
-      <c r="B40" t="s">
-        <v>113</v>
-      </c>
-      <c r="C40" t="s">
-        <v>141</v>
-      </c>
-      <c r="D40" t="s">
-        <v>183</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41">
-        <v>22330051920401</v>
-      </c>
-      <c r="B41" t="s">
-        <v>114</v>
-      </c>
-      <c r="C41" t="s">
-        <v>142</v>
-      </c>
-      <c r="D41" t="s">
-        <v>184</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42">
-        <v>22330051920259</v>
-      </c>
-      <c r="B42" t="s">
-        <v>115</v>
-      </c>
-      <c r="C42" t="s">
-        <v>143</v>
-      </c>
-      <c r="D42" t="s">
-        <v>185</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43">
-        <v>22330051920176</v>
-      </c>
-      <c r="B43" t="s">
-        <v>116</v>
-      </c>
-      <c r="C43" t="s">
-        <v>144</v>
-      </c>
-      <c r="D43" t="s">
-        <v>186</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7837,22 +6866,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920230</v>
+        <v>22330051920233</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7860,22 +6889,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920230</v>
+        <v>22330051920233</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>147</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7883,22 +6912,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920233</v>
+        <v>22330051920240</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7906,22 +6935,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920233</v>
+        <v>22330051920240</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7932,13 +6961,13 @@
         <v>20330051920237</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>168</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -7955,13 +6984,13 @@
         <v>20330051920237</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>168</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -7975,22 +7004,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920401</v>
+        <v>22330051920251</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>184</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7998,22 +7027,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920401</v>
+        <v>22330051920251</v>
       </c>
       <c r="B9" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>184</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -8021,19 +7050,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330061460173</v>
+        <v>22330051920401</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
@@ -8044,22 +7073,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920240</v>
+        <v>22330051920401</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>156</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -8067,22 +7096,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920241</v>
+        <v>22330061460173</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -8090,22 +7119,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051420317</v>
+        <v>22330051920241</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>165</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -8113,22 +7142,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920249</v>
+        <v>21330051420317</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>169</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -8136,22 +7165,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920251</v>
+        <v>22330051920375</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>172</v>
+        <v>106</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -8159,22 +7188,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920375</v>
+        <v>22330061460548</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>174</v>
+        <v>107</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -8182,19 +7211,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330061460548</v>
+        <v>22330051920400</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>175</v>
+        <v>108</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
         <v>66</v>
@@ -8205,22 +7234,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920400</v>
+        <v>22330051920257</v>
       </c>
       <c r="B18" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G18">
         <v>5</v>

--- a/grupos/2ALCV - Estadisticos 20222.xlsx
+++ b/grupos/2ALCV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="100">
   <si>
     <t>Materia</t>
   </si>
@@ -221,15 +221,15 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>Flores Ovalle Victor</t>
+  </si>
+  <si>
+    <t>Rivera Serra Alma Lilian</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Rivera Serra Alma Lilian</t>
-  </si>
-  <si>
-    <t>Flores Ovalle Victor</t>
-  </si>
-  <si>
     <t>Medina Tolentino Francisco</t>
   </si>
   <si>
@@ -248,103 +248,73 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>BONILLA</t>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PIÑA</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>APARICIO</t>
-  </si>
-  <si>
-    <t>GAYTAN</t>
-  </si>
-  <si>
     <t>LLANOS</t>
   </si>
   <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>IBAÑEZ</t>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>GROT</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>PULIDO</t>
   </si>
   <si>
     <t>MARQUEZ</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>GROT</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>FERNANDA MARGARITA</t>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>JACQUELINE</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>JULISSA MICHELLE</t>
+  </si>
+  <si>
+    <t>JUAN EMANUEL</t>
   </si>
   <si>
     <t>AMALIA PAULINA</t>
   </si>
   <si>
-    <t>JACQUELINE</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>JUAN EMANUEL</t>
-  </si>
-  <si>
-    <t>LUZ ARELY</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
     <t>SERGIO</t>
-  </si>
-  <si>
-    <t>ADAMARI</t>
-  </si>
-  <si>
-    <t>NORMA ANGELICA</t>
-  </si>
-  <si>
-    <t>JULISSA MICHELLE</t>
   </si>
   <si>
     <t>KAREN</t>
@@ -867,10 +837,10 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -944,10 +914,10 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1021,10 +991,10 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1057,10 +1027,10 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1098,10 +1068,10 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1175,10 +1145,10 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1211,7 +1181,7 @@
         <v>5</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -1252,10 +1222,10 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1291,7 +1261,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1329,10 +1299,10 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1406,10 +1376,10 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1442,10 +1412,10 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1483,10 +1453,10 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1560,10 +1530,10 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1637,10 +1607,10 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1714,10 +1684,10 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1791,10 +1761,10 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1827,7 +1797,7 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -1868,10 +1838,10 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1904,10 +1874,10 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1945,10 +1915,10 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1981,10 +1951,10 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2022,10 +1992,10 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2058,7 +2028,7 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -2099,10 +2069,10 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2135,7 +2105,7 @@
         <v>5</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2176,10 +2146,10 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2212,7 +2182,7 @@
         <v>10</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2253,10 +2223,10 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2292,7 +2262,7 @@
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2330,10 +2300,10 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2369,7 +2339,7 @@
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2407,10 +2377,10 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2484,10 +2454,10 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2520,7 +2490,7 @@
         <v>10</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>9</v>
@@ -2555,10 +2525,10 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2588,7 +2558,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2626,10 +2596,10 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2662,7 +2632,7 @@
         <v>5</v>
       </c>
       <c r="X27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>6</v>
@@ -2703,10 +2673,10 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2739,7 +2709,7 @@
         <v>7</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -2759,7 +2729,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -2809,10 +2779,10 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2886,10 +2856,10 @@
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2925,7 +2895,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2963,10 +2933,10 @@
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -2999,7 +2969,7 @@
         <v>6</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>7</v>
@@ -3040,10 +3010,10 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3079,7 +3049,7 @@
         <v>6</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3117,10 +3087,10 @@
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3153,10 +3123,10 @@
         <v>8</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3194,10 +3164,10 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3230,7 +3200,7 @@
         <v>9</v>
       </c>
       <c r="X35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y35">
         <v>6</v>
@@ -3271,10 +3241,10 @@
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3307,10 +3277,10 @@
         <v>9</v>
       </c>
       <c r="X36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3348,10 +3318,10 @@
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3425,10 +3395,10 @@
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3461,10 +3431,10 @@
         <v>5</v>
       </c>
       <c r="X38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y38">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3502,10 +3472,10 @@
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3541,7 +3511,7 @@
         <v>5</v>
       </c>
       <c r="Y39">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3579,10 +3549,10 @@
         <v>-1</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3615,7 +3585,7 @@
         <v>10</v>
       </c>
       <c r="X40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y40">
         <v>9</v>
@@ -3656,10 +3626,10 @@
         <v>-1</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3692,7 +3662,7 @@
         <v>6</v>
       </c>
       <c r="X41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y41">
         <v>7</v>
@@ -3733,10 +3703,10 @@
         <v>-1</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -3769,7 +3739,7 @@
         <v>7</v>
       </c>
       <c r="X42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y42">
         <v>8</v>
@@ -3810,10 +3780,10 @@
         <v>-1</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -3849,7 +3819,7 @@
         <v>5</v>
       </c>
       <c r="Y43">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -3887,10 +3857,10 @@
         <v>-1</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N44">
         <v>-1</v>
@@ -3923,7 +3893,7 @@
         <v>5</v>
       </c>
       <c r="X44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y44">
         <v>5</v>
@@ -3964,10 +3934,10 @@
         <v>-1</v>
       </c>
       <c r="L45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N45">
         <v>-1</v>
@@ -4003,7 +3973,7 @@
         <v>5</v>
       </c>
       <c r="Y45">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4151,10 +4121,10 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -4210,10 +4180,10 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -4269,10 +4239,10 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -4328,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -4387,10 +4357,10 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -4446,10 +4416,10 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -4505,10 +4475,10 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -4564,10 +4534,10 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -4623,10 +4593,10 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -4682,10 +4652,10 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -4741,10 +4711,10 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4800,10 +4770,10 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4859,10 +4829,10 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4918,10 +4888,10 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4977,10 +4947,10 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -5036,10 +5006,10 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -5095,10 +5065,10 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -5154,10 +5124,10 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -5213,10 +5183,10 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -5272,10 +5242,10 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -5331,10 +5301,10 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -5390,10 +5360,10 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -5443,10 +5413,10 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -5499,10 +5469,10 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -5558,10 +5528,10 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -5640,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -5699,10 +5669,10 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -5758,10 +5728,10 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -5817,10 +5787,10 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -5876,10 +5846,10 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -5935,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -5994,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -6053,10 +6023,10 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -6112,10 +6082,10 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N38">
         <v>0</v>
@@ -6171,10 +6141,10 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N39">
         <v>0</v>
@@ -6230,10 +6200,10 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N40">
         <v>0</v>
@@ -6289,10 +6259,10 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N41">
         <v>0</v>
@@ -6348,10 +6318,10 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N42">
         <v>0</v>
@@ -6407,10 +6377,10 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N43">
         <v>0</v>
@@ -6466,10 +6436,10 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N44">
         <v>0</v>
@@ -6525,10 +6495,10 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N45">
         <v>0</v>
@@ -6635,28 +6605,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2">
-        <v>53.7</v>
+        <v>69</v>
       </c>
       <c r="G3" s="2">
-        <v>46.3</v>
+        <v>31</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6699,28 +6669,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
       </c>
       <c r="C5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5">
         <v>11</v>
       </c>
       <c r="F5" s="2">
-        <v>73.8</v>
+        <v>73.2</v>
       </c>
       <c r="G5" s="2">
-        <v>26.2</v>
+        <v>26.8</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6834,7 +6804,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6866,16 +6836,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920233</v>
+        <v>22330051920369</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6889,22 +6859,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920233</v>
+        <v>22330051920369</v>
       </c>
       <c r="B3" t="s">
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6912,22 +6882,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920240</v>
+        <v>20330051920237</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6935,19 +6905,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920240</v>
+        <v>20330051920237</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>67</v>
@@ -6958,22 +6928,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920237</v>
+        <v>22330051920251</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6981,22 +6951,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920237</v>
+        <v>22330051920251</v>
       </c>
       <c r="B7" t="s">
         <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7004,16 +6974,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920251</v>
+        <v>22330051920400</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -7027,22 +6997,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920251</v>
+        <v>22330051920400</v>
       </c>
       <c r="B9" t="s">
         <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7056,10 +7026,10 @@
         <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -7079,16 +7049,16 @@
         <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7096,22 +7066,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330061460173</v>
+        <v>22330051920240</v>
       </c>
       <c r="B12" t="s">
         <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7119,22 +7089,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920241</v>
+        <v>21330051420317</v>
       </c>
       <c r="B13" t="s">
         <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7142,16 +7112,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051420317</v>
+        <v>22330051920257</v>
       </c>
       <c r="B14" t="s">
         <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -7160,98 +7130,6 @@
         <v>66</v>
       </c>
       <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920375</v>
-      </c>
-      <c r="B15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>67</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330061460548</v>
-      </c>
-      <c r="B16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" t="s">
-        <v>107</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920400</v>
-      </c>
-      <c r="B17" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>66</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920257</v>
-      </c>
-      <c r="B18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ALCV - Estadisticos 20222.xlsx
+++ b/grupos/2ALCV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="103">
   <si>
     <t>Materia</t>
   </si>
@@ -221,12 +221,12 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>Rivera Serra Alma Lilian</t>
+  </si>
+  <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
-    <t>Rivera Serra Alma Lilian</t>
-  </si>
-  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
@@ -248,7 +248,10 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>HUERTA</t>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>MARIANO</t>
@@ -263,16 +266,19 @@
     <t>VALENTE</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>LLANOS</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>VENTURA</t>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
   </si>
   <si>
     <t>ANTONIO</t>
@@ -287,16 +293,19 @@
     <t>PULIDO</t>
   </si>
   <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>NIDIA GABRIELA</t>
+    <t>AZURA</t>
+  </si>
+  <si>
+    <t>AMALIA PAULINA</t>
   </si>
   <si>
     <t>JACQUELINE</t>
@@ -311,10 +320,10 @@
     <t>JUAN EMANUEL</t>
   </si>
   <si>
-    <t>AMALIA PAULINA</t>
-  </si>
-  <si>
     <t>SERGIO</t>
+  </si>
+  <si>
+    <t>NORMA ANGELICA</t>
   </si>
   <si>
     <t>KAREN</t>
@@ -831,10 +840,10 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>6</v>
@@ -867,10 +876,10 @@
         <v>8</v>
       </c>
       <c r="V4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>5</v>
@@ -908,10 +917,10 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>7</v>
@@ -985,10 +994,10 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -1062,10 +1071,10 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>8</v>
@@ -1098,7 +1107,7 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1139,10 +1148,10 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>8</v>
@@ -1175,7 +1184,7 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>5</v>
@@ -1216,10 +1225,10 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -1252,7 +1261,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -1293,10 +1302,10 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>9</v>
@@ -1329,7 +1338,7 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1370,10 +1379,10 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>6</v>
@@ -1406,7 +1415,7 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1447,10 +1456,10 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>5</v>
@@ -1524,10 +1533,10 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -1601,10 +1610,10 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>8</v>
@@ -1637,7 +1646,7 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1678,10 +1687,10 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -1755,10 +1764,10 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>7</v>
@@ -1791,7 +1800,7 @@
         <v>8</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>5</v>
@@ -1832,10 +1841,10 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>8</v>
@@ -1868,7 +1877,7 @@
         <v>6</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>6</v>
@@ -1909,10 +1918,10 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>9</v>
@@ -1945,7 +1954,7 @@
         <v>9</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -1986,10 +1995,10 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>5</v>
@@ -2063,10 +2072,10 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>5</v>
@@ -2140,10 +2149,10 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -2176,7 +2185,7 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -2217,10 +2226,10 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -2253,7 +2262,7 @@
         <v>7</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>9</v>
@@ -2294,10 +2303,10 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>6</v>
@@ -2333,7 +2342,7 @@
         <v>6</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>5</v>
@@ -2371,10 +2380,10 @@
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>6</v>
@@ -2448,10 +2457,10 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -2484,7 +2493,7 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2522,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>9</v>
@@ -2590,10 +2599,10 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>9</v>
@@ -2667,10 +2676,10 @@
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>7</v>
@@ -2726,7 +2735,7 @@
         <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>5</v>
@@ -2773,10 +2782,10 @@
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
         <v>9</v>
@@ -2850,10 +2859,10 @@
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
         <v>9</v>
@@ -2927,10 +2936,10 @@
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
         <v>5</v>
@@ -3004,10 +3013,10 @@
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
         <v>6</v>
@@ -3040,7 +3049,7 @@
         <v>7</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3081,10 +3090,10 @@
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>8</v>
@@ -3158,10 +3167,10 @@
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
         <v>7</v>
@@ -3194,7 +3203,7 @@
         <v>8</v>
       </c>
       <c r="V35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W35">
         <v>9</v>
@@ -3235,10 +3244,10 @@
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
         <v>10</v>
@@ -3312,10 +3321,10 @@
         <v>-1</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L37">
         <v>5</v>
@@ -3389,10 +3398,10 @@
         <v>-1</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L38">
         <v>8</v>
@@ -3425,7 +3434,7 @@
         <v>5</v>
       </c>
       <c r="V38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W38">
         <v>5</v>
@@ -3466,10 +3475,10 @@
         <v>-1</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L39">
         <v>5</v>
@@ -3543,10 +3552,10 @@
         <v>-1</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L40">
         <v>10</v>
@@ -3620,10 +3629,10 @@
         <v>-1</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L41">
         <v>8</v>
@@ -3656,7 +3665,7 @@
         <v>9</v>
       </c>
       <c r="V41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W41">
         <v>6</v>
@@ -3697,10 +3706,10 @@
         <v>-1</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L42">
         <v>7</v>
@@ -3774,10 +3783,10 @@
         <v>-1</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L43">
         <v>5</v>
@@ -3851,10 +3860,10 @@
         <v>-1</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L44">
         <v>7</v>
@@ -3928,10 +3937,10 @@
         <v>-1</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L45">
         <v>5</v>
@@ -3964,7 +3973,7 @@
         <v>6</v>
       </c>
       <c r="V45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W45">
         <v>5</v>
@@ -4115,10 +4124,10 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -4174,10 +4183,10 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L5">
         <v>100</v>
@@ -4233,10 +4242,10 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -4292,10 +4301,10 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L7">
         <v>95</v>
@@ -4351,10 +4360,10 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -4410,10 +4419,10 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L9">
         <v>80</v>
@@ -4469,10 +4478,10 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L10">
         <v>95</v>
@@ -4528,10 +4537,10 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -4590,7 +4599,7 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L12">
         <v>90</v>
@@ -4649,7 +4658,7 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -4705,10 +4714,10 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -4764,10 +4773,10 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L15">
         <v>80</v>
@@ -4823,10 +4832,10 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L16">
         <v>80</v>
@@ -4882,10 +4891,10 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L17">
         <v>85</v>
@@ -4941,10 +4950,10 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -5000,10 +5009,10 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -5059,10 +5068,10 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -5118,10 +5127,10 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -5177,10 +5186,10 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -5236,10 +5245,10 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L23">
         <v>90</v>
@@ -5295,10 +5304,10 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -5354,10 +5363,10 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L25">
         <v>100</v>
@@ -5410,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L26">
         <v>80</v>
@@ -5463,10 +5472,10 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L27">
         <v>90</v>
@@ -5522,10 +5531,10 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -5563,7 +5572,7 @@
         <v>83.3</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -5604,10 +5613,10 @@
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -5663,10 +5672,10 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L31">
         <v>95</v>
@@ -5722,10 +5731,10 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L32">
         <v>95</v>
@@ -5781,10 +5790,10 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L33">
         <v>100</v>
@@ -5840,10 +5849,10 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L34">
         <v>100</v>
@@ -5899,10 +5908,10 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L35">
         <v>100</v>
@@ -5958,10 +5967,10 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L36">
         <v>100</v>
@@ -6017,10 +6026,10 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L37">
         <v>100</v>
@@ -6076,10 +6085,10 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L38">
         <v>100</v>
@@ -6135,10 +6144,10 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L39">
         <v>100</v>
@@ -6194,10 +6203,10 @@
         <v>0</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L40">
         <v>100</v>
@@ -6253,10 +6262,10 @@
         <v>0</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L41">
         <v>100</v>
@@ -6312,10 +6321,10 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L42">
         <v>100</v>
@@ -6371,10 +6380,10 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L43">
         <v>100</v>
@@ -6430,10 +6439,10 @@
         <v>0</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L44">
         <v>95</v>
@@ -6489,10 +6498,10 @@
         <v>0</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L45">
         <v>100</v>
@@ -6605,7 +6614,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -6614,19 +6623,19 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>69</v>
+        <v>66.7</v>
       </c>
       <c r="G3" s="2">
-        <v>31</v>
+        <v>33.3</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6637,7 +6646,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -6658,7 +6667,7 @@
         <v>31</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6710,19 +6719,19 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="2">
-        <v>80</v>
+        <v>77.5</v>
       </c>
       <c r="G6" s="2">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6804,7 +6813,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6836,16 +6845,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920369</v>
+        <v>22330051920230</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6859,16 +6868,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920369</v>
+        <v>22330051920230</v>
       </c>
       <c r="B3" t="s">
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -6882,22 +6891,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920237</v>
+        <v>22330051920240</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6905,22 +6914,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920237</v>
+        <v>22330051920240</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6928,22 +6937,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920251</v>
+        <v>20330051920237</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6951,22 +6960,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920251</v>
+        <v>20330051920237</v>
       </c>
       <c r="B7" t="s">
         <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6974,16 +6983,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920400</v>
+        <v>22330051920251</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -6997,22 +7006,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920400</v>
+        <v>22330051920251</v>
       </c>
       <c r="B9" t="s">
         <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7020,16 +7029,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920401</v>
+        <v>22330051920400</v>
       </c>
       <c r="B10" t="s">
         <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -7043,22 +7052,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920401</v>
+        <v>22330051920400</v>
       </c>
       <c r="B11" t="s">
         <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7066,16 +7075,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920240</v>
+        <v>22330051920401</v>
       </c>
       <c r="B12" t="s">
         <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -7089,22 +7098,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051420317</v>
+        <v>22330051920401</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
         <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7112,16 +7121,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920257</v>
+        <v>21330051420317</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
         <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -7130,6 +7139,52 @@
         <v>66</v>
       </c>
       <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330061460548</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920257</v>
+      </c>
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ALCV - Estadisticos 20222.xlsx
+++ b/grupos/2ALCV - Estadisticos 20222.xlsx
@@ -837,7 +837,7 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>7</v>
@@ -873,7 +873,7 @@
         <v>5</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>6</v>
@@ -914,7 +914,7 @@
         <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -950,7 +950,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -991,7 +991,7 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -1027,7 +1027,7 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -1068,7 +1068,7 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1104,7 +1104,7 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1145,7 +1145,7 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>8</v>
@@ -1222,7 +1222,7 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <v>5</v>
@@ -1258,7 +1258,7 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>5</v>
@@ -1299,7 +1299,7 @@
         <v>5</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>7</v>
@@ -1335,7 +1335,7 @@
         <v>7</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -1376,7 +1376,7 @@
         <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>9</v>
@@ -1412,7 +1412,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1453,7 +1453,7 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -1530,7 +1530,7 @@
         <v>5</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -1566,7 +1566,7 @@
         <v>5</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -1607,7 +1607,7 @@
         <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>10</v>
@@ -1643,7 +1643,7 @@
         <v>8</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1684,7 +1684,7 @@
         <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>5</v>
@@ -1761,7 +1761,7 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>7</v>
@@ -1797,7 +1797,7 @@
         <v>5</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1838,7 +1838,7 @@
         <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>5</v>
@@ -1874,7 +1874,7 @@
         <v>5</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -1915,7 +1915,7 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>10</v>
@@ -1951,7 +1951,7 @@
         <v>8</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>10</v>
@@ -1992,7 +1992,7 @@
         <v>5</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>6</v>
@@ -2028,7 +2028,7 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>7</v>
@@ -2069,7 +2069,7 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>6</v>
@@ -2105,7 +2105,7 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2146,7 +2146,7 @@
         <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
         <v>9</v>
@@ -2182,7 +2182,7 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -2223,7 +2223,7 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>10</v>
@@ -2259,7 +2259,7 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -2300,7 +2300,7 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
         <v>6</v>
@@ -2377,7 +2377,7 @@
         <v>5</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>6</v>
@@ -2413,7 +2413,7 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>6</v>
@@ -2454,7 +2454,7 @@
         <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>9</v>
@@ -2528,7 +2528,7 @@
         <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
         <v>7</v>
@@ -2558,7 +2558,7 @@
         <v>5</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -2596,7 +2596,7 @@
         <v>5</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>7</v>
@@ -2673,7 +2673,7 @@
         <v>6</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
         <v>7</v>
@@ -2709,7 +2709,7 @@
         <v>6</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>8</v>
@@ -2779,7 +2779,7 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
         <v>10</v>
@@ -2856,7 +2856,7 @@
         <v>6</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
         <v>7</v>
@@ -2892,7 +2892,7 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>7</v>
@@ -2933,7 +2933,7 @@
         <v>5</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J32">
         <v>5</v>
@@ -2969,7 +2969,7 @@
         <v>5</v>
       </c>
       <c r="U32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V32">
         <v>5</v>
@@ -3010,7 +3010,7 @@
         <v>5</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J33">
         <v>7</v>
@@ -3046,7 +3046,7 @@
         <v>7</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V33">
         <v>7</v>
@@ -3087,7 +3087,7 @@
         <v>7</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J34">
         <v>8</v>
@@ -3123,7 +3123,7 @@
         <v>7</v>
       </c>
       <c r="U34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V34">
         <v>8</v>
@@ -3164,7 +3164,7 @@
         <v>6</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
         <v>5</v>
@@ -3200,7 +3200,7 @@
         <v>6</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>5</v>
@@ -3241,7 +3241,7 @@
         <v>5</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
         <v>9</v>
@@ -3318,7 +3318,7 @@
         <v>5</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J37">
         <v>6</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J38">
         <v>7</v>
@@ -3472,7 +3472,7 @@
         <v>6</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J39">
         <v>10</v>
@@ -3508,7 +3508,7 @@
         <v>5</v>
       </c>
       <c r="U39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V39">
         <v>10</v>
@@ -3549,7 +3549,7 @@
         <v>10</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J40">
         <v>8</v>
@@ -3626,7 +3626,7 @@
         <v>6</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J41">
         <v>7</v>
@@ -3703,7 +3703,7 @@
         <v>5</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J42">
         <v>6</v>
@@ -3739,7 +3739,7 @@
         <v>5</v>
       </c>
       <c r="U42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V42">
         <v>6</v>
@@ -3780,7 +3780,7 @@
         <v>5</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J43">
         <v>8</v>
@@ -3857,7 +3857,7 @@
         <v>5</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J44">
         <v>6</v>
@@ -3893,7 +3893,7 @@
         <v>5</v>
       </c>
       <c r="U44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V44">
         <v>5</v>
@@ -3934,7 +3934,7 @@
         <v>5</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J45">
         <v>5</v>
@@ -3970,7 +3970,7 @@
         <v>5</v>
       </c>
       <c r="U45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V45">
         <v>5</v>
@@ -4121,7 +4121,7 @@
         <v>70</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>85</v>
@@ -4180,7 +4180,7 @@
         <v>90</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -4239,7 +4239,7 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -4298,7 +4298,7 @@
         <v>90</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7">
         <v>95</v>
@@ -4357,7 +4357,7 @@
         <v>90</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8">
         <v>90</v>
@@ -4416,7 +4416,7 @@
         <v>70</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9">
         <v>85</v>
@@ -4475,7 +4475,7 @@
         <v>70</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10">
         <v>85</v>
@@ -4534,7 +4534,7 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
         <v>90</v>
@@ -4593,7 +4593,7 @@
         <v>50</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -4652,7 +4652,7 @@
         <v>50</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -4711,7 +4711,7 @@
         <v>90</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -4770,7 +4770,7 @@
         <v>50</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15">
         <v>90</v>
@@ -4829,7 +4829,7 @@
         <v>50</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16">
         <v>90</v>
@@ -4888,7 +4888,7 @@
         <v>50</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17">
         <v>75</v>
@@ -4947,7 +4947,7 @@
         <v>80</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18">
         <v>100</v>
@@ -5006,7 +5006,7 @@
         <v>90</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19">
         <v>90</v>
@@ -5065,7 +5065,7 @@
         <v>80</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20">
         <v>90</v>
@@ -5124,7 +5124,7 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J21">
         <v>90</v>
@@ -5183,7 +5183,7 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22">
         <v>100</v>
@@ -5242,7 +5242,7 @@
         <v>50</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23">
         <v>85</v>
@@ -5301,7 +5301,7 @@
         <v>70</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24">
         <v>85</v>
@@ -5360,7 +5360,7 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25">
         <v>100</v>
@@ -5416,7 +5416,7 @@
         <v>50</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K26">
         <v>104</v>
@@ -5469,7 +5469,7 @@
         <v>70</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27">
         <v>85</v>
@@ -5528,7 +5528,7 @@
         <v>90</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J28">
         <v>90</v>
@@ -5610,7 +5610,7 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -5669,7 +5669,7 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31">
         <v>95</v>
@@ -5728,7 +5728,7 @@
         <v>70</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32">
         <v>90</v>
@@ -5787,7 +5787,7 @@
         <v>90</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33">
         <v>95</v>
@@ -5846,7 +5846,7 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J34">
         <v>100</v>
@@ -5905,7 +5905,7 @@
         <v>80</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J35">
         <v>100</v>
@@ -5964,7 +5964,7 @@
         <v>70</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J36">
         <v>100</v>
@@ -6023,7 +6023,7 @@
         <v>70</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J37">
         <v>90</v>
@@ -6082,7 +6082,7 @@
         <v>70</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J38">
         <v>80</v>
@@ -6141,7 +6141,7 @@
         <v>100</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J39">
         <v>100</v>
@@ -6200,7 +6200,7 @@
         <v>100</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J40">
         <v>95</v>
@@ -6259,7 +6259,7 @@
         <v>90</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J41">
         <v>100</v>
@@ -6318,7 +6318,7 @@
         <v>70</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J42">
         <v>95</v>
@@ -6377,7 +6377,7 @@
         <v>70</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J43">
         <v>100</v>
@@ -6436,7 +6436,7 @@
         <v>70</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J44">
         <v>85</v>
@@ -6495,7 +6495,7 @@
         <v>50</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J45">
         <v>75</v>
@@ -6763,7 +6763,7 @@
         <v>7.3</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/2ALCV - Estadisticos 20222.xlsx
+++ b/grupos/2ALCV - Estadisticos 20222.xlsx
@@ -4109,7 +4109,7 @@
         <v>75</v>
       </c>
       <c r="E4">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>90</v>
@@ -4118,40 +4118,40 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>70</v>
+        <v>77.5</v>
       </c>
       <c r="I4">
         <v>100</v>
       </c>
       <c r="J4">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K4">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M4">
         <v>100</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -4168,7 +4168,7 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>100</v>
@@ -4177,7 +4177,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I5">
         <v>100</v>
@@ -4186,7 +4186,7 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>100</v>
@@ -4195,22 +4195,22 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -4227,7 +4227,7 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -4245,7 +4245,7 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -4254,22 +4254,22 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -4286,7 +4286,7 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>95</v>
@@ -4295,16 +4295,16 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I7">
         <v>100</v>
       </c>
       <c r="J7">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K7">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>95</v>
@@ -4313,22 +4313,22 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -4345,7 +4345,7 @@
         <v>90</v>
       </c>
       <c r="E8">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>85</v>
@@ -4354,7 +4354,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="I8">
         <v>100</v>
@@ -4363,31 +4363,31 @@
         <v>90</v>
       </c>
       <c r="K8">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="M8">
         <v>100</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4404,7 +4404,7 @@
         <v>75</v>
       </c>
       <c r="E9">
-        <v>96</v>
+        <v>92.3</v>
       </c>
       <c r="F9">
         <v>70</v>
@@ -4419,34 +4419,34 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K9">
-        <v>104</v>
+        <v>96.2</v>
       </c>
       <c r="L9">
+        <v>75</v>
+      </c>
+      <c r="M9">
+        <v>100</v>
+      </c>
+      <c r="N9">
+        <v>70</v>
+      </c>
+      <c r="O9">
+        <v>100</v>
+      </c>
+      <c r="P9">
         <v>80</v>
       </c>
-      <c r="M9">
-        <v>100</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
       <c r="Q9">
-        <v>0</v>
+        <v>96.2</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -4463,7 +4463,7 @@
         <v>85</v>
       </c>
       <c r="E10">
-        <v>96</v>
+        <v>92.3</v>
       </c>
       <c r="F10">
         <v>100</v>
@@ -4472,7 +4472,7 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="I10">
         <v>100</v>
@@ -4481,31 +4481,31 @@
         <v>85</v>
       </c>
       <c r="K10">
-        <v>104</v>
+        <v>96.2</v>
       </c>
       <c r="L10">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M10">
         <v>100</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>96.2</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4522,7 +4522,7 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F11">
         <v>95</v>
@@ -4537,34 +4537,34 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K11">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M11">
         <v>100</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4581,7 +4581,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>80</v>
@@ -4590,40 +4590,40 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>76.7</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L12">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M12">
         <v>100</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="P12">
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4640,7 +4640,7 @@
         <v>60</v>
       </c>
       <c r="E13">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F13">
         <v>90</v>
@@ -4649,40 +4649,40 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="I13">
         <v>100</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K13">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M13">
         <v>100</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4699,7 +4699,7 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>100</v>
@@ -4708,7 +4708,7 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I14">
         <v>100</v>
@@ -4717,7 +4717,7 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -4726,22 +4726,22 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4758,7 +4758,7 @@
         <v>50</v>
       </c>
       <c r="E15">
-        <v>96</v>
+        <v>92.3</v>
       </c>
       <c r="F15">
         <v>80</v>
@@ -4767,16 +4767,16 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="J15">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="K15">
-        <v>104</v>
+        <v>96.2</v>
       </c>
       <c r="L15">
         <v>80</v>
@@ -4785,22 +4785,22 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>96.2</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4817,7 +4817,7 @@
         <v>90</v>
       </c>
       <c r="E16">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>95</v>
@@ -4826,7 +4826,7 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -4835,31 +4835,31 @@
         <v>90</v>
       </c>
       <c r="K16">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L16">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="M16">
         <v>100</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4876,7 +4876,7 @@
         <v>85</v>
       </c>
       <c r="E17">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>90</v>
@@ -4885,40 +4885,40 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>50</v>
+        <v>67.5</v>
       </c>
       <c r="I17">
         <v>100</v>
       </c>
       <c r="J17">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K17">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L17">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="M17">
         <v>100</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4935,7 +4935,7 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>100</v>
@@ -4944,7 +4944,7 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="I18">
         <v>100</v>
@@ -4953,7 +4953,7 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -4962,22 +4962,22 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4994,7 +4994,7 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F19">
         <v>100</v>
@@ -5003,16 +5003,16 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I19">
         <v>100</v>
       </c>
       <c r="J19">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K19">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -5021,22 +5021,22 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -5053,7 +5053,7 @@
         <v>95</v>
       </c>
       <c r="E20">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>100</v>
@@ -5062,16 +5062,16 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I20">
         <v>100</v>
       </c>
       <c r="J20">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="K20">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -5080,22 +5080,22 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -5112,7 +5112,7 @@
         <v>100</v>
       </c>
       <c r="E21">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F21">
         <v>100</v>
@@ -5127,10 +5127,10 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K21">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -5139,22 +5139,22 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -5171,7 +5171,7 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>100</v>
@@ -5189,7 +5189,7 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -5198,22 +5198,22 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -5230,7 +5230,7 @@
         <v>100</v>
       </c>
       <c r="E23">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F23">
         <v>90</v>
@@ -5239,16 +5239,16 @@
         <v>100</v>
       </c>
       <c r="H23">
-        <v>50</v>
+        <v>67.5</v>
       </c>
       <c r="I23">
         <v>100</v>
       </c>
       <c r="J23">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="K23">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L23">
         <v>90</v>
@@ -5257,22 +5257,22 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5289,7 +5289,7 @@
         <v>85</v>
       </c>
       <c r="E24">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <v>90</v>
@@ -5298,7 +5298,7 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>70</v>
+        <v>77.5</v>
       </c>
       <c r="I24">
         <v>100</v>
@@ -5307,31 +5307,31 @@
         <v>85</v>
       </c>
       <c r="K24">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M24">
         <v>100</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5348,7 +5348,7 @@
         <v>100</v>
       </c>
       <c r="E25">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>100</v>
@@ -5366,7 +5366,7 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L25">
         <v>100</v>
@@ -5375,22 +5375,22 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -5404,7 +5404,7 @@
         <v>100</v>
       </c>
       <c r="E26">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>100</v>
@@ -5413,34 +5413,34 @@
         <v>100</v>
       </c>
       <c r="H26">
-        <v>50</v>
+        <v>67.5</v>
       </c>
       <c r="I26">
         <v>100</v>
       </c>
       <c r="K26">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L26">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M26">
         <v>100</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5457,7 +5457,7 @@
         <v>80</v>
       </c>
       <c r="E27">
-        <v>88</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="F27">
         <v>90</v>
@@ -5466,16 +5466,16 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>70</v>
+        <v>77.5</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="J27">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="K27">
-        <v>104</v>
+        <v>92.3</v>
       </c>
       <c r="L27">
         <v>90</v>
@@ -5484,22 +5484,22 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5516,7 +5516,7 @@
         <v>90</v>
       </c>
       <c r="E28">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F28">
         <v>100</v>
@@ -5525,7 +5525,7 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I28">
         <v>100</v>
@@ -5534,7 +5534,7 @@
         <v>90</v>
       </c>
       <c r="K28">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -5543,22 +5543,22 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5566,22 +5566,22 @@
         <v>37</v>
       </c>
       <c r="E29">
-        <v>88</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G29">
         <v>83.3</v>
       </c>
       <c r="K29">
-        <v>40</v>
+        <v>61.5</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>61.5</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5598,7 +5598,7 @@
         <v>100</v>
       </c>
       <c r="E30">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F30">
         <v>90</v>
@@ -5607,7 +5607,7 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I30">
         <v>100</v>
@@ -5616,31 +5616,31 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L30">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M30">
         <v>100</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5657,7 +5657,7 @@
         <v>100</v>
       </c>
       <c r="E31">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F31">
         <v>100</v>
@@ -5666,40 +5666,40 @@
         <v>100</v>
       </c>
       <c r="H31">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I31">
         <v>100</v>
       </c>
       <c r="J31">
+        <v>97.5</v>
+      </c>
+      <c r="K31">
+        <v>100</v>
+      </c>
+      <c r="L31">
+        <v>97.5</v>
+      </c>
+      <c r="M31">
+        <v>100</v>
+      </c>
+      <c r="N31">
         <v>95</v>
       </c>
-      <c r="K31">
-        <v>104</v>
-      </c>
-      <c r="L31">
-        <v>95</v>
-      </c>
-      <c r="M31">
-        <v>100</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
       <c r="O31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5716,7 +5716,7 @@
         <v>70</v>
       </c>
       <c r="E32">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F32">
         <v>100</v>
@@ -5725,40 +5725,40 @@
         <v>100</v>
       </c>
       <c r="H32">
-        <v>70</v>
+        <v>77.5</v>
       </c>
       <c r="I32">
         <v>100</v>
       </c>
       <c r="J32">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K32">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L32">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M32">
         <v>100</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5775,7 +5775,7 @@
         <v>85</v>
       </c>
       <c r="E33">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F33">
         <v>100</v>
@@ -5784,16 +5784,16 @@
         <v>100</v>
       </c>
       <c r="H33">
+        <v>87.5</v>
+      </c>
+      <c r="I33">
+        <v>100</v>
+      </c>
+      <c r="J33">
         <v>90</v>
       </c>
-      <c r="I33">
-        <v>100</v>
-      </c>
-      <c r="J33">
-        <v>95</v>
-      </c>
       <c r="K33">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L33">
         <v>100</v>
@@ -5802,22 +5802,22 @@
         <v>100</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5834,7 +5834,7 @@
         <v>100</v>
       </c>
       <c r="E34">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F34">
         <v>100</v>
@@ -5852,7 +5852,7 @@
         <v>100</v>
       </c>
       <c r="K34">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L34">
         <v>100</v>
@@ -5861,22 +5861,22 @@
         <v>100</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5893,7 +5893,7 @@
         <v>85</v>
       </c>
       <c r="E35">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F35">
         <v>100</v>
@@ -5902,16 +5902,16 @@
         <v>100</v>
       </c>
       <c r="H35">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="I35">
         <v>100</v>
       </c>
       <c r="J35">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="K35">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L35">
         <v>100</v>
@@ -5920,22 +5920,22 @@
         <v>100</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5952,7 +5952,7 @@
         <v>100</v>
       </c>
       <c r="E36">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F36">
         <v>100</v>
@@ -5961,7 +5961,7 @@
         <v>100</v>
       </c>
       <c r="H36">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="I36">
         <v>100</v>
@@ -5970,31 +5970,31 @@
         <v>100</v>
       </c>
       <c r="K36">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L36">
         <v>100</v>
       </c>
       <c r="M36">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -6011,7 +6011,7 @@
         <v>100</v>
       </c>
       <c r="E37">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F37">
         <v>100</v>
@@ -6020,16 +6020,16 @@
         <v>100</v>
       </c>
       <c r="H37">
-        <v>70</v>
+        <v>82.5</v>
       </c>
       <c r="I37">
         <v>100</v>
       </c>
       <c r="J37">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K37">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L37">
         <v>100</v>
@@ -6038,22 +6038,22 @@
         <v>100</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -6070,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F38">
         <v>100</v>
@@ -6079,40 +6079,40 @@
         <v>100</v>
       </c>
       <c r="H38">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="I38">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="J38">
+        <v>40</v>
+      </c>
+      <c r="K38">
+        <v>100</v>
+      </c>
+      <c r="L38">
+        <v>100</v>
+      </c>
+      <c r="M38">
+        <v>100</v>
+      </c>
+      <c r="N38">
         <v>80</v>
       </c>
-      <c r="K38">
-        <v>104</v>
-      </c>
-      <c r="L38">
-        <v>100</v>
-      </c>
-      <c r="M38">
-        <v>100</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
       <c r="O38">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -6129,7 +6129,7 @@
         <v>100</v>
       </c>
       <c r="E39">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F39">
         <v>80</v>
@@ -6138,7 +6138,7 @@
         <v>100</v>
       </c>
       <c r="H39">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I39">
         <v>100</v>
@@ -6147,31 +6147,31 @@
         <v>100</v>
       </c>
       <c r="K39">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L39">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M39">
         <v>100</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -6188,7 +6188,7 @@
         <v>100</v>
       </c>
       <c r="E40">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F40">
         <v>90</v>
@@ -6203,34 +6203,34 @@
         <v>100</v>
       </c>
       <c r="J40">
+        <v>97.5</v>
+      </c>
+      <c r="K40">
+        <v>100</v>
+      </c>
+      <c r="L40">
         <v>95</v>
       </c>
-      <c r="K40">
-        <v>104</v>
-      </c>
-      <c r="L40">
-        <v>100</v>
-      </c>
       <c r="M40">
         <v>100</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -6247,7 +6247,7 @@
         <v>100</v>
       </c>
       <c r="E41">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F41">
         <v>100</v>
@@ -6256,7 +6256,7 @@
         <v>100</v>
       </c>
       <c r="H41">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="I41">
         <v>100</v>
@@ -6265,7 +6265,7 @@
         <v>100</v>
       </c>
       <c r="K41">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L41">
         <v>100</v>
@@ -6274,22 +6274,22 @@
         <v>100</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -6306,7 +6306,7 @@
         <v>80</v>
       </c>
       <c r="E42">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F42">
         <v>90</v>
@@ -6315,40 +6315,40 @@
         <v>100</v>
       </c>
       <c r="H42">
-        <v>70</v>
+        <v>82.5</v>
       </c>
       <c r="I42">
         <v>100</v>
       </c>
       <c r="J42">
+        <v>87.5</v>
+      </c>
+      <c r="K42">
+        <v>100</v>
+      </c>
+      <c r="L42">
         <v>95</v>
       </c>
-      <c r="K42">
-        <v>104</v>
-      </c>
-      <c r="L42">
-        <v>100</v>
-      </c>
       <c r="M42">
         <v>100</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -6365,7 +6365,7 @@
         <v>100</v>
       </c>
       <c r="E43">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F43">
         <v>100</v>
@@ -6374,7 +6374,7 @@
         <v>100</v>
       </c>
       <c r="H43">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="I43">
         <v>100</v>
@@ -6383,7 +6383,7 @@
         <v>100</v>
       </c>
       <c r="K43">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L43">
         <v>100</v>
@@ -6392,22 +6392,22 @@
         <v>100</v>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -6424,7 +6424,7 @@
         <v>75</v>
       </c>
       <c r="E44">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F44">
         <v>100</v>
@@ -6433,40 +6433,40 @@
         <v>100</v>
       </c>
       <c r="H44">
-        <v>70</v>
+        <v>82.5</v>
       </c>
       <c r="I44">
         <v>100</v>
       </c>
       <c r="J44">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K44">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L44">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M44">
         <v>100</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -6483,7 +6483,7 @@
         <v>80</v>
       </c>
       <c r="E45">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F45">
         <v>100</v>
@@ -6492,40 +6492,40 @@
         <v>100</v>
       </c>
       <c r="H45">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="I45">
         <v>100</v>
       </c>
       <c r="J45">
+        <v>77.5</v>
+      </c>
+      <c r="K45">
+        <v>100</v>
+      </c>
+      <c r="L45">
+        <v>100</v>
+      </c>
+      <c r="M45">
+        <v>100</v>
+      </c>
+      <c r="N45">
         <v>75</v>
       </c>
-      <c r="K45">
-        <v>104</v>
-      </c>
-      <c r="L45">
-        <v>100</v>
-      </c>
-      <c r="M45">
-        <v>100</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
       <c r="O45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2ALCV - Estadisticos 20222.xlsx
+++ b/grupos/2ALCV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="109">
   <si>
     <t>Materia</t>
   </si>
@@ -224,18 +224,18 @@
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Francisco</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Francisco</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -251,79 +251,97 @@
     <t>ANGELES</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>MARIANO</t>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LLANOS</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>LLANOS</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
     <t>ROCHA</t>
   </si>
   <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>PULIDO</t>
+  </si>
+  <si>
     <t>MARQUEZ</t>
   </si>
   <si>
-    <t>ANTONIO</t>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
   </si>
   <si>
     <t>GROT</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>AZURA</t>
   </si>
   <si>
+    <t>VANNYA</t>
+  </si>
+  <si>
+    <t>CRHIS AMINADAB</t>
+  </si>
+  <si>
+    <t>JARET</t>
+  </si>
+  <si>
+    <t>JACQUELINE</t>
+  </si>
+  <si>
+    <t>JUAN EMANUEL</t>
+  </si>
+  <si>
     <t>AMALIA PAULINA</t>
   </si>
   <si>
-    <t>JACQUELINE</t>
+    <t>ARACELI</t>
+  </si>
+  <si>
+    <t>SERGIO</t>
   </si>
   <si>
     <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>JULISSA MICHELLE</t>
-  </si>
-  <si>
-    <t>JUAN EMANUEL</t>
-  </si>
-  <si>
-    <t>SERGIO</t>
-  </si>
-  <si>
-    <t>NORMA ANGELICA</t>
   </si>
   <si>
     <t>KAREN</t>
@@ -858,7 +876,7 @@
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -867,7 +885,7 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>5</v>
@@ -935,7 +953,7 @@
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -944,7 +962,7 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -1012,7 +1030,7 @@
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -1021,7 +1039,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -1089,7 +1107,7 @@
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1098,7 +1116,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>6</v>
@@ -1107,7 +1125,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1166,7 +1184,7 @@
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1175,7 +1193,7 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>5</v>
@@ -1193,7 +1211,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1243,7 +1261,7 @@
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1252,7 +1270,7 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>5</v>
@@ -1270,7 +1288,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1320,7 +1338,7 @@
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1329,7 +1347,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -1338,7 +1356,7 @@
         <v>8</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1397,7 +1415,7 @@
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1406,7 +1424,7 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>7</v>
@@ -1415,7 +1433,7 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1424,7 +1442,7 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1474,7 +1492,7 @@
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1483,7 +1501,7 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>5</v>
@@ -1551,7 +1569,7 @@
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1560,7 +1578,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
         <v>5</v>
@@ -1578,7 +1596,7 @@
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1628,7 +1646,7 @@
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1637,7 +1655,7 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>8</v>
@@ -1705,7 +1723,7 @@
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -1714,7 +1732,7 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
         <v>5</v>
@@ -1732,7 +1750,7 @@
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1782,7 +1800,7 @@
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -1791,7 +1809,7 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>5</v>
@@ -1800,7 +1818,7 @@
         <v>9</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>5</v>
@@ -1809,7 +1827,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1859,7 +1877,7 @@
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -1868,7 +1886,7 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>5</v>
@@ -1877,7 +1895,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>6</v>
@@ -1936,7 +1954,7 @@
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -1945,7 +1963,7 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>8</v>
@@ -1963,7 +1981,7 @@
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2013,7 +2031,7 @@
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2022,7 +2040,7 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>5</v>
@@ -2031,7 +2049,7 @@
         <v>7</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2090,7 +2108,7 @@
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2099,7 +2117,7 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>5</v>
@@ -2117,7 +2135,7 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2167,7 +2185,7 @@
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2176,7 +2194,7 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -2244,7 +2262,7 @@
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2253,7 +2271,7 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2262,7 +2280,7 @@
         <v>8</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>9</v>
@@ -2321,7 +2339,7 @@
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2330,7 +2348,7 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
         <v>5</v>
@@ -2339,7 +2357,7 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -2398,7 +2416,7 @@
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2407,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>6</v>
@@ -2416,7 +2434,7 @@
         <v>7</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>6</v>
@@ -2475,7 +2493,7 @@
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2484,7 +2502,7 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
         <v>8</v>
@@ -2552,7 +2570,7 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>5</v>
@@ -2617,7 +2635,7 @@
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -2626,7 +2644,7 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>5</v>
@@ -2644,7 +2662,7 @@
         <v>7</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2694,7 +2712,7 @@
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -2703,7 +2721,7 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>6</v>
@@ -2712,7 +2730,7 @@
         <v>7</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -2744,7 +2762,7 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>5</v>
@@ -2800,7 +2818,7 @@
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -2809,7 +2827,7 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>7</v>
@@ -2877,7 +2895,7 @@
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -2886,7 +2904,7 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>7</v>
@@ -2954,7 +2972,7 @@
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -2963,7 +2981,7 @@
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>5</v>
@@ -2972,7 +2990,7 @@
         <v>7</v>
       </c>
       <c r="V32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>6</v>
@@ -3031,7 +3049,7 @@
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3040,7 +3058,7 @@
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
         <v>7</v>
@@ -3049,7 +3067,7 @@
         <v>8</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3108,7 +3126,7 @@
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -3117,7 +3135,7 @@
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
         <v>7</v>
@@ -3135,7 +3153,7 @@
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3185,7 +3203,7 @@
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -3194,7 +3212,7 @@
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>6</v>
@@ -3203,7 +3221,7 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W35">
         <v>9</v>
@@ -3212,7 +3230,7 @@
         <v>6</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3262,7 +3280,7 @@
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -3271,7 +3289,7 @@
         <v>-1</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T36">
         <v>5</v>
@@ -3280,7 +3298,7 @@
         <v>7</v>
       </c>
       <c r="V36">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W36">
         <v>9</v>
@@ -3339,7 +3357,7 @@
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -3348,7 +3366,7 @@
         <v>-1</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T37">
         <v>5</v>
@@ -3357,7 +3375,7 @@
         <v>7</v>
       </c>
       <c r="V37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W37">
         <v>5</v>
@@ -3366,7 +3384,7 @@
         <v>5</v>
       </c>
       <c r="Y37">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3416,7 +3434,7 @@
         <v>-1</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q38">
         <v>-1</v>
@@ -3425,7 +3443,7 @@
         <v>-1</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T38">
         <v>5</v>
@@ -3434,7 +3452,7 @@
         <v>5</v>
       </c>
       <c r="V38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W38">
         <v>5</v>
@@ -3493,7 +3511,7 @@
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
         <v>-1</v>
@@ -3502,7 +3520,7 @@
         <v>-1</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T39">
         <v>5</v>
@@ -3520,7 +3538,7 @@
         <v>5</v>
       </c>
       <c r="Y39">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3570,7 +3588,7 @@
         <v>-1</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q40">
         <v>-1</v>
@@ -3579,7 +3597,7 @@
         <v>-1</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T40">
         <v>9</v>
@@ -3647,7 +3665,7 @@
         <v>-1</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q41">
         <v>-1</v>
@@ -3656,7 +3674,7 @@
         <v>-1</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T41">
         <v>6</v>
@@ -3665,7 +3683,7 @@
         <v>9</v>
       </c>
       <c r="V41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W41">
         <v>6</v>
@@ -3724,7 +3742,7 @@
         <v>-1</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q42">
         <v>-1</v>
@@ -3733,7 +3751,7 @@
         <v>-1</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T42">
         <v>5</v>
@@ -3801,7 +3819,7 @@
         <v>-1</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q43">
         <v>-1</v>
@@ -3810,7 +3828,7 @@
         <v>-1</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T43">
         <v>5</v>
@@ -3878,7 +3896,7 @@
         <v>-1</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q44">
         <v>-1</v>
@@ -3887,7 +3905,7 @@
         <v>-1</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T44">
         <v>5</v>
@@ -3905,7 +3923,7 @@
         <v>6</v>
       </c>
       <c r="Y44">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -3955,7 +3973,7 @@
         <v>-1</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q45">
         <v>-1</v>
@@ -3964,7 +3982,7 @@
         <v>-1</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T45">
         <v>5</v>
@@ -3973,7 +3991,7 @@
         <v>7</v>
       </c>
       <c r="V45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W45">
         <v>5</v>
@@ -3982,7 +4000,7 @@
         <v>5</v>
       </c>
       <c r="Y45">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4142,7 +4160,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>80</v>
+        <v>81.7</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -4260,7 +4278,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -4319,7 +4337,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>97.5</v>
+        <v>91.7</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -4378,7 +4396,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -4437,7 +4455,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>80</v>
+        <v>81.7</v>
       </c>
       <c r="Q9">
         <v>96.2</v>
@@ -4496,7 +4514,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>85</v>
+        <v>88.3</v>
       </c>
       <c r="Q10">
         <v>96.2</v>
@@ -4555,7 +4573,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -4673,7 +4691,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4791,7 +4809,7 @@
         <v>93.3</v>
       </c>
       <c r="P15">
-        <v>70</v>
+        <v>71.7</v>
       </c>
       <c r="Q15">
         <v>96.2</v>
@@ -4909,7 +4927,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -5027,7 +5045,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>95</v>
+        <v>88.3</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -5036,7 +5054,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>100</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -5086,7 +5104,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>92.5</v>
+        <v>91.7</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -5263,7 +5281,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>92.5</v>
+        <v>88.3</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -5322,7 +5340,7 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>85</v>
+        <v>81.7</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -5490,7 +5508,7 @@
         <v>83.3</v>
       </c>
       <c r="P27">
-        <v>82.5</v>
+        <v>86.7</v>
       </c>
       <c r="Q27">
         <v>92.3</v>
@@ -5549,7 +5567,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -5581,7 +5599,7 @@
         <v>61.5</v>
       </c>
       <c r="S29">
-        <v>41.7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5690,7 +5708,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>97.5</v>
+        <v>95</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -5749,7 +5767,7 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -5926,7 +5944,7 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -5985,7 +6003,7 @@
         <v>100</v>
       </c>
       <c r="P36">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q36">
         <v>100</v>
@@ -5994,7 +6012,7 @@
         <v>100</v>
       </c>
       <c r="S36">
-        <v>87.5</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -6044,7 +6062,7 @@
         <v>100</v>
       </c>
       <c r="P37">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="Q37">
         <v>100</v>
@@ -6103,7 +6121,7 @@
         <v>83.3</v>
       </c>
       <c r="P38">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="Q38">
         <v>100</v>
@@ -6221,7 +6239,7 @@
         <v>100</v>
       </c>
       <c r="P40">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="Q40">
         <v>100</v>
@@ -6280,7 +6298,7 @@
         <v>100</v>
       </c>
       <c r="P41">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="Q41">
         <v>100</v>
@@ -6339,7 +6357,7 @@
         <v>100</v>
       </c>
       <c r="P42">
-        <v>87.5</v>
+        <v>88.3</v>
       </c>
       <c r="Q42">
         <v>100</v>
@@ -6516,7 +6534,7 @@
         <v>100</v>
       </c>
       <c r="P45">
-        <v>77.5</v>
+        <v>81.7</v>
       </c>
       <c r="Q45">
         <v>100</v>
@@ -6646,28 +6664,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
       </c>
       <c r="C4">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" s="2">
-        <v>69</v>
+        <v>73.2</v>
       </c>
       <c r="G4" s="2">
-        <v>31</v>
+        <v>26.8</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6678,25 +6696,25 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
       </c>
       <c r="C5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" s="2">
-        <v>73.2</v>
+        <v>75</v>
       </c>
       <c r="G5" s="2">
-        <v>26.8</v>
+        <v>25</v>
       </c>
       <c r="H5">
         <v>6.9</v>
@@ -6710,28 +6728,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
       </c>
       <c r="C6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>77.5</v>
+        <v>92.7</v>
       </c>
       <c r="G6" s="2">
-        <v>22.5</v>
+        <v>7.3</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6742,28 +6760,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
       </c>
       <c r="C7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>92.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6813,7 +6831,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6851,10 +6869,10 @@
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6874,16 +6892,16 @@
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6891,16 +6909,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920240</v>
+        <v>22330051920232</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -6914,22 +6932,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920240</v>
+        <v>22330051920232</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6937,22 +6955,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920237</v>
+        <v>22330051920239</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6960,22 +6978,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920237</v>
+        <v>22330051920239</v>
       </c>
       <c r="B7" t="s">
         <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6983,16 +7001,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920251</v>
+        <v>22330051920357</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -7006,22 +7024,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920251</v>
+        <v>22330051920357</v>
       </c>
       <c r="B9" t="s">
         <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7029,22 +7047,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920400</v>
+        <v>20330051920237</v>
       </c>
       <c r="B10" t="s">
         <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7052,22 +7070,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920400</v>
+        <v>20330051920237</v>
       </c>
       <c r="B11" t="s">
         <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7081,10 +7099,10 @@
         <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -7104,16 +7122,16 @@
         <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7121,16 +7139,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051420317</v>
+        <v>22330051920240</v>
       </c>
       <c r="B14" t="s">
         <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -7144,22 +7162,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330061460548</v>
+        <v>22330051920318</v>
       </c>
       <c r="B15" t="s">
         <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7167,16 +7185,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920257</v>
+        <v>21330051420317</v>
       </c>
       <c r="B16" t="s">
         <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -7185,6 +7203,52 @@
         <v>66</v>
       </c>
       <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920251</v>
+      </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920257</v>
+      </c>
+      <c r="B18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ALCV - Estadisticos 20222.xlsx
+++ b/grupos/2ALCV - Estadisticos 20222.xlsx
@@ -873,7 +873,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>6</v>
@@ -891,7 +891,7 @@
         <v>5</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>6</v>
@@ -950,7 +950,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
         <v>10</v>
@@ -1027,7 +1027,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>8</v>
@@ -1104,7 +1104,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>5</v>
@@ -1122,7 +1122,7 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>7</v>
@@ -1181,7 +1181,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>8</v>
@@ -1258,7 +1258,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>5</v>
@@ -1276,7 +1276,7 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>5</v>
@@ -1335,7 +1335,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>6</v>
@@ -1412,7 +1412,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>8</v>
@@ -1566,7 +1566,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>5</v>
@@ -1643,7 +1643,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
         <v>10</v>
@@ -1797,7 +1797,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
         <v>6</v>
@@ -1874,7 +1874,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
         <v>7</v>
@@ -1951,7 +1951,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>10</v>
@@ -2028,7 +2028,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>5</v>
@@ -2105,7 +2105,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>6</v>
@@ -2182,7 +2182,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>8</v>
@@ -2259,7 +2259,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>9</v>
@@ -2336,7 +2336,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
         <v>5</v>
@@ -2413,7 +2413,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
         <v>5</v>
@@ -2490,7 +2490,7 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>9</v>
@@ -2561,7 +2561,7 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -2576,7 +2576,7 @@
         <v>5</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -2709,7 +2709,7 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
         <v>6</v>
@@ -2815,7 +2815,7 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>10</v>
@@ -2892,7 +2892,7 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
         <v>7</v>
@@ -2969,7 +2969,7 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
         <v>8</v>
@@ -3046,7 +3046,7 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
         <v>6</v>
@@ -3123,7 +3123,7 @@
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
         <v>8</v>
@@ -3200,7 +3200,7 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
         <v>8</v>
@@ -3218,7 +3218,7 @@
         <v>6</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V35">
         <v>6</v>
@@ -3277,7 +3277,7 @@
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P36">
         <v>5</v>
@@ -3295,7 +3295,7 @@
         <v>5</v>
       </c>
       <c r="U36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V36">
         <v>5</v>
@@ -3354,7 +3354,7 @@
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P37">
         <v>5</v>
@@ -3431,7 +3431,7 @@
         <v>-1</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P38">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>5</v>
       </c>
       <c r="U38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V38">
         <v>5</v>
@@ -3508,7 +3508,7 @@
         <v>-1</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P39">
         <v>10</v>
@@ -3526,7 +3526,7 @@
         <v>5</v>
       </c>
       <c r="U39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V39">
         <v>10</v>
@@ -3585,7 +3585,7 @@
         <v>-1</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P40">
         <v>8</v>
@@ -3662,7 +3662,7 @@
         <v>-1</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P41">
         <v>6</v>
@@ -3739,7 +3739,7 @@
         <v>-1</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P42">
         <v>6</v>
@@ -3816,7 +3816,7 @@
         <v>-1</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P43">
         <v>10</v>
@@ -3893,7 +3893,7 @@
         <v>-1</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P44">
         <v>5</v>
@@ -3911,7 +3911,7 @@
         <v>5</v>
       </c>
       <c r="U44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V44">
         <v>5</v>
@@ -3970,7 +3970,7 @@
         <v>-1</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P45">
         <v>7</v>
@@ -4629,7 +4629,7 @@
         <v>60</v>
       </c>
       <c r="O12">
-        <v>76.7</v>
+        <v>51.1</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>60</v>
       </c>
       <c r="O15">
-        <v>93.3</v>
+        <v>62.2</v>
       </c>
       <c r="P15">
         <v>71.7</v>
@@ -5505,7 +5505,7 @@
         <v>77.5</v>
       </c>
       <c r="O27">
-        <v>83.3</v>
+        <v>55.6</v>
       </c>
       <c r="P27">
         <v>86.7</v>
@@ -6000,7 +6000,7 @@
         <v>85</v>
       </c>
       <c r="O36">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="P36">
         <v>66.7</v>
@@ -6118,7 +6118,7 @@
         <v>80</v>
       </c>
       <c r="O38">
-        <v>83.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P38">
         <v>55</v>
@@ -6749,7 +6749,7 @@
         <v>7.3</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/2ALCV - Estadisticos 20222.xlsx
+++ b/grupos/2ALCV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="114">
   <si>
     <t>Materia</t>
   </si>
@@ -221,21 +221,21 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Francisco</t>
+  </si>
+  <si>
+    <t>Flores Ovalle Victor</t>
+  </si>
+  <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Francisco</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Flores Ovalle Victor</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -248,103 +248,118 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZAVALA</t>
+  </si>
+  <si>
     <t>ANGELES</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
     <t>GAMBOA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARIANO</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
   </si>
   <si>
     <t>VALENTE</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LLANOS</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>DELGADO</t>
   </si>
   <si>
     <t>ROCHA</t>
   </si>
   <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>GROT</t>
   </si>
   <si>
     <t>PULIDO</t>
   </si>
   <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>GROT</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
+    <t>ARACELI</t>
+  </si>
+  <si>
+    <t>JACQUELINE</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
+    <t>BRENDA JANELY</t>
+  </si>
+  <si>
+    <t>AXEL GAEL</t>
   </si>
   <si>
     <t>AZURA</t>
   </si>
   <si>
-    <t>VANNYA</t>
-  </si>
-  <si>
     <t>CRHIS AMINADAB</t>
   </si>
   <si>
-    <t>JARET</t>
-  </si>
-  <si>
-    <t>JACQUELINE</t>
+    <t>AMALIA PAULINA</t>
+  </si>
+  <si>
+    <t>SERGIO</t>
+  </si>
+  <si>
+    <t>LUISA MARIA</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>HAZEL</t>
   </si>
   <si>
     <t>JUAN EMANUEL</t>
-  </si>
-  <si>
-    <t>AMALIA PAULINA</t>
-  </si>
-  <si>
-    <t>ARACELI</t>
-  </si>
-  <si>
-    <t>SERGIO</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>KAREN</t>
   </si>
 </sst>
 </file>
@@ -870,7 +885,7 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
         <v>8</v>
@@ -879,7 +894,7 @@
         <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -888,7 +903,7 @@
         <v>8</v>
       </c>
       <c r="T4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>8</v>
@@ -947,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
         <v>9</v>
@@ -956,7 +971,7 @@
         <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1024,7 +1039,7 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
         <v>7</v>
@@ -1033,7 +1048,7 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1101,7 +1116,7 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>7</v>
@@ -1110,7 +1125,7 @@
         <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1178,7 +1193,7 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>10</v>
@@ -1187,7 +1202,7 @@
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1196,7 +1211,7 @@
         <v>9</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>10</v>
@@ -1205,7 +1220,7 @@
         <v>7</v>
       </c>
       <c r="W8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>7</v>
@@ -1255,7 +1270,7 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>8</v>
@@ -1264,7 +1279,7 @@
         <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1332,7 +1347,7 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
         <v>8</v>
@@ -1341,7 +1356,7 @@
         <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1350,7 +1365,7 @@
         <v>9</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>8</v>
@@ -1409,7 +1424,7 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>8</v>
@@ -1418,7 +1433,7 @@
         <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1427,7 +1442,7 @@
         <v>9</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>8</v>
@@ -1486,16 +1501,16 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
         <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1507,13 +1522,13 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>5</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -1563,7 +1578,7 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>8</v>
@@ -1572,7 +1587,7 @@
         <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1590,7 +1605,7 @@
         <v>5</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>5</v>
@@ -1640,7 +1655,7 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>8</v>
@@ -1649,7 +1664,7 @@
         <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1717,16 +1732,16 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>5</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1744,7 +1759,7 @@
         <v>5</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1794,7 +1809,7 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>9</v>
@@ -1803,7 +1818,7 @@
         <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -1821,7 +1836,7 @@
         <v>6</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -1871,7 +1886,7 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>7</v>
@@ -1880,7 +1895,7 @@
         <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -1948,7 +1963,7 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>10</v>
@@ -1957,7 +1972,7 @@
         <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -1966,7 +1981,7 @@
         <v>10</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>10</v>
@@ -2025,7 +2040,7 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>7</v>
@@ -2034,7 +2049,7 @@
         <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2102,7 +2117,7 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
         <v>8</v>
@@ -2111,7 +2126,7 @@
         <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2120,7 +2135,7 @@
         <v>8</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2129,7 +2144,7 @@
         <v>6</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>6</v>
@@ -2179,7 +2194,7 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>8</v>
@@ -2188,7 +2203,7 @@
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2197,7 +2212,7 @@
         <v>9</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2256,7 +2271,7 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>8</v>
@@ -2265,7 +2280,7 @@
         <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2333,7 +2348,7 @@
         <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>7</v>
@@ -2342,7 +2357,7 @@
         <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2360,7 +2375,7 @@
         <v>5</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>5</v>
@@ -2410,7 +2425,7 @@
         <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
         <v>8</v>
@@ -2419,7 +2434,7 @@
         <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2428,7 +2443,7 @@
         <v>8</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U24">
         <v>7</v>
@@ -2437,7 +2452,7 @@
         <v>5</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>6</v>
@@ -2487,7 +2502,7 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>10</v>
@@ -2496,7 +2511,7 @@
         <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2505,7 +2520,7 @@
         <v>9</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>10</v>
@@ -2558,13 +2573,13 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
         <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2579,7 +2594,7 @@
         <v>8</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2629,16 +2644,16 @@
         <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
         <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -2650,13 +2665,13 @@
         <v>5</v>
       </c>
       <c r="U27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V27">
         <v>7</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>7</v>
@@ -2706,7 +2721,7 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>8</v>
@@ -2715,7 +2730,7 @@
         <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -2759,7 +2774,7 @@
         <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S29">
         <v>5</v>
@@ -2812,7 +2827,7 @@
         <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
         <v>9</v>
@@ -2821,7 +2836,7 @@
         <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -2889,7 +2904,7 @@
         <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
         <v>7</v>
@@ -2898,7 +2913,7 @@
         <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -2966,7 +2981,7 @@
         <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O32">
         <v>7</v>
@@ -2975,7 +2990,7 @@
         <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -2993,7 +3008,7 @@
         <v>6</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X32">
         <v>7</v>
@@ -3043,7 +3058,7 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>8</v>
@@ -3052,7 +3067,7 @@
         <v>6</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3061,7 +3076,7 @@
         <v>9</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U33">
         <v>8</v>
@@ -3120,7 +3135,7 @@
         <v>8</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
         <v>8</v>
@@ -3129,7 +3144,7 @@
         <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3138,7 +3153,7 @@
         <v>9</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U34">
         <v>7</v>
@@ -3147,7 +3162,7 @@
         <v>8</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>7</v>
@@ -3197,7 +3212,7 @@
         <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
         <v>8</v>
@@ -3206,7 +3221,7 @@
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -3215,7 +3230,7 @@
         <v>9</v>
       </c>
       <c r="T35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U35">
         <v>8</v>
@@ -3274,7 +3289,7 @@
         <v>5</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O36">
         <v>5</v>
@@ -3283,7 +3298,7 @@
         <v>5</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -3301,7 +3316,7 @@
         <v>5</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X36">
         <v>8</v>
@@ -3351,7 +3366,7 @@
         <v>6</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O37">
         <v>7</v>
@@ -3360,7 +3375,7 @@
         <v>5</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -3378,7 +3393,7 @@
         <v>5</v>
       </c>
       <c r="W37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X37">
         <v>5</v>
@@ -3428,7 +3443,7 @@
         <v>7</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O38">
         <v>7</v>
@@ -3437,7 +3452,7 @@
         <v>5</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -3455,7 +3470,7 @@
         <v>5</v>
       </c>
       <c r="W38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X38">
         <v>7</v>
@@ -3505,7 +3520,7 @@
         <v>5</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O39">
         <v>6</v>
@@ -3514,7 +3529,7 @@
         <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -3523,7 +3538,7 @@
         <v>8</v>
       </c>
       <c r="T39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U39">
         <v>6</v>
@@ -3532,7 +3547,7 @@
         <v>10</v>
       </c>
       <c r="W39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X39">
         <v>5</v>
@@ -3582,7 +3597,7 @@
         <v>9</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O40">
         <v>10</v>
@@ -3591,7 +3606,7 @@
         <v>8</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -3659,7 +3674,7 @@
         <v>7</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O41">
         <v>9</v>
@@ -3668,7 +3683,7 @@
         <v>6</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R41">
         <v>-1</v>
@@ -3736,7 +3751,7 @@
         <v>7</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O42">
         <v>8</v>
@@ -3745,7 +3760,7 @@
         <v>6</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R42">
         <v>-1</v>
@@ -3754,7 +3769,7 @@
         <v>8</v>
       </c>
       <c r="T42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U42">
         <v>8</v>
@@ -3763,7 +3778,7 @@
         <v>6</v>
       </c>
       <c r="W42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X42">
         <v>7</v>
@@ -3813,7 +3828,7 @@
         <v>7</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O43">
         <v>8</v>
@@ -3822,7 +3837,7 @@
         <v>10</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R43">
         <v>-1</v>
@@ -3831,7 +3846,7 @@
         <v>9</v>
       </c>
       <c r="T43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U43">
         <v>7</v>
@@ -3840,7 +3855,7 @@
         <v>9</v>
       </c>
       <c r="W43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X43">
         <v>5</v>
@@ -3890,7 +3905,7 @@
         <v>6</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O44">
         <v>8</v>
@@ -3899,7 +3914,7 @@
         <v>5</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R44">
         <v>-1</v>
@@ -3917,7 +3932,7 @@
         <v>5</v>
       </c>
       <c r="W44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X44">
         <v>6</v>
@@ -3967,7 +3982,7 @@
         <v>5</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O45">
         <v>7</v>
@@ -3976,7 +3991,7 @@
         <v>7</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R45">
         <v>-1</v>
@@ -3994,7 +4009,7 @@
         <v>6</v>
       </c>
       <c r="W45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X45">
         <v>5</v>
@@ -4154,7 +4169,7 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>77.5</v>
+        <v>82.8</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -4213,7 +4228,7 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -4331,7 +4346,7 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -4390,7 +4405,7 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -4449,7 +4464,7 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>70</v>
+        <v>62.5</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -4458,7 +4473,7 @@
         <v>81.7</v>
       </c>
       <c r="Q9">
-        <v>96.2</v>
+        <v>97.5</v>
       </c>
       <c r="R9">
         <v>75</v>
@@ -4508,7 +4523,7 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -4517,7 +4532,7 @@
         <v>88.3</v>
       </c>
       <c r="Q10">
-        <v>96.2</v>
+        <v>97.5</v>
       </c>
       <c r="R10">
         <v>97.5</v>
@@ -4626,10 +4641,10 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>60</v>
+        <v>37.5</v>
       </c>
       <c r="O12">
-        <v>51.1</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -4685,7 +4700,7 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>65</v>
+        <v>40.6</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -4744,7 +4759,7 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -4803,16 +4818,16 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>60</v>
+        <v>59.4</v>
       </c>
       <c r="O15">
-        <v>62.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="P15">
         <v>71.7</v>
       </c>
       <c r="Q15">
-        <v>96.2</v>
+        <v>97.5</v>
       </c>
       <c r="R15">
         <v>80</v>
@@ -4862,7 +4877,7 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>70</v>
+        <v>68.8</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -4921,7 +4936,7 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>67.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -4980,7 +4995,7 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>82.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -5039,7 +5054,7 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>95</v>
+        <v>59.4</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -5048,7 +5063,7 @@
         <v>88.3</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -5098,7 +5113,7 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -5275,7 +5290,7 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>67.5</v>
+        <v>42.2</v>
       </c>
       <c r="O23">
         <v>100</v>
@@ -5334,7 +5349,7 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>77.5</v>
+        <v>79.7</v>
       </c>
       <c r="O24">
         <v>100</v>
@@ -5446,7 +5461,7 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>67.5</v>
+        <v>67.2</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -5502,16 +5517,16 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>77.5</v>
+        <v>48.4</v>
       </c>
       <c r="O27">
-        <v>55.6</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P27">
         <v>86.7</v>
       </c>
       <c r="Q27">
-        <v>92.3</v>
+        <v>95</v>
       </c>
       <c r="R27">
         <v>90</v>
@@ -5561,7 +5576,7 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O28">
         <v>100</v>
@@ -5596,7 +5611,7 @@
         <v>41.7</v>
       </c>
       <c r="Q29">
-        <v>61.5</v>
+        <v>40</v>
       </c>
       <c r="S29">
         <v>26</v>
@@ -5643,7 +5658,7 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O30">
         <v>100</v>
@@ -5702,7 +5717,7 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O31">
         <v>100</v>
@@ -5761,7 +5776,7 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>77.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O32">
         <v>100</v>
@@ -5820,7 +5835,7 @@
         <v>100</v>
       </c>
       <c r="N33">
-        <v>87.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O33">
         <v>100</v>
@@ -5938,7 +5953,7 @@
         <v>100</v>
       </c>
       <c r="N35">
-        <v>87.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O35">
         <v>100</v>
@@ -5997,7 +6012,7 @@
         <v>87.5</v>
       </c>
       <c r="N36">
-        <v>85</v>
+        <v>53.1</v>
       </c>
       <c r="O36">
         <v>66.7</v>
@@ -6006,7 +6021,7 @@
         <v>66.7</v>
       </c>
       <c r="Q36">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="R36">
         <v>100</v>
@@ -6056,7 +6071,7 @@
         <v>100</v>
       </c>
       <c r="N37">
-        <v>82.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O37">
         <v>100</v>
@@ -6115,7 +6130,7 @@
         <v>100</v>
       </c>
       <c r="N38">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="O38">
         <v>88.90000000000001</v>
@@ -6174,7 +6189,7 @@
         <v>100</v>
       </c>
       <c r="N39">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="O39">
         <v>100</v>
@@ -6292,7 +6307,7 @@
         <v>100</v>
       </c>
       <c r="N41">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="O41">
         <v>100</v>
@@ -6351,7 +6366,7 @@
         <v>100</v>
       </c>
       <c r="N42">
-        <v>82.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O42">
         <v>100</v>
@@ -6410,7 +6425,7 @@
         <v>100</v>
       </c>
       <c r="N43">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O43">
         <v>100</v>
@@ -6469,7 +6484,7 @@
         <v>100</v>
       </c>
       <c r="N44">
-        <v>82.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="O44">
         <v>100</v>
@@ -6609,19 +6624,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F2" s="2">
-        <v>46.3</v>
+        <v>58.5</v>
       </c>
       <c r="G2" s="2">
-        <v>53.7</v>
+        <v>41.5</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6632,25 +6647,25 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2">
-        <v>66.7</v>
+        <v>73.2</v>
       </c>
       <c r="G3" s="2">
-        <v>33.3</v>
+        <v>26.8</v>
       </c>
       <c r="H3">
         <v>6.9</v>
@@ -6664,25 +6679,25 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
       </c>
       <c r="C4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2">
-        <v>73.2</v>
+        <v>75</v>
       </c>
       <c r="G4" s="2">
-        <v>26.8</v>
+        <v>25</v>
       </c>
       <c r="H4">
         <v>6.9</v>
@@ -6696,28 +6711,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>75</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>25</v>
+        <v>7.1</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6728,28 +6743,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
       </c>
       <c r="C6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>92.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G6" s="2">
+        <v>7.1</v>
+      </c>
+      <c r="H6">
         <v>7.3</v>
-      </c>
-      <c r="H6">
-        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6760,28 +6775,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>92.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>7.1</v>
+        <v>2.4</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6831,7 +6846,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6863,16 +6878,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920230</v>
+        <v>22330051920318</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6886,19 +6901,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920230</v>
+        <v>22330051920318</v>
       </c>
       <c r="B3" t="s">
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>68</v>
@@ -6909,22 +6924,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920232</v>
+        <v>20330051920237</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6932,22 +6947,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920232</v>
+        <v>20330051920237</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6955,16 +6970,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920239</v>
+        <v>22330051920366</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -6978,22 +6993,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920239</v>
+        <v>22330051920366</v>
       </c>
       <c r="B7" t="s">
         <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7001,16 +7016,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920357</v>
+        <v>22330051920259</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -7024,22 +7039,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920357</v>
+        <v>22330051920259</v>
       </c>
       <c r="B9" t="s">
         <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7047,22 +7062,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920237</v>
+        <v>22330051920176</v>
       </c>
       <c r="B10" t="s">
         <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7070,22 +7085,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920237</v>
+        <v>22330051920176</v>
       </c>
       <c r="B11" t="s">
         <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7093,22 +7108,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920401</v>
+        <v>22330051920230</v>
       </c>
       <c r="B12" t="s">
         <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7116,22 +7131,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920401</v>
+        <v>22330051920239</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7142,13 +7157,13 @@
         <v>22330051920240</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -7162,22 +7177,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920318</v>
+        <v>21330051420317</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7185,16 +7200,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051420317</v>
+        <v>22330051920246</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -7211,13 +7226,13 @@
         <v>22330051920251</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E17" t="s">
         <v>5</v>
@@ -7231,24 +7246,47 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920257</v>
+        <v>22330051920368</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920401</v>
+      </c>
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>67</v>
+      </c>
+      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ALCV - Estadisticos 20222.xlsx
+++ b/grupos/2ALCV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="119">
   <si>
     <t>Materia</t>
   </si>
@@ -221,12 +221,12 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>Medina Tolentino Francisco</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Medina Tolentino Francisco</t>
-  </si>
-  <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
@@ -248,12 +248,27 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>ESCOBAR</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
     <t>MARIANO</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -263,9 +278,6 @@
     <t>ZAVALA</t>
   </si>
   <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
     <t>GAMBOA</t>
   </si>
   <si>
@@ -281,10 +293,16 @@
     <t>MORALES</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
   </si>
   <si>
     <t>PORTILLA</t>
@@ -302,12 +320,6 @@
     <t>DELGADO</t>
   </si>
   <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
     <t>MARQUEZ</t>
   </si>
   <si>
@@ -320,7 +332,16 @@
     <t>GROT</t>
   </si>
   <si>
-    <t>PULIDO</t>
+    <t>FERNANDA MARGARITA</t>
+  </si>
+  <si>
+    <t>KEVIN ALEXIS</t>
+  </si>
+  <si>
+    <t>LUZ ALONDRA</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
   </si>
   <si>
     <t>ARACELI</t>
@@ -329,6 +350,9 @@
     <t>JACQUELINE</t>
   </si>
   <si>
+    <t>NOEMI DEL ROCIO</t>
+  </si>
+  <si>
     <t>AILYN</t>
   </si>
   <si>
@@ -338,9 +362,6 @@
     <t>AXEL GAEL</t>
   </si>
   <si>
-    <t>AZURA</t>
-  </si>
-  <si>
     <t>CRHIS AMINADAB</t>
   </si>
   <si>
@@ -354,12 +375,6 @@
   </si>
   <si>
     <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>HAZEL</t>
-  </si>
-  <si>
-    <t>JUAN EMANUEL</t>
   </si>
 </sst>
 </file>
@@ -897,7 +912,7 @@
         <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>8</v>
@@ -915,7 +930,7 @@
         <v>7</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -974,7 +989,7 @@
         <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>10</v>
@@ -992,7 +1007,7 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>9</v>
@@ -1051,7 +1066,7 @@
         <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
         <v>9</v>
@@ -1069,7 +1084,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1128,7 +1143,7 @@
         <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
         <v>9</v>
@@ -1146,7 +1161,7 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1205,7 +1220,7 @@
         <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
         <v>9</v>
@@ -1223,7 +1238,7 @@
         <v>7</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1282,7 +1297,7 @@
         <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>7</v>
@@ -1300,7 +1315,7 @@
         <v>6</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1359,7 +1374,7 @@
         <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
         <v>9</v>
@@ -1377,7 +1392,7 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1436,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>9</v>
@@ -1454,7 +1469,7 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1513,7 +1528,7 @@
         <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
         <v>6</v>
@@ -1531,7 +1546,7 @@
         <v>6</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1590,7 +1605,7 @@
         <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>7</v>
@@ -1608,7 +1623,7 @@
         <v>7</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1667,7 +1682,7 @@
         <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
         <v>9</v>
@@ -1744,7 +1759,7 @@
         <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
         <v>8</v>
@@ -1821,7 +1836,7 @@
         <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
         <v>8</v>
@@ -1898,7 +1913,7 @@
         <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
         <v>8</v>
@@ -1916,7 +1931,7 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -1975,7 +1990,7 @@
         <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>10</v>
@@ -2052,7 +2067,7 @@
         <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>5</v>
@@ -2070,7 +2085,7 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -2129,7 +2144,7 @@
         <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
         <v>8</v>
@@ -2206,7 +2221,7 @@
         <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
         <v>9</v>
@@ -2283,7 +2298,7 @@
         <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>10</v>
@@ -2360,7 +2375,7 @@
         <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
         <v>7</v>
@@ -2378,7 +2393,7 @@
         <v>6</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>6</v>
@@ -2437,7 +2452,7 @@
         <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
         <v>8</v>
@@ -2514,7 +2529,7 @@
         <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
         <v>9</v>
@@ -2582,7 +2597,7 @@
         <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S26">
         <v>7</v>
@@ -2597,7 +2612,7 @@
         <v>8</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>7</v>
@@ -2656,7 +2671,7 @@
         <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
         <v>8</v>
@@ -2674,7 +2689,7 @@
         <v>6</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2733,7 +2748,7 @@
         <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S28">
         <v>8</v>
@@ -2751,7 +2766,7 @@
         <v>7</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -2839,7 +2854,7 @@
         <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
         <v>8</v>
@@ -2857,7 +2872,7 @@
         <v>9</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -2916,7 +2931,7 @@
         <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
         <v>9</v>
@@ -2934,7 +2949,7 @@
         <v>7</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -2993,7 +3008,7 @@
         <v>8</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
         <v>8</v>
@@ -3070,7 +3085,7 @@
         <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
         <v>9</v>
@@ -3147,7 +3162,7 @@
         <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
         <v>9</v>
@@ -3224,7 +3239,7 @@
         <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
         <v>9</v>
@@ -3242,7 +3257,7 @@
         <v>9</v>
       </c>
       <c r="X35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y35">
         <v>7</v>
@@ -3301,7 +3316,7 @@
         <v>5</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S36">
         <v>5</v>
@@ -3319,7 +3334,7 @@
         <v>5</v>
       </c>
       <c r="X36">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y36">
         <v>5</v>
@@ -3378,7 +3393,7 @@
         <v>8</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S37">
         <v>7</v>
@@ -3396,7 +3411,7 @@
         <v>6</v>
       </c>
       <c r="X37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y37">
         <v>6</v>
@@ -3455,7 +3470,7 @@
         <v>8</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S38">
         <v>8</v>
@@ -3532,7 +3547,7 @@
         <v>8</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S39">
         <v>8</v>
@@ -3550,7 +3565,7 @@
         <v>6</v>
       </c>
       <c r="X39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y39">
         <v>6</v>
@@ -3609,7 +3624,7 @@
         <v>10</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S40">
         <v>9</v>
@@ -3686,7 +3701,7 @@
         <v>6</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S41">
         <v>8</v>
@@ -3763,7 +3778,7 @@
         <v>10</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S42">
         <v>8</v>
@@ -3840,7 +3855,7 @@
         <v>8</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S43">
         <v>9</v>
@@ -3858,7 +3873,7 @@
         <v>7</v>
       </c>
       <c r="X43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y43">
         <v>7</v>
@@ -3917,7 +3932,7 @@
         <v>8</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S44">
         <v>7</v>
@@ -3994,7 +4009,7 @@
         <v>8</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S45">
         <v>7</v>
@@ -4181,7 +4196,7 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -4358,7 +4373,7 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -4417,7 +4432,7 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -4476,7 +4491,7 @@
         <v>97.5</v>
       </c>
       <c r="R9">
-        <v>75</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -4535,7 +4550,7 @@
         <v>97.5</v>
       </c>
       <c r="R10">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -4594,7 +4609,7 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -4653,7 +4668,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>85</v>
+        <v>90.3</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -4712,7 +4727,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -4830,7 +4845,7 @@
         <v>97.5</v>
       </c>
       <c r="R15">
-        <v>80</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -4889,7 +4904,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>87.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -4948,7 +4963,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>87.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -5302,7 +5317,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -5361,7 +5376,7 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -5470,7 +5485,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -5529,7 +5544,7 @@
         <v>95</v>
       </c>
       <c r="R27">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -5670,7 +5685,7 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -5729,7 +5744,7 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -5788,7 +5803,7 @@
         <v>100</v>
       </c>
       <c r="R32">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S32">
         <v>100</v>
@@ -6024,7 +6039,7 @@
         <v>65</v>
       </c>
       <c r="R36">
-        <v>100</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="S36">
         <v>54.7</v>
@@ -6201,7 +6216,7 @@
         <v>100</v>
       </c>
       <c r="R39">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="S39">
         <v>100</v>
@@ -6260,7 +6275,7 @@
         <v>100</v>
       </c>
       <c r="R40">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="S40">
         <v>100</v>
@@ -6378,7 +6393,7 @@
         <v>100</v>
       </c>
       <c r="R42">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="S42">
         <v>100</v>
@@ -6496,7 +6511,7 @@
         <v>100</v>
       </c>
       <c r="R44">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S44">
         <v>100</v>
@@ -6555,7 +6570,7 @@
         <v>100</v>
       </c>
       <c r="R45">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="S45">
         <v>100</v>
@@ -6647,25 +6662,25 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3">
         <v>30</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2">
-        <v>73.2</v>
+        <v>75</v>
       </c>
       <c r="G3" s="2">
-        <v>26.8</v>
+        <v>25</v>
       </c>
       <c r="H3">
         <v>6.9</v>
@@ -6679,28 +6694,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>75</v>
+        <v>92.7</v>
       </c>
       <c r="G4" s="2">
-        <v>25</v>
+        <v>7.3</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6846,7 +6861,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6878,16 +6893,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920318</v>
+        <v>22330051920233</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6901,22 +6916,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920318</v>
+        <v>22330051920233</v>
       </c>
       <c r="B3" t="s">
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6924,22 +6939,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920237</v>
+        <v>22330051920236</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6947,22 +6962,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920237</v>
+        <v>22330051920236</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6970,16 +6985,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920366</v>
+        <v>22330051920237</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -6993,22 +7008,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920366</v>
+        <v>22330051920237</v>
       </c>
       <c r="B7" t="s">
         <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7016,16 +7031,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920259</v>
+        <v>22330051920369</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -7039,22 +7054,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920259</v>
+        <v>22330051920369</v>
       </c>
       <c r="B9" t="s">
         <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7062,16 +7077,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920176</v>
+        <v>22330051920318</v>
       </c>
       <c r="B10" t="s">
         <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -7085,19 +7100,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920176</v>
+        <v>22330051920318</v>
       </c>
       <c r="B11" t="s">
         <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
         <v>67</v>
@@ -7108,22 +7123,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920230</v>
+        <v>20330051920237</v>
       </c>
       <c r="B12" t="s">
         <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7131,22 +7146,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920239</v>
+        <v>20330051920237</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7154,16 +7169,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920240</v>
+        <v>22330051920253</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -7177,22 +7192,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051420317</v>
+        <v>22330051920253</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7200,16 +7215,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920246</v>
+        <v>22330051920366</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -7223,22 +7238,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920251</v>
+        <v>22330051920366</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
         <v>111</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -7246,22 +7261,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920368</v>
+        <v>22330051920259</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
         <v>112</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -7269,24 +7284,185 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920401</v>
+        <v>22330051920259</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
         <v>67</v>
       </c>
       <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>22330051920176</v>
+      </c>
+      <c r="B20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" t="s">
+        <v>66</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>22330051920176</v>
+      </c>
+      <c r="B21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>22330051920239</v>
+      </c>
+      <c r="B22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>22330051920240</v>
+      </c>
+      <c r="B23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" t="s">
+        <v>115</v>
+      </c>
+      <c r="E23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>21330051420317</v>
+      </c>
+      <c r="B24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" t="s">
+        <v>116</v>
+      </c>
+      <c r="E24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>22330051920246</v>
+      </c>
+      <c r="B25" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" t="s">
+        <v>102</v>
+      </c>
+      <c r="D25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>22330051920251</v>
+      </c>
+      <c r="B26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" t="s">
+        <v>118</v>
+      </c>
+      <c r="E26" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26">
         <v>5</v>
       </c>
     </row>
